--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2145">
   <si>
     <t>en</t>
   </si>
@@ -6043,400 +6043,403 @@
     <t>Страна витых чудес</t>
   </si>
   <si>
+    <t>ULTRAKILL</t>
+  </si>
+  <si>
+    <t>Umineko - When They Cry</t>
+  </si>
+  <si>
+    <t>Undertale</t>
+  </si>
+  <si>
+    <t>Undertale AU</t>
+  </si>
+  <si>
+    <t>Undertale Yellow</t>
+  </si>
+  <si>
+    <t>Universal Symbol</t>
+  </si>
+  <si>
+    <t>Универсальный символ</t>
+  </si>
+  <si>
+    <t>Up</t>
+  </si>
+  <si>
+    <t>Вверх</t>
+  </si>
+  <si>
+    <t>Urban Wildlife</t>
+  </si>
+  <si>
+    <t>Городская дикая природа</t>
+  </si>
+  <si>
+    <t>V for Vendetta</t>
+  </si>
+  <si>
+    <t>Valentines</t>
+  </si>
+  <si>
+    <t>Валентинки</t>
+  </si>
+  <si>
+    <t>Valorant</t>
+  </si>
+  <si>
+    <t>Vanilla (removed)</t>
+  </si>
+  <si>
+    <t>Ваниль (удалена)</t>
+  </si>
+  <si>
+    <t>Vanilla Block</t>
+  </si>
+  <si>
+    <t>Ванильный блок</t>
+  </si>
+  <si>
+    <t>Vanilla Food</t>
+  </si>
+  <si>
+    <t>Ванильная еда</t>
+  </si>
+  <si>
+    <t>Vanilla Helmet</t>
+  </si>
+  <si>
+    <t>Ванильный шлем</t>
+  </si>
+  <si>
+    <t>Vanilla Item</t>
+  </si>
+  <si>
+    <t>Ванильный предмет</t>
+  </si>
+  <si>
+    <t>Vanilla Mob</t>
+  </si>
+  <si>
+    <t>Ванильная мафия</t>
+  </si>
+  <si>
+    <t>Vault Hunters</t>
+  </si>
+  <si>
+    <t>Охотники за хранилищами</t>
+  </si>
+  <si>
+    <t>Vegetable</t>
+  </si>
+  <si>
+    <t>Овощи</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Автомобиль</t>
+  </si>
+  <si>
+    <t>Vikings</t>
+  </si>
+  <si>
+    <t>Викинги</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Житель</t>
+  </si>
+  <si>
+    <t>Villager (Desert)</t>
+  </si>
+  <si>
+    <t>Деревенский житель (Пустыня)</t>
+  </si>
+  <si>
+    <t>Villager (Jungle)</t>
+  </si>
+  <si>
+    <t>Деревенский житель (Джунгли)</t>
+  </si>
+  <si>
+    <t>Villager (Plains)</t>
+  </si>
+  <si>
+    <t>Деревенский житель (Равнины)</t>
+  </si>
+  <si>
+    <t>Villager (Savanna)</t>
+  </si>
+  <si>
+    <t>Деревенский житель (Саванна)</t>
+  </si>
+  <si>
+    <t>Villager (Snowy Tundra)</t>
+  </si>
+  <si>
+    <t>Деревенский житель (Снежная тундра)</t>
+  </si>
+  <si>
+    <t>Villager (Swamp)</t>
+  </si>
+  <si>
+    <t>Деревенский житель (Болото)</t>
+  </si>
+  <si>
+    <t>Villager (Taiga)</t>
+  </si>
+  <si>
+    <t>Деревенский житель (Тайга)</t>
+  </si>
+  <si>
+    <t>Virtual Youtuber</t>
+  </si>
+  <si>
+    <t>Виртуальный ютубер</t>
+  </si>
+  <si>
+    <t>Vocaloid</t>
+  </si>
+  <si>
+    <t>Вокалоид</t>
+  </si>
+  <si>
+    <t>Voltron</t>
+  </si>
+  <si>
+    <t>Вольтрон</t>
+  </si>
+  <si>
+    <t>Wakfu</t>
+  </si>
+  <si>
+    <t>Вакфу</t>
+  </si>
+  <si>
+    <t>Walking Dead</t>
+  </si>
+  <si>
+    <t>Ходячие мертвецы</t>
+  </si>
+  <si>
+    <t>Wall-E</t>
+  </si>
+  <si>
+    <t>Wallace and Gromit</t>
+  </si>
+  <si>
+    <t>Уоллес и Громит</t>
+  </si>
+  <si>
+    <t>War of the Worlds</t>
+  </si>
+  <si>
+    <t>Война миров</t>
+  </si>
+  <si>
+    <t>Warcraft</t>
+  </si>
+  <si>
+    <t>Варкрафт</t>
+  </si>
+  <si>
+    <t>Warframe</t>
+  </si>
+  <si>
+    <t>Warhammer</t>
+  </si>
+  <si>
+    <t>Warrior Cats</t>
+  </si>
+  <si>
+    <t>Коты-воители</t>
+  </si>
+  <si>
+    <t>We Bear Bears</t>
+  </si>
+  <si>
+    <t>Мы, медвежата</t>
+  </si>
+  <si>
+    <t>We Happy Few</t>
+  </si>
+  <si>
+    <t>Мы, счастливые немногие</t>
+  </si>
+  <si>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>Погода</t>
+  </si>
+  <si>
+    <t>Welcome Home</t>
+  </si>
+  <si>
+    <t>Добро пожаловать домой</t>
+  </si>
+  <si>
+    <t>Who is this?</t>
+  </si>
+  <si>
+    <t>Кто это?</t>
+  </si>
+  <si>
+    <t>Wild Update</t>
+  </si>
+  <si>
+    <t>Дикое обновление</t>
+  </si>
+  <si>
+    <t>Wings of Fire</t>
+  </si>
+  <si>
+    <t>Огненные крылья</t>
+  </si>
+  <si>
+    <t>Winnie the Pooh</t>
+  </si>
+  <si>
+    <t>Винни-Пух</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>Зима</t>
+  </si>
+  <si>
+    <t>Witcher</t>
+  </si>
+  <si>
+    <t>Ведьмак</t>
+  </si>
+  <si>
+    <t>Wonderful Wonder World</t>
+  </si>
+  <si>
+    <t>Удивительный мир чудес</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>Дерево</t>
+  </si>
+  <si>
+    <t>Wool</t>
+  </si>
+  <si>
+    <t>Шерсть</t>
+  </si>
+  <si>
+    <t>Work Safety Helmet</t>
+  </si>
+  <si>
+    <t>Рабочая защитная каска</t>
+  </si>
+  <si>
+    <t>Wreck It Ralph</t>
+  </si>
+  <si>
+    <t>Wybel</t>
+  </si>
+  <si>
+    <t>Вайбл</t>
+  </si>
+  <si>
+    <t>Wynncraft</t>
+  </si>
+  <si>
+    <t>Винкрафт</t>
+  </si>
+  <si>
+    <t>X-Men</t>
+  </si>
+  <si>
+    <t>Люди Икс</t>
+  </si>
+  <si>
+    <t>Xenoblade Chronicles</t>
+  </si>
+  <si>
+    <t>Yandere Simulator</t>
+  </si>
+  <si>
+    <t>Симулятор яндере</t>
+  </si>
+  <si>
+    <t>Yellow Submarine</t>
+  </si>
+  <si>
+    <t>Желтая подводная лодка</t>
+  </si>
+  <si>
+    <t>Yokai</t>
+  </si>
+  <si>
+    <t>Йокай</t>
+  </si>
+  <si>
+    <t>Yooka Laylee</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>Молодой</t>
+  </si>
+  <si>
+    <t>Youtube</t>
+  </si>
+  <si>
+    <t>Yu-Gi-Oh</t>
+  </si>
+  <si>
+    <t>Yume Nikki</t>
+  </si>
+  <si>
+    <t>Юмэ Никки</t>
+  </si>
+  <si>
+    <t>Zero no Tsukaima</t>
+  </si>
+  <si>
+    <t>Zero Wing</t>
+  </si>
+  <si>
+    <t>Нулевое крыло</t>
+  </si>
+  <si>
+    <t>Zodiac Sign</t>
+  </si>
+  <si>
+    <t>Знак зодиака</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>Зомби</t>
+  </si>
+  <si>
+    <t>Zombie (Vanilla)</t>
+  </si>
+  <si>
+    <t>Зомби (ваниль)</t>
+  </si>
+  <si>
+    <t>Zootopia</t>
+  </si>
+  <si>
     <t>Ultrakill</t>
   </si>
   <si>
     <t>Ультракилл</t>
-  </si>
-  <si>
-    <t>Umineko - When They Cry</t>
-  </si>
-  <si>
-    <t>Undertale</t>
-  </si>
-  <si>
-    <t>Undertale AU</t>
-  </si>
-  <si>
-    <t>Undertale Yellow</t>
-  </si>
-  <si>
-    <t>Universal Symbol</t>
-  </si>
-  <si>
-    <t>Универсальный символ</t>
-  </si>
-  <si>
-    <t>Up</t>
-  </si>
-  <si>
-    <t>Вверх</t>
-  </si>
-  <si>
-    <t>Urban Wildlife</t>
-  </si>
-  <si>
-    <t>Городская дикая природа</t>
-  </si>
-  <si>
-    <t>V for Vendetta</t>
-  </si>
-  <si>
-    <t>Valentines</t>
-  </si>
-  <si>
-    <t>Валентинки</t>
-  </si>
-  <si>
-    <t>Valorant</t>
-  </si>
-  <si>
-    <t>Vanilla (removed)</t>
-  </si>
-  <si>
-    <t>Ваниль (удалена)</t>
-  </si>
-  <si>
-    <t>Vanilla Block</t>
-  </si>
-  <si>
-    <t>Ванильный блок</t>
-  </si>
-  <si>
-    <t>Vanilla Food</t>
-  </si>
-  <si>
-    <t>Ванильная еда</t>
-  </si>
-  <si>
-    <t>Vanilla Helmet</t>
-  </si>
-  <si>
-    <t>Ванильный шлем</t>
-  </si>
-  <si>
-    <t>Vanilla Item</t>
-  </si>
-  <si>
-    <t>Ванильный предмет</t>
-  </si>
-  <si>
-    <t>Vanilla Mob</t>
-  </si>
-  <si>
-    <t>Ванильная мафия</t>
-  </si>
-  <si>
-    <t>Vault Hunters</t>
-  </si>
-  <si>
-    <t>Охотники за хранилищами</t>
-  </si>
-  <si>
-    <t>Vegetable</t>
-  </si>
-  <si>
-    <t>Овощи</t>
-  </si>
-  <si>
-    <t>Vehicle</t>
-  </si>
-  <si>
-    <t>Автомобиль</t>
-  </si>
-  <si>
-    <t>Vikings</t>
-  </si>
-  <si>
-    <t>Викинги</t>
-  </si>
-  <si>
-    <t>Villager</t>
-  </si>
-  <si>
-    <t>Житель</t>
-  </si>
-  <si>
-    <t>Villager (Desert)</t>
-  </si>
-  <si>
-    <t>Деревенский житель (Пустыня)</t>
-  </si>
-  <si>
-    <t>Villager (Jungle)</t>
-  </si>
-  <si>
-    <t>Деревенский житель (Джунгли)</t>
-  </si>
-  <si>
-    <t>Villager (Plains)</t>
-  </si>
-  <si>
-    <t>Деревенский житель (Равнины)</t>
-  </si>
-  <si>
-    <t>Villager (Savanna)</t>
-  </si>
-  <si>
-    <t>Деревенский житель (Саванна)</t>
-  </si>
-  <si>
-    <t>Villager (Snowy Tundra)</t>
-  </si>
-  <si>
-    <t>Деревенский житель (Снежная тундра)</t>
-  </si>
-  <si>
-    <t>Villager (Swamp)</t>
-  </si>
-  <si>
-    <t>Деревенский житель (Болото)</t>
-  </si>
-  <si>
-    <t>Villager (Taiga)</t>
-  </si>
-  <si>
-    <t>Деревенский житель (Тайга)</t>
-  </si>
-  <si>
-    <t>Virtual Youtuber</t>
-  </si>
-  <si>
-    <t>Виртуальный ютубер</t>
-  </si>
-  <si>
-    <t>Vocaloid</t>
-  </si>
-  <si>
-    <t>Вокалоид</t>
-  </si>
-  <si>
-    <t>Voltron</t>
-  </si>
-  <si>
-    <t>Вольтрон</t>
-  </si>
-  <si>
-    <t>Wakfu</t>
-  </si>
-  <si>
-    <t>Вакфу</t>
-  </si>
-  <si>
-    <t>Walking Dead</t>
-  </si>
-  <si>
-    <t>Ходячие мертвецы</t>
-  </si>
-  <si>
-    <t>Wall-E</t>
-  </si>
-  <si>
-    <t>Wallace and Gromit</t>
-  </si>
-  <si>
-    <t>Уоллес и Громит</t>
-  </si>
-  <si>
-    <t>War of the Worlds</t>
-  </si>
-  <si>
-    <t>Война миров</t>
-  </si>
-  <si>
-    <t>Warcraft</t>
-  </si>
-  <si>
-    <t>Варкрафт</t>
-  </si>
-  <si>
-    <t>Warframe</t>
-  </si>
-  <si>
-    <t>Warhammer</t>
-  </si>
-  <si>
-    <t>Warrior Cats</t>
-  </si>
-  <si>
-    <t>Коты-воители</t>
-  </si>
-  <si>
-    <t>We Bear Bears</t>
-  </si>
-  <si>
-    <t>Мы, медвежата</t>
-  </si>
-  <si>
-    <t>We Happy Few</t>
-  </si>
-  <si>
-    <t>Мы, счастливые немногие</t>
-  </si>
-  <si>
-    <t>Weather</t>
-  </si>
-  <si>
-    <t>Погода</t>
-  </si>
-  <si>
-    <t>Welcome Home</t>
-  </si>
-  <si>
-    <t>Добро пожаловать домой</t>
-  </si>
-  <si>
-    <t>Who is this?</t>
-  </si>
-  <si>
-    <t>Кто это?</t>
-  </si>
-  <si>
-    <t>Wild Update</t>
-  </si>
-  <si>
-    <t>Дикое обновление</t>
-  </si>
-  <si>
-    <t>Wings of Fire</t>
-  </si>
-  <si>
-    <t>Огненные крылья</t>
-  </si>
-  <si>
-    <t>Winnie the Pooh</t>
-  </si>
-  <si>
-    <t>Винни-Пух</t>
-  </si>
-  <si>
-    <t>Winter</t>
-  </si>
-  <si>
-    <t>Зима</t>
-  </si>
-  <si>
-    <t>Witcher</t>
-  </si>
-  <si>
-    <t>Ведьмак</t>
-  </si>
-  <si>
-    <t>Wonderful Wonder World</t>
-  </si>
-  <si>
-    <t>Удивительный мир чудес</t>
-  </si>
-  <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>Дерево</t>
-  </si>
-  <si>
-    <t>Wool</t>
-  </si>
-  <si>
-    <t>Шерсть</t>
-  </si>
-  <si>
-    <t>Work Safety Helmet</t>
-  </si>
-  <si>
-    <t>Рабочая защитная каска</t>
-  </si>
-  <si>
-    <t>Wreck It Ralph</t>
-  </si>
-  <si>
-    <t>Wybel</t>
-  </si>
-  <si>
-    <t>Вайбл</t>
-  </si>
-  <si>
-    <t>Wynncraft</t>
-  </si>
-  <si>
-    <t>Винкрафт</t>
-  </si>
-  <si>
-    <t>X-Men</t>
-  </si>
-  <si>
-    <t>Люди Икс</t>
-  </si>
-  <si>
-    <t>Xenoblade Chronicles</t>
-  </si>
-  <si>
-    <t>Yandere Simulator</t>
-  </si>
-  <si>
-    <t>Симулятор яндере</t>
-  </si>
-  <si>
-    <t>Yellow Submarine</t>
-  </si>
-  <si>
-    <t>Желтая подводная лодка</t>
-  </si>
-  <si>
-    <t>Yokai</t>
-  </si>
-  <si>
-    <t>Йокай</t>
-  </si>
-  <si>
-    <t>Yooka Laylee</t>
-  </si>
-  <si>
-    <t>Young</t>
-  </si>
-  <si>
-    <t>Молодой</t>
-  </si>
-  <si>
-    <t>Youtube</t>
-  </si>
-  <si>
-    <t>Yu-Gi-Oh</t>
-  </si>
-  <si>
-    <t>Yume Nikki</t>
-  </si>
-  <si>
-    <t>Юмэ Никки</t>
-  </si>
-  <si>
-    <t>Zero no Tsukaima</t>
-  </si>
-  <si>
-    <t>Zero Wing</t>
-  </si>
-  <si>
-    <t>Нулевое крыло</t>
-  </si>
-  <si>
-    <t>Zodiac Sign</t>
-  </si>
-  <si>
-    <t>Знак зодиака</t>
-  </si>
-  <si>
-    <t>Zombie</t>
-  </si>
-  <si>
-    <t>Зомби</t>
-  </si>
-  <si>
-    <t>Zombie (Vanilla)</t>
-  </si>
-  <si>
-    <t>Зомби (ваниль)</t>
-  </si>
-  <si>
-    <t>Zootopia</t>
   </si>
   <si>
     <t>Hypixel (Mutations) Tag</t>
@@ -6795,7 +6798,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1177"/>
+  <dimension ref="A1:B1178"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -15615,611 +15618,619 @@
         <v>2008</v>
       </c>
       <c r="B1102" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B1103" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B1104" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B1105" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B1106" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B1107" t="s">
         <v>2014</v>
-      </c>
-      <c r="B1107" t="s">
-        <v>2015</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1108" t="s">
         <v>2016</v>
-      </c>
-      <c r="B1108" t="s">
-        <v>2017</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B1109" t="s">
         <v>2018</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>2019</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B1110" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B1111" t="s">
         <v>2021</v>
-      </c>
-      <c r="B1111" t="s">
-        <v>2022</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B1112" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B1113" t="s">
         <v>2024</v>
-      </c>
-      <c r="B1113" t="s">
-        <v>2025</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B1114" t="s">
         <v>2026</v>
-      </c>
-      <c r="B1114" t="s">
-        <v>2027</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B1115" t="s">
         <v>2028</v>
-      </c>
-      <c r="B1115" t="s">
-        <v>2029</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B1116" t="s">
         <v>2030</v>
-      </c>
-      <c r="B1116" t="s">
-        <v>2031</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B1117" t="s">
         <v>2032</v>
-      </c>
-      <c r="B1117" t="s">
-        <v>2033</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B1118" t="s">
         <v>2034</v>
-      </c>
-      <c r="B1118" t="s">
-        <v>2035</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B1119" t="s">
         <v>2036</v>
-      </c>
-      <c r="B1119" t="s">
-        <v>2037</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B1120" t="s">
         <v>2038</v>
-      </c>
-      <c r="B1120" t="s">
-        <v>2039</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B1121" t="s">
         <v>2040</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>2041</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B1122" t="s">
         <v>2042</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>2043</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B1123" t="s">
         <v>2044</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>2045</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B1124" t="s">
         <v>2046</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>2047</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B1125" t="s">
         <v>2048</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>2049</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B1126" t="s">
         <v>2050</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>2051</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B1127" t="s">
         <v>2052</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>2053</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B1128" t="s">
         <v>2054</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B1129" t="s">
         <v>2056</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>2057</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B1130" t="s">
         <v>2058</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>2059</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B1131" t="s">
         <v>2060</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>2061</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B1132" t="s">
         <v>2062</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>2063</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B1133" t="s">
         <v>2064</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>2065</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B1134" t="s">
         <v>2066</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>2067</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B1135" t="s">
         <v>2068</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>2069</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="B1136" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B1137" t="s">
         <v>2071</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>2072</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B1138" t="s">
         <v>2073</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>2074</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B1139" t="s">
         <v>2075</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>2076</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="B1140" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="B1141" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B1142" t="s">
         <v>2079</v>
-      </c>
-      <c r="B1142" t="s">
-        <v>2080</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B1143" t="s">
         <v>2081</v>
-      </c>
-      <c r="B1143" t="s">
-        <v>2082</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B1144" t="s">
         <v>2083</v>
-      </c>
-      <c r="B1144" t="s">
-        <v>2084</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B1145" t="s">
         <v>2085</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>2086</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B1146" t="s">
         <v>2087</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>2088</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B1147" t="s">
         <v>2089</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>2090</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B1148" t="s">
         <v>2091</v>
-      </c>
-      <c r="B1148" t="s">
-        <v>2092</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B1149" t="s">
         <v>2093</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>2094</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B1150" t="s">
         <v>2095</v>
-      </c>
-      <c r="B1150" t="s">
-        <v>2096</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B1151" t="s">
         <v>2097</v>
-      </c>
-      <c r="B1151" t="s">
-        <v>2098</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
+        <v>2098</v>
+      </c>
+      <c r="B1152" t="s">
         <v>2099</v>
-      </c>
-      <c r="B1152" t="s">
-        <v>2100</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B1153" t="s">
         <v>2101</v>
-      </c>
-      <c r="B1153" t="s">
-        <v>2102</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B1154" t="s">
         <v>2103</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>2104</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B1155" t="s">
         <v>2105</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>2106</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B1156" t="s">
         <v>2107</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>2108</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="B1157" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1158" t="s">
         <v>2110</v>
-      </c>
-      <c r="B1158" t="s">
-        <v>2111</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B1159" t="s">
         <v>2112</v>
-      </c>
-      <c r="B1159" t="s">
-        <v>2113</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B1160" t="s">
         <v>2114</v>
-      </c>
-      <c r="B1160" t="s">
-        <v>2115</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="B1161" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B1162" t="s">
         <v>2117</v>
-      </c>
-      <c r="B1162" t="s">
-        <v>2118</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B1163" t="s">
         <v>2119</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>2120</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B1164" t="s">
         <v>2121</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>2122</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="B1165" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B1166" t="s">
         <v>2124</v>
-      </c>
-      <c r="B1166" t="s">
-        <v>2125</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="B1167" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="B1168" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B1169" t="s">
         <v>2128</v>
-      </c>
-      <c r="B1169" t="s">
-        <v>2129</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="B1170" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B1171" t="s">
         <v>2131</v>
-      </c>
-      <c r="B1171" t="s">
-        <v>2132</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B1172" t="s">
         <v>2133</v>
-      </c>
-      <c r="B1172" t="s">
-        <v>2134</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B1173" t="s">
         <v>2135</v>
-      </c>
-      <c r="B1173" t="s">
-        <v>2136</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B1174" t="s">
         <v>2137</v>
-      </c>
-      <c r="B1174" t="s">
-        <v>2138</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="B1175" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B1176" t="s">
         <v>2140</v>
-      </c>
-      <c r="B1176" t="s">
-        <v>2141</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B1177" t="s">
         <v>2142</v>
       </c>
-      <c r="B1177" t="s">
+    </row>
+    <row r="1178" spans="1:2">
+      <c r="A1178" t="s">
         <v>2143</v>
       </c>
+      <c r="B1178" t="s">
+        <v>2144</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1177"/>
+  <autoFilter ref="A1:B1178"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2147">
   <si>
     <t>en</t>
   </si>
@@ -4409,6 +4409,12 @@
   </si>
   <si>
     <t>Объекты с открытым исходным кодом</t>
+  </si>
+  <si>
+    <t>Opus Magnum</t>
+  </si>
+  <si>
+    <t>Опус Магнум</t>
   </si>
   <si>
     <t>Orb</t>
@@ -6798,7 +6804,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1178"/>
+  <dimension ref="A1:B1179"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13186,15 +13192,15 @@
         <v>1464</v>
       </c>
       <c r="B798" t="s">
-        <v>132</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B799" t="s">
-        <v>1466</v>
+        <v>132</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -13258,20 +13264,20 @@
         <v>1481</v>
       </c>
       <c r="B807" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B808" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B809" t="s">
         <v>1484</v>
@@ -13322,20 +13328,20 @@
         <v>1495</v>
       </c>
       <c r="B815" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B816" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B817" t="s">
         <v>1498</v>
@@ -13354,20 +13360,20 @@
         <v>1501</v>
       </c>
       <c r="B819" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B820" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B821" t="s">
         <v>1504</v>
@@ -13402,12 +13408,12 @@
         <v>1511</v>
       </c>
       <c r="B825" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B826" t="s">
         <v>1513</v>
@@ -13458,28 +13464,28 @@
         <v>1524</v>
       </c>
       <c r="B832" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B833" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B834" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B835" t="s">
         <v>1528</v>
@@ -13538,12 +13544,12 @@
         <v>1541</v>
       </c>
       <c r="B842" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B843" t="s">
         <v>1543</v>
@@ -13562,84 +13568,84 @@
         <v>1546</v>
       </c>
       <c r="B845" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B846" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B847" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B848" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B849" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B850" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B851" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B852" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B853" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B854" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B855" t="s">
         <v>1557</v>
@@ -13698,12 +13704,12 @@
         <v>1570</v>
       </c>
       <c r="B862" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B863" t="s">
         <v>1572</v>
@@ -13826,20 +13832,20 @@
         <v>1601</v>
       </c>
       <c r="B878" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B879" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B880" t="s">
         <v>1604</v>
@@ -13890,12 +13896,12 @@
         <v>1615</v>
       </c>
       <c r="B886" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B887" t="s">
         <v>1617</v>
@@ -13906,12 +13912,12 @@
         <v>1618</v>
       </c>
       <c r="B888" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B889" t="s">
         <v>1620</v>
@@ -13922,12 +13928,12 @@
         <v>1621</v>
       </c>
       <c r="B890" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B891" t="s">
         <v>1623</v>
@@ -14050,12 +14056,12 @@
         <v>1652</v>
       </c>
       <c r="B906" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B907" t="s">
         <v>1654</v>
@@ -14122,20 +14128,20 @@
         <v>1669</v>
       </c>
       <c r="B915" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B916" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B917" t="s">
         <v>1672</v>
@@ -14186,12 +14192,12 @@
         <v>1683</v>
       </c>
       <c r="B923" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B924" t="s">
         <v>1685</v>
@@ -14250,12 +14256,12 @@
         <v>1698</v>
       </c>
       <c r="B931" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="932" spans="1:2">
       <c r="A932" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B932" t="s">
         <v>1700</v>
@@ -14266,12 +14272,12 @@
         <v>1701</v>
       </c>
       <c r="B933" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B934" t="s">
         <v>1703</v>
@@ -14306,12 +14312,12 @@
         <v>1710</v>
       </c>
       <c r="B938" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B939" t="s">
         <v>1712</v>
@@ -14338,12 +14344,12 @@
         <v>1717</v>
       </c>
       <c r="B942" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B943" t="s">
         <v>1719</v>
@@ -14402,12 +14408,12 @@
         <v>1732</v>
       </c>
       <c r="B950" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B951" t="s">
         <v>1734</v>
@@ -14450,20 +14456,20 @@
         <v>1743</v>
       </c>
       <c r="B956" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B957" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B958" t="s">
         <v>1746</v>
@@ -14522,12 +14528,12 @@
         <v>1759</v>
       </c>
       <c r="B965" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B966" t="s">
         <v>1761</v>
@@ -14642,12 +14648,12 @@
         <v>1788</v>
       </c>
       <c r="B980" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="B981" t="s">
         <v>1790</v>
@@ -14674,20 +14680,20 @@
         <v>1795</v>
       </c>
       <c r="B984" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B985" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B986" t="s">
         <v>1798</v>
@@ -14706,12 +14712,12 @@
         <v>1801</v>
       </c>
       <c r="B988" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B989" t="s">
         <v>1803</v>
@@ -14746,12 +14752,12 @@
         <v>1810</v>
       </c>
       <c r="B993" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B994" t="s">
         <v>1812</v>
@@ -14770,12 +14776,12 @@
         <v>1815</v>
       </c>
       <c r="B996" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B997" t="s">
         <v>1817</v>
@@ -14826,20 +14832,20 @@
         <v>1828</v>
       </c>
       <c r="B1003" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1004" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B1005" t="s">
         <v>1831</v>
@@ -14874,12 +14880,12 @@
         <v>1838</v>
       </c>
       <c r="B1009" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B1010" t="s">
         <v>1840</v>
@@ -14938,12 +14944,12 @@
         <v>1853</v>
       </c>
       <c r="B1017" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1018" t="s">
         <v>1855</v>
@@ -15018,12 +15024,12 @@
         <v>1872</v>
       </c>
       <c r="B1027" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B1028" t="s">
         <v>1874</v>
@@ -15034,44 +15040,44 @@
         <v>1875</v>
       </c>
       <c r="B1029" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="B1030" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="B1031" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B1032" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B1033" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1034" t="s">
         <v>1881</v>
@@ -15098,12 +15104,12 @@
         <v>1886</v>
       </c>
       <c r="B1037" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="B1038" t="s">
         <v>1888</v>
@@ -15130,12 +15136,12 @@
         <v>1893</v>
       </c>
       <c r="B1041" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="B1042" t="s">
         <v>1895</v>
@@ -15170,12 +15176,12 @@
         <v>1902</v>
       </c>
       <c r="B1046" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B1047" t="s">
         <v>1904</v>
@@ -15186,12 +15192,12 @@
         <v>1905</v>
       </c>
       <c r="B1048" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1049" t="s">
         <v>1907</v>
@@ -15282,12 +15288,12 @@
         <v>1928</v>
       </c>
       <c r="B1060" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="B1061" t="s">
         <v>1930</v>
@@ -15410,12 +15416,12 @@
         <v>1959</v>
       </c>
       <c r="B1076" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="B1077" t="s">
         <v>1961</v>
@@ -15434,12 +15440,12 @@
         <v>1964</v>
       </c>
       <c r="B1079" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B1080" t="s">
         <v>1966</v>
@@ -15538,12 +15544,12 @@
         <v>1989</v>
       </c>
       <c r="B1092" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="B1093" t="s">
         <v>1991</v>
@@ -15618,44 +15624,44 @@
         <v>2008</v>
       </c>
       <c r="B1102" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B1103" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B1104" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B1105" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B1106" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B1107" t="s">
         <v>2014</v>
@@ -15682,12 +15688,12 @@
         <v>2019</v>
       </c>
       <c r="B1110" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B1111" t="s">
         <v>2021</v>
@@ -15698,12 +15704,12 @@
         <v>2022</v>
       </c>
       <c r="B1112" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B1113" t="s">
         <v>2024</v>
@@ -15890,12 +15896,12 @@
         <v>2069</v>
       </c>
       <c r="B1136" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="B1137" t="s">
         <v>2071</v>
@@ -15922,20 +15928,20 @@
         <v>2076</v>
       </c>
       <c r="B1140" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="B1141" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="B1142" t="s">
         <v>2079</v>
@@ -16058,12 +16064,12 @@
         <v>2108</v>
       </c>
       <c r="B1157" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="B1158" t="s">
         <v>2110</v>
@@ -16090,12 +16096,12 @@
         <v>2115</v>
       </c>
       <c r="B1161" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="B1162" t="s">
         <v>2117</v>
@@ -16122,12 +16128,12 @@
         <v>2122</v>
       </c>
       <c r="B1165" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="B1166" t="s">
         <v>2124</v>
@@ -16138,20 +16144,20 @@
         <v>2125</v>
       </c>
       <c r="B1167" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="B1168" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="B1169" t="s">
         <v>2128</v>
@@ -16162,12 +16168,12 @@
         <v>2129</v>
       </c>
       <c r="B1170" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="B1171" t="s">
         <v>2131</v>
@@ -16202,12 +16208,12 @@
         <v>2138</v>
       </c>
       <c r="B1175" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="B1176" t="s">
         <v>2140</v>
@@ -16229,8 +16235,16 @@
         <v>2144</v>
       </c>
     </row>
+    <row r="1179" spans="1:2">
+      <c r="A1179" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>2146</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1178"/>
+  <autoFilter ref="A1:B1179"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1180</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2149">
   <si>
     <t>en</t>
   </si>
@@ -923,6 +923,12 @@
   </si>
   <si>
     <t>Чаша</t>
+  </si>
+  <si>
+    <t>Chaos Cubed</t>
+  </si>
+  <si>
+    <t>Кубик хаоса</t>
   </si>
   <si>
     <t>Charlie and the Chocolate Factory</t>
@@ -6804,7 +6810,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1179"/>
+  <dimension ref="A1:B1180"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -8168,12 +8174,12 @@
         <v>316</v>
       </c>
       <c r="B170" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B171" t="s">
         <v>318</v>
@@ -8208,12 +8214,12 @@
         <v>325</v>
       </c>
       <c r="B175" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B176" t="s">
         <v>327</v>
@@ -8224,12 +8230,12 @@
         <v>328</v>
       </c>
       <c r="B177" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B178" t="s">
         <v>330</v>
@@ -8240,20 +8246,20 @@
         <v>331</v>
       </c>
       <c r="B179" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B180" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B181" t="s">
         <v>334</v>
@@ -8472,12 +8478,12 @@
         <v>387</v>
       </c>
       <c r="B208" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B209" t="s">
         <v>389</v>
@@ -8520,12 +8526,12 @@
         <v>398</v>
       </c>
       <c r="B214" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B215" t="s">
         <v>400</v>
@@ -8544,12 +8550,12 @@
         <v>403</v>
       </c>
       <c r="B217" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B218" t="s">
         <v>405</v>
@@ -8576,20 +8582,20 @@
         <v>410</v>
       </c>
       <c r="B221" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B222" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B223" t="s">
         <v>413</v>
@@ -8648,12 +8654,12 @@
         <v>426</v>
       </c>
       <c r="B230" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B231" t="s">
         <v>428</v>
@@ -8784,12 +8790,12 @@
         <v>459</v>
       </c>
       <c r="B247" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B248" t="s">
         <v>461</v>
@@ -8808,12 +8814,12 @@
         <v>464</v>
       </c>
       <c r="B250" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B251" t="s">
         <v>466</v>
@@ -8824,20 +8830,20 @@
         <v>467</v>
       </c>
       <c r="B252" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B253" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B254" t="s">
         <v>470</v>
@@ -8848,12 +8854,12 @@
         <v>471</v>
       </c>
       <c r="B255" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B256" t="s">
         <v>473</v>
@@ -8928,12 +8934,12 @@
         <v>490</v>
       </c>
       <c r="B265" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B266" t="s">
         <v>492</v>
@@ -8952,12 +8958,12 @@
         <v>495</v>
       </c>
       <c r="B268" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B269" t="s">
         <v>497</v>
@@ -8968,12 +8974,12 @@
         <v>498</v>
       </c>
       <c r="B270" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B271" t="s">
         <v>500</v>
@@ -9000,12 +9006,12 @@
         <v>505</v>
       </c>
       <c r="B274" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B275" t="s">
         <v>507</v>
@@ -9056,12 +9062,12 @@
         <v>518</v>
       </c>
       <c r="B281" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B282" t="s">
         <v>520</v>
@@ -9088,12 +9094,12 @@
         <v>525</v>
       </c>
       <c r="B285" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B286" t="s">
         <v>527</v>
@@ -9120,12 +9126,12 @@
         <v>532</v>
       </c>
       <c r="B289" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B290" t="s">
         <v>534</v>
@@ -9160,20 +9166,20 @@
         <v>541</v>
       </c>
       <c r="B294" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B295" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B296" t="s">
         <v>544</v>
@@ -9352,20 +9358,20 @@
         <v>587</v>
       </c>
       <c r="B318" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B319" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B320" t="s">
         <v>590</v>
@@ -9400,12 +9406,12 @@
         <v>597</v>
       </c>
       <c r="B324" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B325" t="s">
         <v>599</v>
@@ -9448,12 +9454,12 @@
         <v>608</v>
       </c>
       <c r="B330" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B331" t="s">
         <v>610</v>
@@ -9520,12 +9526,12 @@
         <v>625</v>
       </c>
       <c r="B339" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B340" t="s">
         <v>627</v>
@@ -9680,12 +9686,12 @@
         <v>664</v>
       </c>
       <c r="B359" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B360" t="s">
         <v>666</v>
@@ -9712,12 +9718,12 @@
         <v>671</v>
       </c>
       <c r="B363" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B364" t="s">
         <v>673</v>
@@ -10256,12 +10262,12 @@
         <v>806</v>
       </c>
       <c r="B431" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B432" t="s">
         <v>808</v>
@@ -10296,12 +10302,12 @@
         <v>815</v>
       </c>
       <c r="B436" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B437" t="s">
         <v>817</v>
@@ -10360,12 +10366,12 @@
         <v>830</v>
       </c>
       <c r="B444" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B445" t="s">
         <v>832</v>
@@ -10392,12 +10398,12 @@
         <v>837</v>
       </c>
       <c r="B448" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B449" t="s">
         <v>839</v>
@@ -10440,12 +10446,12 @@
         <v>848</v>
       </c>
       <c r="B454" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="455" spans="1:2">
       <c r="A455" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B455" t="s">
         <v>850</v>
@@ -10528,20 +10534,20 @@
         <v>869</v>
       </c>
       <c r="B465" t="s">
-        <v>586</v>
+        <v>870</v>
       </c>
     </row>
     <row r="466" spans="1:2">
       <c r="A466" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B466" t="s">
-        <v>870</v>
+        <v>588</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B467" t="s">
         <v>872</v>
@@ -10584,15 +10590,15 @@
         <v>881</v>
       </c>
       <c r="B472" t="s">
-        <v>586</v>
+        <v>882</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B473" t="s">
-        <v>883</v>
+        <v>588</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -10600,12 +10606,12 @@
         <v>884</v>
       </c>
       <c r="B474" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B475" t="s">
         <v>886</v>
@@ -10656,12 +10662,12 @@
         <v>897</v>
       </c>
       <c r="B481" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B482" t="s">
         <v>899</v>
@@ -10680,12 +10686,12 @@
         <v>902</v>
       </c>
       <c r="B484" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B485" t="s">
         <v>904</v>
@@ -10696,12 +10702,12 @@
         <v>905</v>
       </c>
       <c r="B486" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B487" t="s">
         <v>907</v>
@@ -10880,12 +10886,12 @@
         <v>950</v>
       </c>
       <c r="B509" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="510" spans="1:2">
       <c r="A510" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B510" t="s">
         <v>952</v>
@@ -10904,12 +10910,12 @@
         <v>955</v>
       </c>
       <c r="B512" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B513" t="s">
         <v>957</v>
@@ -11056,12 +11062,12 @@
         <v>992</v>
       </c>
       <c r="B531" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B532" t="s">
         <v>994</v>
@@ -11208,76 +11214,76 @@
         <v>1029</v>
       </c>
       <c r="B550" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B551" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B552" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B553" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B554" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B555" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B556" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B557" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B558" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B559" t="s">
         <v>1039</v>
@@ -11304,20 +11310,20 @@
         <v>1044</v>
       </c>
       <c r="B562" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B563" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B564" t="s">
         <v>1047</v>
@@ -11392,12 +11398,12 @@
         <v>1064</v>
       </c>
       <c r="B573" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B574" t="s">
         <v>1066</v>
@@ -11416,20 +11422,20 @@
         <v>1069</v>
       </c>
       <c r="B576" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B577" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B578" t="s">
         <v>1072</v>
@@ -11464,12 +11470,12 @@
         <v>1079</v>
       </c>
       <c r="B582" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B583" t="s">
         <v>1081</v>
@@ -11480,12 +11486,12 @@
         <v>1082</v>
       </c>
       <c r="B584" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B585" t="s">
         <v>1084</v>
@@ -11512,12 +11518,12 @@
         <v>1089</v>
       </c>
       <c r="B588" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B589" t="s">
         <v>1091</v>
@@ -11552,12 +11558,12 @@
         <v>1098</v>
       </c>
       <c r="B593" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B594" t="s">
         <v>1100</v>
@@ -11632,12 +11638,12 @@
         <v>1117</v>
       </c>
       <c r="B603" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B604" t="s">
         <v>1119</v>
@@ -11680,12 +11686,12 @@
         <v>1128</v>
       </c>
       <c r="B609" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B610" t="s">
         <v>1130</v>
@@ -11696,12 +11702,12 @@
         <v>1131</v>
       </c>
       <c r="B611" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B612" t="s">
         <v>1133</v>
@@ -11744,12 +11750,12 @@
         <v>1142</v>
       </c>
       <c r="B617" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B618" t="s">
         <v>1144</v>
@@ -11784,12 +11790,12 @@
         <v>1151</v>
       </c>
       <c r="B622" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B623" t="s">
         <v>1153</v>
@@ -11856,20 +11862,20 @@
         <v>1168</v>
       </c>
       <c r="B631" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B632" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B633" t="s">
         <v>1171</v>
@@ -11888,12 +11894,12 @@
         <v>1174</v>
       </c>
       <c r="B635" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B636" t="s">
         <v>1176</v>
@@ -11904,20 +11910,20 @@
         <v>1177</v>
       </c>
       <c r="B637" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B638" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B639" t="s">
         <v>1180</v>
@@ -11960,12 +11966,12 @@
         <v>1189</v>
       </c>
       <c r="B644" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B645" t="s">
         <v>1191</v>
@@ -12000,12 +12006,12 @@
         <v>1198</v>
       </c>
       <c r="B649" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B650" t="s">
         <v>1200</v>
@@ -12016,12 +12022,12 @@
         <v>1201</v>
       </c>
       <c r="B651" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B652" t="s">
         <v>1203</v>
@@ -12264,20 +12270,20 @@
         <v>1262</v>
       </c>
       <c r="B682" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B683" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B684" t="s">
         <v>1265</v>
@@ -12336,12 +12342,12 @@
         <v>1278</v>
       </c>
       <c r="B691" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B692" t="s">
         <v>1280</v>
@@ -12408,12 +12414,12 @@
         <v>1295</v>
       </c>
       <c r="B700" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B701" t="s">
         <v>1297</v>
@@ -12424,20 +12430,20 @@
         <v>1298</v>
       </c>
       <c r="B702" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B703" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B704" t="s">
         <v>1301</v>
@@ -12480,12 +12486,12 @@
         <v>1310</v>
       </c>
       <c r="B709" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B710" t="s">
         <v>1312</v>
@@ -12496,12 +12502,12 @@
         <v>1313</v>
       </c>
       <c r="B711" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B712" t="s">
         <v>1315</v>
@@ -12536,12 +12542,12 @@
         <v>1322</v>
       </c>
       <c r="B716" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B717" t="s">
         <v>1324</v>
@@ -12560,12 +12566,12 @@
         <v>1327</v>
       </c>
       <c r="B719" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B720" t="s">
         <v>1329</v>
@@ -12576,20 +12582,20 @@
         <v>1330</v>
       </c>
       <c r="B721" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B722" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B723" t="s">
         <v>1333</v>
@@ -12608,12 +12614,12 @@
         <v>1336</v>
       </c>
       <c r="B725" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B726" t="s">
         <v>1338</v>
@@ -12624,20 +12630,20 @@
         <v>1339</v>
       </c>
       <c r="B727" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B728" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B729" t="s">
         <v>1342</v>
@@ -12704,12 +12710,12 @@
         <v>1357</v>
       </c>
       <c r="B737" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B738" t="s">
         <v>1359</v>
@@ -12736,12 +12742,12 @@
         <v>1364</v>
       </c>
       <c r="B741" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B742" t="s">
         <v>1366</v>
@@ -12856,20 +12862,20 @@
         <v>1393</v>
       </c>
       <c r="B756" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B757" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="758" spans="1:2">
       <c r="A758" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B758" t="s">
         <v>1396</v>
@@ -12912,12 +12918,12 @@
         <v>1405</v>
       </c>
       <c r="B763" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B764" t="s">
         <v>1407</v>
@@ -12960,12 +12966,12 @@
         <v>1416</v>
       </c>
       <c r="B769" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B770" t="s">
         <v>1418</v>
@@ -13000,12 +13006,12 @@
         <v>1425</v>
       </c>
       <c r="B774" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="775" spans="1:2">
       <c r="A775" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B775" t="s">
         <v>1427</v>
@@ -13072,28 +13078,28 @@
         <v>1442</v>
       </c>
       <c r="B783" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B784" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B785" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B786" t="s">
         <v>1446</v>
@@ -13144,44 +13150,44 @@
         <v>1457</v>
       </c>
       <c r="B792" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B793" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B794" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B795" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B796" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B797" t="s">
         <v>1463</v>
@@ -13200,15 +13206,15 @@
         <v>1466</v>
       </c>
       <c r="B799" t="s">
-        <v>132</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B800" t="s">
-        <v>1468</v>
+        <v>132</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -13272,20 +13278,20 @@
         <v>1483</v>
       </c>
       <c r="B808" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B809" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B810" t="s">
         <v>1486</v>
@@ -13336,20 +13342,20 @@
         <v>1497</v>
       </c>
       <c r="B816" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B817" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B818" t="s">
         <v>1500</v>
@@ -13368,20 +13374,20 @@
         <v>1503</v>
       </c>
       <c r="B820" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B821" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B822" t="s">
         <v>1506</v>
@@ -13416,12 +13422,12 @@
         <v>1513</v>
       </c>
       <c r="B826" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B827" t="s">
         <v>1515</v>
@@ -13472,28 +13478,28 @@
         <v>1526</v>
       </c>
       <c r="B833" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B834" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B835" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B836" t="s">
         <v>1530</v>
@@ -13552,12 +13558,12 @@
         <v>1543</v>
       </c>
       <c r="B843" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B844" t="s">
         <v>1545</v>
@@ -13576,84 +13582,84 @@
         <v>1548</v>
       </c>
       <c r="B846" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B847" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B848" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B849" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B850" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B851" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B852" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B853" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B854" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B855" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B856" t="s">
         <v>1559</v>
@@ -13712,12 +13718,12 @@
         <v>1572</v>
       </c>
       <c r="B863" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B864" t="s">
         <v>1574</v>
@@ -13840,20 +13846,20 @@
         <v>1603</v>
       </c>
       <c r="B879" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B880" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B881" t="s">
         <v>1606</v>
@@ -13904,12 +13910,12 @@
         <v>1617</v>
       </c>
       <c r="B887" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B888" t="s">
         <v>1619</v>
@@ -13920,12 +13926,12 @@
         <v>1620</v>
       </c>
       <c r="B889" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B890" t="s">
         <v>1622</v>
@@ -13936,12 +13942,12 @@
         <v>1623</v>
       </c>
       <c r="B891" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B892" t="s">
         <v>1625</v>
@@ -14064,12 +14070,12 @@
         <v>1654</v>
       </c>
       <c r="B907" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B908" t="s">
         <v>1656</v>
@@ -14136,20 +14142,20 @@
         <v>1671</v>
       </c>
       <c r="B916" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B917" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B918" t="s">
         <v>1674</v>
@@ -14200,12 +14206,12 @@
         <v>1685</v>
       </c>
       <c r="B924" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B925" t="s">
         <v>1687</v>
@@ -14264,12 +14270,12 @@
         <v>1700</v>
       </c>
       <c r="B932" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B933" t="s">
         <v>1702</v>
@@ -14280,12 +14286,12 @@
         <v>1703</v>
       </c>
       <c r="B934" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B935" t="s">
         <v>1705</v>
@@ -14320,12 +14326,12 @@
         <v>1712</v>
       </c>
       <c r="B939" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B940" t="s">
         <v>1714</v>
@@ -14352,12 +14358,12 @@
         <v>1719</v>
       </c>
       <c r="B943" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B944" t="s">
         <v>1721</v>
@@ -14416,12 +14422,12 @@
         <v>1734</v>
       </c>
       <c r="B951" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B952" t="s">
         <v>1736</v>
@@ -14464,20 +14470,20 @@
         <v>1745</v>
       </c>
       <c r="B957" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B958" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B959" t="s">
         <v>1748</v>
@@ -14536,12 +14542,12 @@
         <v>1761</v>
       </c>
       <c r="B966" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B967" t="s">
         <v>1763</v>
@@ -14656,12 +14662,12 @@
         <v>1790</v>
       </c>
       <c r="B981" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="B982" t="s">
         <v>1792</v>
@@ -14688,20 +14694,20 @@
         <v>1797</v>
       </c>
       <c r="B985" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="B986" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B987" t="s">
         <v>1800</v>
@@ -14720,12 +14726,12 @@
         <v>1803</v>
       </c>
       <c r="B989" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B990" t="s">
         <v>1805</v>
@@ -14760,12 +14766,12 @@
         <v>1812</v>
       </c>
       <c r="B994" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B995" t="s">
         <v>1814</v>
@@ -14784,12 +14790,12 @@
         <v>1817</v>
       </c>
       <c r="B997" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B998" t="s">
         <v>1819</v>
@@ -14840,20 +14846,20 @@
         <v>1830</v>
       </c>
       <c r="B1004" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B1005" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B1006" t="s">
         <v>1833</v>
@@ -14888,12 +14894,12 @@
         <v>1840</v>
       </c>
       <c r="B1010" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B1011" t="s">
         <v>1842</v>
@@ -14952,12 +14958,12 @@
         <v>1855</v>
       </c>
       <c r="B1018" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B1019" t="s">
         <v>1857</v>
@@ -15032,12 +15038,12 @@
         <v>1874</v>
       </c>
       <c r="B1028" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B1029" t="s">
         <v>1876</v>
@@ -15048,44 +15054,44 @@
         <v>1877</v>
       </c>
       <c r="B1030" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B1031" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B1032" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1033" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1034" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="B1035" t="s">
         <v>1883</v>
@@ -15112,12 +15118,12 @@
         <v>1888</v>
       </c>
       <c r="B1038" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="B1039" t="s">
         <v>1890</v>
@@ -15144,12 +15150,12 @@
         <v>1895</v>
       </c>
       <c r="B1042" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="B1043" t="s">
         <v>1897</v>
@@ -15184,12 +15190,12 @@
         <v>1904</v>
       </c>
       <c r="B1047" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="B1048" t="s">
         <v>1906</v>
@@ -15200,12 +15206,12 @@
         <v>1907</v>
       </c>
       <c r="B1049" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B1050" t="s">
         <v>1909</v>
@@ -15296,12 +15302,12 @@
         <v>1930</v>
       </c>
       <c r="B1061" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="B1062" t="s">
         <v>1932</v>
@@ -15424,12 +15430,12 @@
         <v>1961</v>
       </c>
       <c r="B1077" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B1078" t="s">
         <v>1963</v>
@@ -15448,12 +15454,12 @@
         <v>1966</v>
       </c>
       <c r="B1080" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="B1081" t="s">
         <v>1968</v>
@@ -15552,12 +15558,12 @@
         <v>1991</v>
       </c>
       <c r="B1093" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B1094" t="s">
         <v>1993</v>
@@ -15632,44 +15638,44 @@
         <v>2010</v>
       </c>
       <c r="B1103" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B1104" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B1105" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B1106" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1107" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B1108" t="s">
         <v>2016</v>
@@ -15696,12 +15702,12 @@
         <v>2021</v>
       </c>
       <c r="B1111" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B1112" t="s">
         <v>2023</v>
@@ -15712,12 +15718,12 @@
         <v>2024</v>
       </c>
       <c r="B1113" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B1114" t="s">
         <v>2026</v>
@@ -15904,12 +15910,12 @@
         <v>2071</v>
       </c>
       <c r="B1137" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="B1138" t="s">
         <v>2073</v>
@@ -15936,20 +15942,20 @@
         <v>2078</v>
       </c>
       <c r="B1141" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="B1142" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="B1143" t="s">
         <v>2081</v>
@@ -16072,12 +16078,12 @@
         <v>2110</v>
       </c>
       <c r="B1158" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="B1159" t="s">
         <v>2112</v>
@@ -16104,12 +16110,12 @@
         <v>2117</v>
       </c>
       <c r="B1162" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="B1163" t="s">
         <v>2119</v>
@@ -16136,12 +16142,12 @@
         <v>2124</v>
       </c>
       <c r="B1166" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="B1167" t="s">
         <v>2126</v>
@@ -16152,20 +16158,20 @@
         <v>2127</v>
       </c>
       <c r="B1168" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="B1169" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="B1170" t="s">
         <v>2130</v>
@@ -16176,12 +16182,12 @@
         <v>2131</v>
       </c>
       <c r="B1171" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="B1172" t="s">
         <v>2133</v>
@@ -16216,12 +16222,12 @@
         <v>2140</v>
       </c>
       <c r="B1176" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="B1177" t="s">
         <v>2142</v>
@@ -16243,8 +16249,16 @@
         <v>2146</v>
       </c>
     </row>
+    <row r="1180" spans="1:2">
+      <c r="A1180" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>2148</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1179"/>
+  <autoFilter ref="A1:B1180"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1181</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2151">
   <si>
     <t>en</t>
   </si>
@@ -4739,6 +4739,12 @@
   </si>
   <si>
     <t>Поп-команда Эпик</t>
+  </si>
+  <si>
+    <t>Popee the Performer</t>
+  </si>
+  <si>
+    <t>Исполнитель Попи</t>
   </si>
   <si>
     <t>POPGOES</t>
@@ -6810,7 +6816,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1180"/>
+  <dimension ref="A1:B1181"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13726,12 +13732,12 @@
         <v>1574</v>
       </c>
       <c r="B864" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B865" t="s">
         <v>1576</v>
@@ -13854,20 +13860,20 @@
         <v>1605</v>
       </c>
       <c r="B880" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B881" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B882" t="s">
         <v>1608</v>
@@ -13918,12 +13924,12 @@
         <v>1619</v>
       </c>
       <c r="B888" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B889" t="s">
         <v>1621</v>
@@ -13934,12 +13940,12 @@
         <v>1622</v>
       </c>
       <c r="B890" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B891" t="s">
         <v>1624</v>
@@ -13950,12 +13956,12 @@
         <v>1625</v>
       </c>
       <c r="B892" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B893" t="s">
         <v>1627</v>
@@ -14078,12 +14084,12 @@
         <v>1656</v>
       </c>
       <c r="B908" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B909" t="s">
         <v>1658</v>
@@ -14150,20 +14156,20 @@
         <v>1673</v>
       </c>
       <c r="B917" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B918" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B919" t="s">
         <v>1676</v>
@@ -14214,12 +14220,12 @@
         <v>1687</v>
       </c>
       <c r="B925" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B926" t="s">
         <v>1689</v>
@@ -14278,12 +14284,12 @@
         <v>1702</v>
       </c>
       <c r="B933" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B934" t="s">
         <v>1704</v>
@@ -14294,12 +14300,12 @@
         <v>1705</v>
       </c>
       <c r="B935" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B936" t="s">
         <v>1707</v>
@@ -14334,12 +14340,12 @@
         <v>1714</v>
       </c>
       <c r="B940" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B941" t="s">
         <v>1716</v>
@@ -14366,12 +14372,12 @@
         <v>1721</v>
       </c>
       <c r="B944" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B945" t="s">
         <v>1723</v>
@@ -14430,12 +14436,12 @@
         <v>1736</v>
       </c>
       <c r="B952" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="B953" t="s">
         <v>1738</v>
@@ -14478,20 +14484,20 @@
         <v>1747</v>
       </c>
       <c r="B958" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B959" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B960" t="s">
         <v>1750</v>
@@ -14550,12 +14556,12 @@
         <v>1763</v>
       </c>
       <c r="B967" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="B968" t="s">
         <v>1765</v>
@@ -14670,12 +14676,12 @@
         <v>1792</v>
       </c>
       <c r="B982" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B983" t="s">
         <v>1794</v>
@@ -14702,20 +14708,20 @@
         <v>1799</v>
       </c>
       <c r="B986" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B987" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B988" t="s">
         <v>1802</v>
@@ -14734,12 +14740,12 @@
         <v>1805</v>
       </c>
       <c r="B990" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B991" t="s">
         <v>1807</v>
@@ -14774,12 +14780,12 @@
         <v>1814</v>
       </c>
       <c r="B995" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B996" t="s">
         <v>1816</v>
@@ -14798,12 +14804,12 @@
         <v>1819</v>
       </c>
       <c r="B998" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="B999" t="s">
         <v>1821</v>
@@ -14854,20 +14860,20 @@
         <v>1832</v>
       </c>
       <c r="B1005" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B1006" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1007" t="s">
         <v>1835</v>
@@ -14902,12 +14908,12 @@
         <v>1842</v>
       </c>
       <c r="B1011" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="B1012" t="s">
         <v>1844</v>
@@ -14966,12 +14972,12 @@
         <v>1857</v>
       </c>
       <c r="B1019" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B1020" t="s">
         <v>1859</v>
@@ -15046,12 +15052,12 @@
         <v>1876</v>
       </c>
       <c r="B1029" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="B1030" t="s">
         <v>1878</v>
@@ -15062,44 +15068,44 @@
         <v>1879</v>
       </c>
       <c r="B1031" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1032" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1033" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="B1034" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B1035" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="B1036" t="s">
         <v>1885</v>
@@ -15126,12 +15132,12 @@
         <v>1890</v>
       </c>
       <c r="B1039" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1040" t="s">
         <v>1892</v>
@@ -15158,12 +15164,12 @@
         <v>1897</v>
       </c>
       <c r="B1043" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B1044" t="s">
         <v>1899</v>
@@ -15198,12 +15204,12 @@
         <v>1906</v>
       </c>
       <c r="B1048" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1049" t="s">
         <v>1908</v>
@@ -15214,12 +15220,12 @@
         <v>1909</v>
       </c>
       <c r="B1050" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B1051" t="s">
         <v>1911</v>
@@ -15310,12 +15316,12 @@
         <v>1932</v>
       </c>
       <c r="B1062" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B1063" t="s">
         <v>1934</v>
@@ -15438,12 +15444,12 @@
         <v>1963</v>
       </c>
       <c r="B1078" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="B1079" t="s">
         <v>1965</v>
@@ -15462,12 +15468,12 @@
         <v>1968</v>
       </c>
       <c r="B1081" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B1082" t="s">
         <v>1970</v>
@@ -15566,12 +15572,12 @@
         <v>1993</v>
       </c>
       <c r="B1094" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="B1095" t="s">
         <v>1995</v>
@@ -15646,44 +15652,44 @@
         <v>2012</v>
       </c>
       <c r="B1104" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B1105" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B1106" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B1107" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B1108" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B1109" t="s">
         <v>2018</v>
@@ -15710,12 +15716,12 @@
         <v>2023</v>
       </c>
       <c r="B1112" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B1113" t="s">
         <v>2025</v>
@@ -15726,12 +15732,12 @@
         <v>2026</v>
       </c>
       <c r="B1114" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B1115" t="s">
         <v>2028</v>
@@ -15918,12 +15924,12 @@
         <v>2073</v>
       </c>
       <c r="B1138" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="B1139" t="s">
         <v>2075</v>
@@ -15950,20 +15956,20 @@
         <v>2080</v>
       </c>
       <c r="B1142" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="B1143" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="B1144" t="s">
         <v>2083</v>
@@ -16086,12 +16092,12 @@
         <v>2112</v>
       </c>
       <c r="B1159" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="B1160" t="s">
         <v>2114</v>
@@ -16118,12 +16124,12 @@
         <v>2119</v>
       </c>
       <c r="B1163" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="B1164" t="s">
         <v>2121</v>
@@ -16150,12 +16156,12 @@
         <v>2126</v>
       </c>
       <c r="B1167" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="B1168" t="s">
         <v>2128</v>
@@ -16166,20 +16172,20 @@
         <v>2129</v>
       </c>
       <c r="B1169" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="B1170" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="B1171" t="s">
         <v>2132</v>
@@ -16190,12 +16196,12 @@
         <v>2133</v>
       </c>
       <c r="B1172" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="B1173" t="s">
         <v>2135</v>
@@ -16230,12 +16236,12 @@
         <v>2142</v>
       </c>
       <c r="B1177" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="B1178" t="s">
         <v>2144</v>
@@ -16257,8 +16263,16 @@
         <v>2148</v>
       </c>
     </row>
+    <row r="1181" spans="1:2">
+      <c r="A1181" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>2150</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1180"/>
+  <autoFilter ref="A1:B1181"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1182</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2153">
   <si>
     <t>en</t>
   </si>
@@ -5912,6 +5912,12 @@
   </si>
   <si>
     <t>Конструкция Тинкера</t>
+  </si>
+  <si>
+    <t>Tiny Takeover</t>
+  </si>
+  <si>
+    <t>Крошечный захват</t>
   </si>
   <si>
     <t>Titanfall</t>
@@ -6816,7 +6822,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1181"/>
+  <dimension ref="A1:B1182"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -15452,12 +15458,12 @@
         <v>1965</v>
       </c>
       <c r="B1079" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="B1080" t="s">
         <v>1967</v>
@@ -15476,12 +15482,12 @@
         <v>1970</v>
       </c>
       <c r="B1082" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="B1083" t="s">
         <v>1972</v>
@@ -15580,12 +15586,12 @@
         <v>1995</v>
       </c>
       <c r="B1095" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="B1096" t="s">
         <v>1997</v>
@@ -15660,44 +15666,44 @@
         <v>2014</v>
       </c>
       <c r="B1105" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B1106" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B1107" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B1108" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B1109" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B1110" t="s">
         <v>2020</v>
@@ -15724,12 +15730,12 @@
         <v>2025</v>
       </c>
       <c r="B1113" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B1114" t="s">
         <v>2027</v>
@@ -15740,12 +15746,12 @@
         <v>2028</v>
       </c>
       <c r="B1115" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B1116" t="s">
         <v>2030</v>
@@ -15932,12 +15938,12 @@
         <v>2075</v>
       </c>
       <c r="B1139" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="B1140" t="s">
         <v>2077</v>
@@ -15964,20 +15970,20 @@
         <v>2082</v>
       </c>
       <c r="B1143" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="B1144" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="B1145" t="s">
         <v>2085</v>
@@ -16100,12 +16106,12 @@
         <v>2114</v>
       </c>
       <c r="B1160" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="B1161" t="s">
         <v>2116</v>
@@ -16132,12 +16138,12 @@
         <v>2121</v>
       </c>
       <c r="B1164" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="B1165" t="s">
         <v>2123</v>
@@ -16164,12 +16170,12 @@
         <v>2128</v>
       </c>
       <c r="B1168" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="B1169" t="s">
         <v>2130</v>
@@ -16180,20 +16186,20 @@
         <v>2131</v>
       </c>
       <c r="B1170" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="B1171" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="B1172" t="s">
         <v>2134</v>
@@ -16204,12 +16210,12 @@
         <v>2135</v>
       </c>
       <c r="B1173" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="B1174" t="s">
         <v>2137</v>
@@ -16244,12 +16250,12 @@
         <v>2144</v>
       </c>
       <c r="B1178" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="B1179" t="s">
         <v>2146</v>
@@ -16271,8 +16277,16 @@
         <v>2150</v>
       </c>
     </row>
+    <row r="1182" spans="1:2">
+      <c r="A1182" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>2152</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1181"/>
+  <autoFilter ref="A1:B1182"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1186</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2160">
   <si>
     <t>en</t>
   </si>
@@ -3244,6 +3244,9 @@
     <t>Гипиксель</t>
   </si>
   <si>
+    <t>Hypixel (Abiphone)</t>
+  </si>
+  <si>
     <t>Hypixel (Attribute Shard)</t>
   </si>
   <si>
@@ -3265,6 +3268,12 @@
     <t>Hypixel (Gear)</t>
   </si>
   <si>
+    <t>Hypixel (Gemstone)</t>
+  </si>
+  <si>
+    <t>Гипиксель (драгоценный камень)</t>
+  </si>
+  <si>
     <t>Hypixel (Minion)</t>
   </si>
   <si>
@@ -3280,6 +3289,12 @@
     <t>Гипиксель (NPC)</t>
   </si>
   <si>
+    <t>Hypixel (Pet Items)</t>
+  </si>
+  <si>
+    <t>Гипиксель (Предметы для домашних животных)</t>
+  </si>
+  <si>
     <t>Hypixel (Pets)</t>
   </si>
   <si>
@@ -3290,6 +3305,12 @@
   </si>
   <si>
     <t>Гипиксель (Рефордж Стоун)</t>
+  </si>
+  <si>
+    <t>Hypixel (Runes)</t>
+  </si>
+  <si>
+    <t>Гипиксель (Руны)</t>
   </si>
   <si>
     <t>Hypixel (Sacks)</t>
@@ -6822,7 +6843,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1182"/>
+  <dimension ref="A1:B1186"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -11466,28 +11487,28 @@
         <v>1075</v>
       </c>
       <c r="B580" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B581" t="s">
         <v>1077</v>
-      </c>
-      <c r="B581" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B582" t="s">
         <v>1079</v>
-      </c>
-      <c r="B582" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B583" t="s">
         <v>1081</v>
@@ -11498,12 +11519,12 @@
         <v>1082</v>
       </c>
       <c r="B584" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B585" t="s">
         <v>1084</v>
@@ -11522,20 +11543,20 @@
         <v>1087</v>
       </c>
       <c r="B587" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B588" t="s">
         <v>1089</v>
-      </c>
-      <c r="B588" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B589" t="s">
         <v>1091</v>
@@ -11570,12 +11591,12 @@
         <v>1098</v>
       </c>
       <c r="B593" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B594" t="s">
         <v>1100</v>
@@ -11610,52 +11631,52 @@
         <v>1107</v>
       </c>
       <c r="B598" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B599" t="s">
         <v>1109</v>
-      </c>
-      <c r="B599" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B600" t="s">
         <v>1111</v>
-      </c>
-      <c r="B600" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B601" t="s">
         <v>1113</v>
-      </c>
-      <c r="B601" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B602" t="s">
         <v>1115</v>
-      </c>
-      <c r="B602" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B603" t="s">
         <v>1117</v>
-      </c>
-      <c r="B603" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B604" t="s">
         <v>1119</v>
@@ -11690,20 +11711,20 @@
         <v>1126</v>
       </c>
       <c r="B608" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B609" t="s">
         <v>1128</v>
-      </c>
-      <c r="B609" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B610" t="s">
         <v>1130</v>
@@ -11722,20 +11743,20 @@
         <v>1133</v>
       </c>
       <c r="B612" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B613" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B614" t="s">
         <v>1137</v>
@@ -11754,20 +11775,20 @@
         <v>1140</v>
       </c>
       <c r="B616" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B617" t="s">
         <v>1142</v>
-      </c>
-      <c r="B617" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B618" t="s">
         <v>1144</v>
@@ -11802,12 +11823,12 @@
         <v>1151</v>
       </c>
       <c r="B622" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B623" t="s">
         <v>1153</v>
@@ -11842,44 +11863,44 @@
         <v>1160</v>
       </c>
       <c r="B627" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B628" t="s">
         <v>1162</v>
-      </c>
-      <c r="B628" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B629" t="s">
         <v>1164</v>
-      </c>
-      <c r="B629" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B630" t="s">
         <v>1166</v>
-      </c>
-      <c r="B630" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B631" t="s">
         <v>1168</v>
-      </c>
-      <c r="B631" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B632" t="s">
         <v>1170</v>
@@ -11890,36 +11911,36 @@
         <v>1171</v>
       </c>
       <c r="B633" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B634" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B635" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B636" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B637" t="s">
         <v>1178</v>
@@ -11930,36 +11951,36 @@
         <v>1179</v>
       </c>
       <c r="B638" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B639" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="B640" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B641" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B642" t="s">
         <v>1186</v>
@@ -11970,20 +11991,20 @@
         <v>1187</v>
       </c>
       <c r="B643" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B644" t="s">
         <v>1189</v>
-      </c>
-      <c r="B644" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B645" t="s">
         <v>1191</v>
@@ -12018,12 +12039,12 @@
         <v>1198</v>
       </c>
       <c r="B649" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B650" t="s">
         <v>1200</v>
@@ -12042,20 +12063,20 @@
         <v>1203</v>
       </c>
       <c r="B652" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B653" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B654" t="s">
         <v>1207</v>
@@ -12074,220 +12095,220 @@
         <v>1210</v>
       </c>
       <c r="B656" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B657" t="s">
         <v>1212</v>
-      </c>
-      <c r="B657" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B658" t="s">
         <v>1214</v>
-      </c>
-      <c r="B658" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B659" t="s">
         <v>1216</v>
-      </c>
-      <c r="B659" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B660" t="s">
         <v>1218</v>
-      </c>
-      <c r="B660" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B661" t="s">
         <v>1220</v>
-      </c>
-      <c r="B661" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B662" t="s">
         <v>1222</v>
-      </c>
-      <c r="B662" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B663" t="s">
         <v>1224</v>
-      </c>
-      <c r="B663" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B664" t="s">
         <v>1226</v>
-      </c>
-      <c r="B664" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B665" t="s">
         <v>1228</v>
-      </c>
-      <c r="B665" t="s">
-        <v>1229</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B666" t="s">
         <v>1230</v>
-      </c>
-      <c r="B666" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B667" t="s">
         <v>1232</v>
-      </c>
-      <c r="B667" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B668" t="s">
         <v>1234</v>
-      </c>
-      <c r="B668" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="669" spans="1:2">
       <c r="A669" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B669" t="s">
         <v>1236</v>
-      </c>
-      <c r="B669" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="670" spans="1:2">
       <c r="A670" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B670" t="s">
         <v>1238</v>
-      </c>
-      <c r="B670" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="671" spans="1:2">
       <c r="A671" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B671" t="s">
         <v>1240</v>
-      </c>
-      <c r="B671" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="672" spans="1:2">
       <c r="A672" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B672" t="s">
         <v>1242</v>
-      </c>
-      <c r="B672" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B673" t="s">
         <v>1244</v>
-      </c>
-      <c r="B673" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B674" t="s">
         <v>1246</v>
-      </c>
-      <c r="B674" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B675" t="s">
         <v>1248</v>
-      </c>
-      <c r="B675" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B676" t="s">
         <v>1250</v>
-      </c>
-      <c r="B676" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B677" t="s">
         <v>1252</v>
-      </c>
-      <c r="B677" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B678" t="s">
         <v>1254</v>
-      </c>
-      <c r="B678" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B679" t="s">
         <v>1256</v>
-      </c>
-      <c r="B679" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B680" t="s">
         <v>1258</v>
-      </c>
-      <c r="B680" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B681" t="s">
         <v>1260</v>
-      </c>
-      <c r="B681" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B682" t="s">
         <v>1262</v>
-      </c>
-      <c r="B682" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B683" t="s">
         <v>1264</v>
@@ -12298,28 +12319,28 @@
         <v>1265</v>
       </c>
       <c r="B684" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B685" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B686" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B687" t="s">
         <v>1271</v>
@@ -12330,36 +12351,36 @@
         <v>1272</v>
       </c>
       <c r="B688" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B689" t="s">
         <v>1274</v>
-      </c>
-      <c r="B689" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B690" t="s">
         <v>1276</v>
-      </c>
-      <c r="B690" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B691" t="s">
         <v>1278</v>
-      </c>
-      <c r="B691" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B692" t="s">
         <v>1280</v>
@@ -12394,44 +12415,44 @@
         <v>1287</v>
       </c>
       <c r="B696" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="697" spans="1:2">
       <c r="A697" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B697" t="s">
         <v>1289</v>
-      </c>
-      <c r="B697" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="698" spans="1:2">
       <c r="A698" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B698" t="s">
         <v>1291</v>
-      </c>
-      <c r="B698" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="699" spans="1:2">
       <c r="A699" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B699" t="s">
         <v>1293</v>
-      </c>
-      <c r="B699" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="700" spans="1:2">
       <c r="A700" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B700" t="s">
         <v>1295</v>
-      </c>
-      <c r="B700" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B701" t="s">
         <v>1297</v>
@@ -12450,36 +12471,36 @@
         <v>1300</v>
       </c>
       <c r="B703" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B704" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="B705" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B706" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B707" t="s">
         <v>1307</v>
@@ -12490,20 +12511,20 @@
         <v>1308</v>
       </c>
       <c r="B708" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B709" t="s">
         <v>1310</v>
-      </c>
-      <c r="B709" t="s">
-        <v>1311</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="B710" t="s">
         <v>1312</v>
@@ -12522,20 +12543,20 @@
         <v>1315</v>
       </c>
       <c r="B712" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B713" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B714" t="s">
         <v>1319</v>
@@ -12554,12 +12575,12 @@
         <v>1322</v>
       </c>
       <c r="B716" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B717" t="s">
         <v>1324</v>
@@ -12586,12 +12607,12 @@
         <v>1329</v>
       </c>
       <c r="B720" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B721" t="s">
         <v>1331</v>
@@ -12602,44 +12623,44 @@
         <v>1332</v>
       </c>
       <c r="B722" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B723" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="B724" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B725" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B726" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B727" t="s">
         <v>1340</v>
@@ -12650,36 +12671,36 @@
         <v>1341</v>
       </c>
       <c r="B728" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B729" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="B730" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B731" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B732" t="s">
         <v>1348</v>
@@ -12690,44 +12711,44 @@
         <v>1349</v>
       </c>
       <c r="B733" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B734" t="s">
         <v>1351</v>
-      </c>
-      <c r="B734" t="s">
-        <v>1352</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B735" t="s">
         <v>1353</v>
-      </c>
-      <c r="B735" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B736" t="s">
         <v>1355</v>
-      </c>
-      <c r="B736" t="s">
-        <v>1356</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B737" t="s">
         <v>1357</v>
-      </c>
-      <c r="B737" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="B738" t="s">
         <v>1359</v>
@@ -12794,92 +12815,92 @@
         <v>1373</v>
       </c>
       <c r="B746" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B747" t="s">
         <v>1375</v>
-      </c>
-      <c r="B747" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B748" t="s">
         <v>1377</v>
-      </c>
-      <c r="B748" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B749" t="s">
         <v>1379</v>
-      </c>
-      <c r="B749" t="s">
-        <v>1380</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B750" t="s">
         <v>1381</v>
-      </c>
-      <c r="B750" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B751" t="s">
         <v>1383</v>
-      </c>
-      <c r="B751" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B752" t="s">
         <v>1385</v>
-      </c>
-      <c r="B752" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="753" spans="1:2">
       <c r="A753" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B753" t="s">
         <v>1387</v>
-      </c>
-      <c r="B753" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B754" t="s">
         <v>1389</v>
-      </c>
-      <c r="B754" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B755" t="s">
         <v>1391</v>
-      </c>
-      <c r="B755" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B756" t="s">
         <v>1393</v>
-      </c>
-      <c r="B756" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B757" t="s">
         <v>1395</v>
@@ -12890,28 +12911,28 @@
         <v>1396</v>
       </c>
       <c r="B758" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B759" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="760" spans="1:2">
       <c r="A760" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B760" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B761" t="s">
         <v>1402</v>
@@ -12922,20 +12943,20 @@
         <v>1403</v>
       </c>
       <c r="B762" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="763" spans="1:2">
       <c r="A763" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B763" t="s">
         <v>1405</v>
-      </c>
-      <c r="B763" t="s">
-        <v>1406</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B764" t="s">
         <v>1407</v>
@@ -12970,20 +12991,20 @@
         <v>1414</v>
       </c>
       <c r="B768" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B769" t="s">
         <v>1416</v>
-      </c>
-      <c r="B769" t="s">
-        <v>1417</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="B770" t="s">
         <v>1418</v>
@@ -13018,12 +13039,12 @@
         <v>1425</v>
       </c>
       <c r="B774" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="775" spans="1:2">
       <c r="A775" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B775" t="s">
         <v>1427</v>
@@ -13058,44 +13079,44 @@
         <v>1434</v>
       </c>
       <c r="B779" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="780" spans="1:2">
       <c r="A780" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B780" t="s">
         <v>1436</v>
-      </c>
-      <c r="B780" t="s">
-        <v>1437</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B781" t="s">
         <v>1438</v>
-      </c>
-      <c r="B781" t="s">
-        <v>1439</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B782" t="s">
         <v>1440</v>
-      </c>
-      <c r="B782" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B783" t="s">
         <v>1442</v>
-      </c>
-      <c r="B783" t="s">
-        <v>1443</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B784" t="s">
         <v>1444</v>
@@ -13106,36 +13127,36 @@
         <v>1445</v>
       </c>
       <c r="B785" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B786" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="B787" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="B788" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B789" t="s">
         <v>1452</v>
@@ -13146,28 +13167,28 @@
         <v>1453</v>
       </c>
       <c r="B790" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B791" t="s">
         <v>1455</v>
-      </c>
-      <c r="B791" t="s">
-        <v>1456</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B792" t="s">
         <v>1457</v>
-      </c>
-      <c r="B792" t="s">
-        <v>1458</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B793" t="s">
         <v>1459</v>
@@ -13178,60 +13199,60 @@
         <v>1460</v>
       </c>
       <c r="B794" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B795" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="B796" t="s">
-        <v>1462</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
       <c r="B797" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="B798" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="B799" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B800" t="s">
-        <v>132</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B801" t="s">
         <v>1470</v>
@@ -13258,44 +13279,44 @@
         <v>1475</v>
       </c>
       <c r="B804" t="s">
-        <v>1476</v>
+        <v>132</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B805" t="s">
         <v>1477</v>
-      </c>
-      <c r="B805" t="s">
-        <v>1478</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B806" t="s">
         <v>1479</v>
-      </c>
-      <c r="B806" t="s">
-        <v>1480</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B807" t="s">
         <v>1481</v>
-      </c>
-      <c r="B807" t="s">
-        <v>1482</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B808" t="s">
         <v>1483</v>
-      </c>
-      <c r="B808" t="s">
-        <v>1484</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B809" t="s">
         <v>1485</v>
@@ -13306,28 +13327,28 @@
         <v>1486</v>
       </c>
       <c r="B810" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B811" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B812" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B813" t="s">
         <v>1492</v>
@@ -13338,28 +13359,28 @@
         <v>1493</v>
       </c>
       <c r="B814" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B815" t="s">
         <v>1495</v>
-      </c>
-      <c r="B815" t="s">
-        <v>1496</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B816" t="s">
         <v>1497</v>
-      </c>
-      <c r="B816" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B817" t="s">
         <v>1499</v>
@@ -13370,60 +13391,60 @@
         <v>1500</v>
       </c>
       <c r="B818" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B819" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B820" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B821" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B822" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B823" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B824" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B825" t="s">
         <v>1512</v>
@@ -13434,12 +13455,12 @@
         <v>1513</v>
       </c>
       <c r="B826" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="B827" t="s">
         <v>1515</v>
@@ -13474,28 +13495,28 @@
         <v>1522</v>
       </c>
       <c r="B831" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B832" t="s">
         <v>1524</v>
-      </c>
-      <c r="B832" t="s">
-        <v>1525</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B833" t="s">
         <v>1526</v>
-      </c>
-      <c r="B833" t="s">
-        <v>1527</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B834" t="s">
         <v>1528</v>
@@ -13506,36 +13527,36 @@
         <v>1529</v>
       </c>
       <c r="B835" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B836" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="B837" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="B838" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B839" t="s">
         <v>1536</v>
@@ -13546,36 +13567,36 @@
         <v>1537</v>
       </c>
       <c r="B840" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B841" t="s">
         <v>1539</v>
-      </c>
-      <c r="B841" t="s">
-        <v>1540</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B842" t="s">
         <v>1541</v>
-      </c>
-      <c r="B842" t="s">
-        <v>1542</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B843" t="s">
         <v>1543</v>
-      </c>
-      <c r="B843" t="s">
-        <v>1544</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="B844" t="s">
         <v>1545</v>
@@ -13602,100 +13623,100 @@
         <v>1550</v>
       </c>
       <c r="B847" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B848" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B849" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="B850" t="s">
-        <v>1553</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1554</v>
+        <v>1557</v>
       </c>
       <c r="B851" t="s">
-        <v>1554</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="B852" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="B853" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
       <c r="B854" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1558</v>
+        <v>1561</v>
       </c>
       <c r="B855" t="s">
-        <v>1558</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1559</v>
+        <v>1562</v>
       </c>
       <c r="B856" t="s">
-        <v>1559</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
-        <v>1560</v>
+        <v>1563</v>
       </c>
       <c r="B857" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="B858" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B859" t="s">
         <v>1565</v>
@@ -13706,44 +13727,44 @@
         <v>1566</v>
       </c>
       <c r="B860" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B861" t="s">
         <v>1568</v>
-      </c>
-      <c r="B861" t="s">
-        <v>1569</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B862" t="s">
         <v>1570</v>
-      </c>
-      <c r="B862" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B863" t="s">
         <v>1572</v>
-      </c>
-      <c r="B863" t="s">
-        <v>1573</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B864" t="s">
         <v>1574</v>
-      </c>
-      <c r="B864" t="s">
-        <v>1575</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B865" t="s">
         <v>1576</v>
@@ -13778,100 +13799,100 @@
         <v>1583</v>
       </c>
       <c r="B869" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B870" t="s">
         <v>1585</v>
-      </c>
-      <c r="B870" t="s">
-        <v>1586</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B871" t="s">
         <v>1587</v>
-      </c>
-      <c r="B871" t="s">
-        <v>1588</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B872" t="s">
         <v>1589</v>
-      </c>
-      <c r="B872" t="s">
-        <v>1590</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B873" t="s">
         <v>1591</v>
-      </c>
-      <c r="B873" t="s">
-        <v>1592</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B874" t="s">
         <v>1593</v>
-      </c>
-      <c r="B874" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B875" t="s">
         <v>1595</v>
-      </c>
-      <c r="B875" t="s">
-        <v>1596</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B876" t="s">
         <v>1597</v>
-      </c>
-      <c r="B876" t="s">
-        <v>1598</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B877" t="s">
         <v>1599</v>
-      </c>
-      <c r="B877" t="s">
-        <v>1600</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B878" t="s">
         <v>1601</v>
-      </c>
-      <c r="B878" t="s">
-        <v>1602</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B879" t="s">
         <v>1603</v>
-      </c>
-      <c r="B879" t="s">
-        <v>1604</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B880" t="s">
         <v>1605</v>
-      </c>
-      <c r="B880" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="B881" t="s">
         <v>1607</v>
@@ -13882,28 +13903,28 @@
         <v>1608</v>
       </c>
       <c r="B882" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B883" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B884" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B885" t="s">
         <v>1614</v>
@@ -13914,28 +13935,28 @@
         <v>1615</v>
       </c>
       <c r="B886" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B887" t="s">
         <v>1617</v>
-      </c>
-      <c r="B887" t="s">
-        <v>1618</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B888" t="s">
         <v>1619</v>
-      </c>
-      <c r="B888" t="s">
-        <v>1620</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="B889" t="s">
         <v>1621</v>
@@ -13954,36 +13975,36 @@
         <v>1624</v>
       </c>
       <c r="B891" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B892" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B893" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B894" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B895" t="s">
         <v>1631</v>
@@ -14002,100 +14023,100 @@
         <v>1634</v>
       </c>
       <c r="B897" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B898" t="s">
         <v>1636</v>
-      </c>
-      <c r="B898" t="s">
-        <v>1637</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B899" t="s">
         <v>1638</v>
-      </c>
-      <c r="B899" t="s">
-        <v>1639</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B900" t="s">
         <v>1640</v>
-      </c>
-      <c r="B900" t="s">
-        <v>1641</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B901" t="s">
         <v>1642</v>
-      </c>
-      <c r="B901" t="s">
-        <v>1643</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B902" t="s">
         <v>1644</v>
-      </c>
-      <c r="B902" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B903" t="s">
         <v>1646</v>
-      </c>
-      <c r="B903" t="s">
-        <v>1647</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B904" t="s">
         <v>1648</v>
-      </c>
-      <c r="B904" t="s">
-        <v>1649</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B905" t="s">
         <v>1650</v>
-      </c>
-      <c r="B905" t="s">
-        <v>1651</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B906" t="s">
         <v>1652</v>
-      </c>
-      <c r="B906" t="s">
-        <v>1653</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B907" t="s">
         <v>1654</v>
-      </c>
-      <c r="B907" t="s">
-        <v>1655</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B908" t="s">
         <v>1656</v>
-      </c>
-      <c r="B908" t="s">
-        <v>1657</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="B909" t="s">
         <v>1658</v>
@@ -14130,44 +14151,44 @@
         <v>1665</v>
       </c>
       <c r="B913" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B914" t="s">
         <v>1667</v>
-      </c>
-      <c r="B914" t="s">
-        <v>1668</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B915" t="s">
         <v>1669</v>
-      </c>
-      <c r="B915" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B916" t="s">
         <v>1671</v>
-      </c>
-      <c r="B916" t="s">
-        <v>1672</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B917" t="s">
         <v>1673</v>
-      </c>
-      <c r="B917" t="s">
-        <v>1674</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="B918" t="s">
         <v>1675</v>
@@ -14178,28 +14199,28 @@
         <v>1676</v>
       </c>
       <c r="B919" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B920" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B921" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B922" t="s">
         <v>1682</v>
@@ -14210,28 +14231,28 @@
         <v>1683</v>
       </c>
       <c r="B923" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B924" t="s">
         <v>1685</v>
-      </c>
-      <c r="B924" t="s">
-        <v>1686</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B925" t="s">
         <v>1687</v>
-      </c>
-      <c r="B925" t="s">
-        <v>1688</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="B926" t="s">
         <v>1689</v>
@@ -14266,36 +14287,36 @@
         <v>1696</v>
       </c>
       <c r="B930" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B931" t="s">
         <v>1698</v>
-      </c>
-      <c r="B931" t="s">
-        <v>1699</v>
       </c>
     </row>
     <row r="932" spans="1:2">
       <c r="A932" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B932" t="s">
         <v>1700</v>
-      </c>
-      <c r="B932" t="s">
-        <v>1701</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B933" t="s">
         <v>1702</v>
-      </c>
-      <c r="B933" t="s">
-        <v>1703</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="B934" t="s">
         <v>1704</v>
@@ -14314,20 +14335,20 @@
         <v>1707</v>
       </c>
       <c r="B936" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B937" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B938" t="s">
         <v>1711</v>
@@ -14346,12 +14367,12 @@
         <v>1714</v>
       </c>
       <c r="B940" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="B941" t="s">
         <v>1716</v>
@@ -14418,36 +14439,36 @@
         <v>1730</v>
       </c>
       <c r="B949" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B950" t="s">
         <v>1732</v>
-      </c>
-      <c r="B950" t="s">
-        <v>1733</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B951" t="s">
         <v>1734</v>
-      </c>
-      <c r="B951" t="s">
-        <v>1735</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B952" t="s">
         <v>1736</v>
-      </c>
-      <c r="B952" t="s">
-        <v>1737</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="B953" t="s">
         <v>1738</v>
@@ -14482,20 +14503,20 @@
         <v>1745</v>
       </c>
       <c r="B957" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B958" t="s">
         <v>1747</v>
-      </c>
-      <c r="B958" t="s">
-        <v>1748</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="B959" t="s">
         <v>1749</v>
@@ -14506,28 +14527,28 @@
         <v>1750</v>
       </c>
       <c r="B960" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B961" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B962" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B963" t="s">
         <v>1756</v>
@@ -14538,36 +14559,36 @@
         <v>1757</v>
       </c>
       <c r="B964" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B965" t="s">
         <v>1759</v>
-      </c>
-      <c r="B965" t="s">
-        <v>1760</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B966" t="s">
         <v>1761</v>
-      </c>
-      <c r="B966" t="s">
-        <v>1762</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B967" t="s">
         <v>1763</v>
-      </c>
-      <c r="B967" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B968" t="s">
         <v>1765</v>
@@ -14602,92 +14623,92 @@
         <v>1772</v>
       </c>
       <c r="B972" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B973" t="s">
         <v>1774</v>
-      </c>
-      <c r="B973" t="s">
-        <v>1775</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B974" t="s">
         <v>1776</v>
-      </c>
-      <c r="B974" t="s">
-        <v>1777</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B975" t="s">
         <v>1778</v>
-      </c>
-      <c r="B975" t="s">
-        <v>1779</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B976" t="s">
         <v>1780</v>
-      </c>
-      <c r="B976" t="s">
-        <v>1781</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B977" t="s">
         <v>1782</v>
-      </c>
-      <c r="B977" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B978" t="s">
         <v>1784</v>
-      </c>
-      <c r="B978" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B979" t="s">
         <v>1786</v>
-      </c>
-      <c r="B979" t="s">
-        <v>1787</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B980" t="s">
         <v>1788</v>
-      </c>
-      <c r="B980" t="s">
-        <v>1789</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B981" t="s">
         <v>1790</v>
-      </c>
-      <c r="B981" t="s">
-        <v>1791</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B982" t="s">
         <v>1792</v>
-      </c>
-      <c r="B982" t="s">
-        <v>1793</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="B983" t="s">
         <v>1794</v>
@@ -14730,36 +14751,36 @@
         <v>1802</v>
       </c>
       <c r="B988" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B989" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B990" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B991" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B992" t="s">
         <v>1809</v>
@@ -14786,12 +14807,12 @@
         <v>1814</v>
       </c>
       <c r="B995" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="B996" t="s">
         <v>1816</v>
@@ -14818,12 +14839,12 @@
         <v>1821</v>
       </c>
       <c r="B999" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B1000" t="s">
         <v>1823</v>
@@ -14850,28 +14871,28 @@
         <v>1828</v>
       </c>
       <c r="B1003" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B1004" t="s">
         <v>1830</v>
-      </c>
-      <c r="B1004" t="s">
-        <v>1831</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B1005" t="s">
         <v>1832</v>
-      </c>
-      <c r="B1005" t="s">
-        <v>1833</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="B1006" t="s">
         <v>1834</v>
@@ -14882,28 +14903,28 @@
         <v>1835</v>
       </c>
       <c r="B1007" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1008" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B1009" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B1010" t="s">
         <v>1841</v>
@@ -14914,12 +14935,12 @@
         <v>1842</v>
       </c>
       <c r="B1011" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="B1012" t="s">
         <v>1844</v>
@@ -14954,36 +14975,36 @@
         <v>1851</v>
       </c>
       <c r="B1016" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B1017" t="s">
         <v>1853</v>
-      </c>
-      <c r="B1017" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B1018" t="s">
         <v>1855</v>
-      </c>
-      <c r="B1018" t="s">
-        <v>1856</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B1019" t="s">
         <v>1857</v>
-      </c>
-      <c r="B1019" t="s">
-        <v>1858</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="B1020" t="s">
         <v>1859</v>
@@ -15018,52 +15039,52 @@
         <v>1866</v>
       </c>
       <c r="B1024" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B1025" t="s">
         <v>1868</v>
-      </c>
-      <c r="B1025" t="s">
-        <v>1869</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B1026" t="s">
         <v>1870</v>
-      </c>
-      <c r="B1026" t="s">
-        <v>1871</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B1027" t="s">
         <v>1872</v>
-      </c>
-      <c r="B1027" t="s">
-        <v>1873</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B1028" t="s">
         <v>1874</v>
-      </c>
-      <c r="B1028" t="s">
-        <v>1875</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B1029" t="s">
         <v>1876</v>
-      </c>
-      <c r="B1029" t="s">
-        <v>1877</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="B1030" t="s">
         <v>1878</v>
@@ -15082,60 +15103,60 @@
         <v>1881</v>
       </c>
       <c r="B1032" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="B1033" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="B1034" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="B1035" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
       <c r="B1036" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1886</v>
+        <v>1889</v>
       </c>
       <c r="B1037" t="s">
-        <v>1887</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="B1038" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="B1039" t="s">
         <v>1891</v>
@@ -15210,12 +15231,12 @@
         <v>1906</v>
       </c>
       <c r="B1048" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B1049" t="s">
         <v>1908</v>
@@ -15234,20 +15255,20 @@
         <v>1911</v>
       </c>
       <c r="B1051" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="B1052" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B1053" t="s">
         <v>1915</v>
@@ -15266,68 +15287,68 @@
         <v>1918</v>
       </c>
       <c r="B1055" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B1056" t="s">
         <v>1920</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>1921</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B1057" t="s">
         <v>1922</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>1923</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B1058" t="s">
         <v>1924</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>1925</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B1059" t="s">
         <v>1926</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>1927</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B1060" t="s">
         <v>1928</v>
-      </c>
-      <c r="B1060" t="s">
-        <v>1929</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B1061" t="s">
         <v>1930</v>
-      </c>
-      <c r="B1061" t="s">
-        <v>1931</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B1062" t="s">
         <v>1932</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>1933</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="B1063" t="s">
         <v>1934</v>
@@ -15362,108 +15383,108 @@
         <v>1941</v>
       </c>
       <c r="B1067" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B1068" t="s">
         <v>1943</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>1944</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B1069" t="s">
         <v>1945</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>1946</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B1070" t="s">
         <v>1947</v>
-      </c>
-      <c r="B1070" t="s">
-        <v>1948</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B1071" t="s">
         <v>1949</v>
-      </c>
-      <c r="B1071" t="s">
-        <v>1950</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B1072" t="s">
         <v>1951</v>
-      </c>
-      <c r="B1072" t="s">
-        <v>1952</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B1073" t="s">
         <v>1953</v>
-      </c>
-      <c r="B1073" t="s">
-        <v>1954</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B1074" t="s">
         <v>1955</v>
-      </c>
-      <c r="B1074" t="s">
-        <v>1956</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
+        <v>1956</v>
+      </c>
+      <c r="B1075" t="s">
         <v>1957</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>1958</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B1076" t="s">
         <v>1959</v>
-      </c>
-      <c r="B1076" t="s">
-        <v>1960</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B1077" t="s">
         <v>1961</v>
-      </c>
-      <c r="B1077" t="s">
-        <v>1962</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B1078" t="s">
         <v>1963</v>
-      </c>
-      <c r="B1078" t="s">
-        <v>1964</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B1079" t="s">
         <v>1965</v>
-      </c>
-      <c r="B1079" t="s">
-        <v>1966</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B1080" t="s">
         <v>1967</v>
@@ -15490,12 +15511,12 @@
         <v>1972</v>
       </c>
       <c r="B1083" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="B1084" t="s">
         <v>1974</v>
@@ -15522,76 +15543,76 @@
         <v>1979</v>
       </c>
       <c r="B1087" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B1088" t="s">
         <v>1981</v>
-      </c>
-      <c r="B1088" t="s">
-        <v>1982</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B1089" t="s">
         <v>1983</v>
-      </c>
-      <c r="B1089" t="s">
-        <v>1984</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B1090" t="s">
         <v>1985</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>1986</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B1091" t="s">
         <v>1987</v>
-      </c>
-      <c r="B1091" t="s">
-        <v>1988</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B1092" t="s">
         <v>1989</v>
-      </c>
-      <c r="B1092" t="s">
-        <v>1990</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B1093" t="s">
         <v>1991</v>
-      </c>
-      <c r="B1093" t="s">
-        <v>1992</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B1094" t="s">
         <v>1993</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>1994</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B1095" t="s">
         <v>1995</v>
-      </c>
-      <c r="B1095" t="s">
-        <v>1996</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B1096" t="s">
         <v>1997</v>
@@ -15626,52 +15647,52 @@
         <v>2004</v>
       </c>
       <c r="B1100" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B1101" t="s">
         <v>2006</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>2007</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B1102" t="s">
         <v>2008</v>
-      </c>
-      <c r="B1102" t="s">
-        <v>2009</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B1103" t="s">
         <v>2010</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>2011</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B1104" t="s">
         <v>2012</v>
-      </c>
-      <c r="B1104" t="s">
-        <v>2013</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B1105" t="s">
         <v>2014</v>
-      </c>
-      <c r="B1105" t="s">
-        <v>2015</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B1106" t="s">
         <v>2016</v>
@@ -15682,52 +15703,52 @@
         <v>2017</v>
       </c>
       <c r="B1107" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B1108" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="B1109" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="B1110" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B1111" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B1112" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B1113" t="s">
         <v>2026</v>
@@ -15754,20 +15775,20 @@
         <v>2030</v>
       </c>
       <c r="B1116" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B1117" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B1118" t="s">
         <v>2034</v>
@@ -15786,164 +15807,164 @@
         <v>2037</v>
       </c>
       <c r="B1120" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B1121" t="s">
         <v>2039</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>2040</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>2040</v>
+      </c>
+      <c r="B1122" t="s">
         <v>2041</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>2042</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B1123" t="s">
         <v>2043</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>2044</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B1124" t="s">
         <v>2045</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>2046</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B1125" t="s">
         <v>2047</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>2048</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B1126" t="s">
         <v>2049</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>2050</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B1127" t="s">
         <v>2051</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>2052</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B1128" t="s">
         <v>2053</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>2054</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B1129" t="s">
         <v>2055</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>2056</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B1130" t="s">
         <v>2057</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>2058</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B1131" t="s">
         <v>2059</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>2060</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B1132" t="s">
         <v>2061</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>2062</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1133" t="s">
         <v>2063</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>2064</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B1134" t="s">
         <v>2065</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>2066</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B1135" t="s">
         <v>2067</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>2068</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B1136" t="s">
         <v>2069</v>
-      </c>
-      <c r="B1136" t="s">
-        <v>2070</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B1137" t="s">
         <v>2071</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>2072</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B1138" t="s">
         <v>2073</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>2074</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B1139" t="s">
         <v>2075</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>2076</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="B1140" t="s">
         <v>2077</v>
@@ -15986,28 +16007,28 @@
         <v>2085</v>
       </c>
       <c r="B1145" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="B1146" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="B1147" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="B1148" t="s">
         <v>2091</v>
@@ -16018,100 +16039,100 @@
         <v>2092</v>
       </c>
       <c r="B1149" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B1150" t="s">
         <v>2094</v>
-      </c>
-      <c r="B1150" t="s">
-        <v>2095</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B1151" t="s">
         <v>2096</v>
-      </c>
-      <c r="B1151" t="s">
-        <v>2097</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B1152" t="s">
         <v>2098</v>
-      </c>
-      <c r="B1152" t="s">
-        <v>2099</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B1153" t="s">
         <v>2100</v>
-      </c>
-      <c r="B1153" t="s">
-        <v>2101</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B1154" t="s">
         <v>2102</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>2103</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B1155" t="s">
         <v>2104</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>2105</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B1156" t="s">
         <v>2106</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>2107</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B1157" t="s">
         <v>2108</v>
-      </c>
-      <c r="B1157" t="s">
-        <v>2109</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1158" t="s">
         <v>2110</v>
-      </c>
-      <c r="B1158" t="s">
-        <v>2111</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B1159" t="s">
         <v>2112</v>
-      </c>
-      <c r="B1159" t="s">
-        <v>2113</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B1160" t="s">
         <v>2114</v>
-      </c>
-      <c r="B1160" t="s">
-        <v>2115</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="B1161" t="s">
         <v>2116</v>
@@ -16194,44 +16215,44 @@
         <v>2133</v>
       </c>
       <c r="B1171" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="B1172" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="B1173" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="B1174" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="B1175" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="B1176" t="s">
         <v>2141</v>
@@ -16250,12 +16271,12 @@
         <v>2144</v>
       </c>
       <c r="B1178" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="B1179" t="s">
         <v>2146</v>
@@ -16285,8 +16306,40 @@
         <v>2152</v>
       </c>
     </row>
+    <row r="1183" spans="1:2">
+      <c r="A1183" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:2">
+      <c r="A1184" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:2">
+      <c r="A1185" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:2">
+      <c r="A1186" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>2159</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1182"/>
+  <autoFilter ref="A1:B1186"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2162">
   <si>
     <t>en</t>
   </si>
@@ -4841,6 +4841,12 @@
   </si>
   <si>
     <t>Профессор Лейтон</t>
+  </si>
+  <si>
+    <t>Project Zomboid</t>
+  </si>
+  <si>
+    <t>Проект "Зомбоид</t>
   </si>
   <si>
     <t>Pumpkin</t>
@@ -6843,7 +6849,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1186"/>
+  <dimension ref="A1:B1187"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13927,20 +13933,20 @@
         <v>1614</v>
       </c>
       <c r="B885" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B886" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B887" t="s">
         <v>1617</v>
@@ -13991,12 +13997,12 @@
         <v>1628</v>
       </c>
       <c r="B893" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B894" t="s">
         <v>1630</v>
@@ -14007,12 +14013,12 @@
         <v>1631</v>
       </c>
       <c r="B895" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B896" t="s">
         <v>1633</v>
@@ -14023,12 +14029,12 @@
         <v>1634</v>
       </c>
       <c r="B897" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B898" t="s">
         <v>1636</v>
@@ -14151,12 +14157,12 @@
         <v>1665</v>
       </c>
       <c r="B913" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B914" t="s">
         <v>1667</v>
@@ -14223,20 +14229,20 @@
         <v>1682</v>
       </c>
       <c r="B922" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B923" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B924" t="s">
         <v>1685</v>
@@ -14287,12 +14293,12 @@
         <v>1696</v>
       </c>
       <c r="B930" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B931" t="s">
         <v>1698</v>
@@ -14351,12 +14357,12 @@
         <v>1711</v>
       </c>
       <c r="B938" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B939" t="s">
         <v>1713</v>
@@ -14367,12 +14373,12 @@
         <v>1714</v>
       </c>
       <c r="B940" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B941" t="s">
         <v>1716</v>
@@ -14407,12 +14413,12 @@
         <v>1723</v>
       </c>
       <c r="B945" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B946" t="s">
         <v>1725</v>
@@ -14439,12 +14445,12 @@
         <v>1730</v>
       </c>
       <c r="B949" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B950" t="s">
         <v>1732</v>
@@ -14503,12 +14509,12 @@
         <v>1745</v>
       </c>
       <c r="B957" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B958" t="s">
         <v>1747</v>
@@ -14551,20 +14557,20 @@
         <v>1756</v>
       </c>
       <c r="B963" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="B964" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B965" t="s">
         <v>1759</v>
@@ -14623,12 +14629,12 @@
         <v>1772</v>
       </c>
       <c r="B972" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B973" t="s">
         <v>1774</v>
@@ -14743,12 +14749,12 @@
         <v>1801</v>
       </c>
       <c r="B987" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B988" t="s">
         <v>1803</v>
@@ -14775,20 +14781,20 @@
         <v>1808</v>
       </c>
       <c r="B991" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B992" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B993" t="s">
         <v>1811</v>
@@ -14807,12 +14813,12 @@
         <v>1814</v>
       </c>
       <c r="B995" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B996" t="s">
         <v>1816</v>
@@ -14847,12 +14853,12 @@
         <v>1823</v>
       </c>
       <c r="B1000" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1001" t="s">
         <v>1825</v>
@@ -14871,12 +14877,12 @@
         <v>1828</v>
       </c>
       <c r="B1003" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1004" t="s">
         <v>1830</v>
@@ -14927,20 +14933,20 @@
         <v>1841</v>
       </c>
       <c r="B1010" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B1011" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="B1012" t="s">
         <v>1844</v>
@@ -14975,12 +14981,12 @@
         <v>1851</v>
       </c>
       <c r="B1016" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B1017" t="s">
         <v>1853</v>
@@ -15039,12 +15045,12 @@
         <v>1866</v>
       </c>
       <c r="B1024" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="B1025" t="s">
         <v>1868</v>
@@ -15119,12 +15125,12 @@
         <v>1885</v>
       </c>
       <c r="B1034" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="B1035" t="s">
         <v>1887</v>
@@ -15135,44 +15141,44 @@
         <v>1888</v>
       </c>
       <c r="B1036" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="B1037" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="B1038" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1039" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="B1040" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="B1041" t="s">
         <v>1894</v>
@@ -15199,12 +15205,12 @@
         <v>1899</v>
       </c>
       <c r="B1044" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B1045" t="s">
         <v>1901</v>
@@ -15231,12 +15237,12 @@
         <v>1906</v>
       </c>
       <c r="B1048" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1049" t="s">
         <v>1908</v>
@@ -15271,12 +15277,12 @@
         <v>1915</v>
       </c>
       <c r="B1053" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B1054" t="s">
         <v>1917</v>
@@ -15287,12 +15293,12 @@
         <v>1918</v>
       </c>
       <c r="B1055" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="B1056" t="s">
         <v>1920</v>
@@ -15383,12 +15389,12 @@
         <v>1941</v>
       </c>
       <c r="B1067" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="B1068" t="s">
         <v>1943</v>
@@ -15519,12 +15525,12 @@
         <v>1974</v>
       </c>
       <c r="B1084" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1085" t="s">
         <v>1976</v>
@@ -15543,12 +15549,12 @@
         <v>1979</v>
       </c>
       <c r="B1087" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B1088" t="s">
         <v>1981</v>
@@ -15647,12 +15653,12 @@
         <v>2004</v>
       </c>
       <c r="B1100" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B1101" t="s">
         <v>2006</v>
@@ -15727,44 +15733,44 @@
         <v>2023</v>
       </c>
       <c r="B1110" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B1111" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B1112" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B1113" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B1114" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B1115" t="s">
         <v>2029</v>
@@ -15791,12 +15797,12 @@
         <v>2034</v>
       </c>
       <c r="B1118" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="B1119" t="s">
         <v>2036</v>
@@ -15807,12 +15813,12 @@
         <v>2037</v>
       </c>
       <c r="B1120" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="B1121" t="s">
         <v>2039</v>
@@ -15999,12 +16005,12 @@
         <v>2084</v>
       </c>
       <c r="B1144" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="B1145" t="s">
         <v>2086</v>
@@ -16031,20 +16037,20 @@
         <v>2091</v>
       </c>
       <c r="B1148" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="B1149" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="B1150" t="s">
         <v>2094</v>
@@ -16167,12 +16173,12 @@
         <v>2123</v>
       </c>
       <c r="B1165" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="B1166" t="s">
         <v>2125</v>
@@ -16199,12 +16205,12 @@
         <v>2130</v>
       </c>
       <c r="B1169" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="B1170" t="s">
         <v>2132</v>
@@ -16231,12 +16237,12 @@
         <v>2137</v>
       </c>
       <c r="B1173" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="B1174" t="s">
         <v>2139</v>
@@ -16247,20 +16253,20 @@
         <v>2140</v>
       </c>
       <c r="B1175" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="B1176" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="B1177" t="s">
         <v>2143</v>
@@ -16271,12 +16277,12 @@
         <v>2144</v>
       </c>
       <c r="B1178" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="B1179" t="s">
         <v>2146</v>
@@ -16311,12 +16317,12 @@
         <v>2153</v>
       </c>
       <c r="B1183" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="B1184" t="s">
         <v>2155</v>
@@ -16338,8 +16344,16 @@
         <v>2159</v>
       </c>
     </row>
+    <row r="1187" spans="1:2">
+      <c r="A1187" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>2161</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1186"/>
+  <autoFilter ref="A1:B1187"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2164">
   <si>
     <t>en</t>
   </si>
@@ -404,6 +404,12 @@
   </si>
   <si>
     <t>Бака и Тест</t>
+  </si>
+  <si>
+    <t>Bakugan</t>
+  </si>
+  <si>
+    <t>Бакуган</t>
   </si>
   <si>
     <t>Baldi's Basics</t>
@@ -6849,7 +6855,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1187"/>
+  <dimension ref="A1:B1188"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -7429,20 +7435,20 @@
         <v>135</v>
       </c>
       <c r="B72" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B73" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B74" t="s">
         <v>138</v>
@@ -7637,12 +7643,12 @@
         <v>185</v>
       </c>
       <c r="B98" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B99" t="s">
         <v>187</v>
@@ -7693,12 +7699,12 @@
         <v>198</v>
       </c>
       <c r="B105" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B106" t="s">
         <v>200</v>
@@ -7741,12 +7747,12 @@
         <v>209</v>
       </c>
       <c r="B111" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B112" t="s">
         <v>211</v>
@@ -7773,12 +7779,12 @@
         <v>216</v>
       </c>
       <c r="B115" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B116" t="s">
         <v>218</v>
@@ -7837,12 +7843,12 @@
         <v>231</v>
       </c>
       <c r="B123" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B124" t="s">
         <v>233</v>
@@ -7869,12 +7875,12 @@
         <v>238</v>
       </c>
       <c r="B127" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B128" t="s">
         <v>240</v>
@@ -7893,12 +7899,12 @@
         <v>243</v>
       </c>
       <c r="B130" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B131" t="s">
         <v>245</v>
@@ -7909,12 +7915,12 @@
         <v>246</v>
       </c>
       <c r="B132" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B133" t="s">
         <v>248</v>
@@ -7949,12 +7955,12 @@
         <v>255</v>
       </c>
       <c r="B137" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B138" t="s">
         <v>257</v>
@@ -7973,12 +7979,12 @@
         <v>260</v>
       </c>
       <c r="B140" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B141" t="s">
         <v>262</v>
@@ -8053,28 +8059,28 @@
         <v>279</v>
       </c>
       <c r="B150" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B151" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B152" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B153" t="s">
         <v>283</v>
@@ -8221,12 +8227,12 @@
         <v>318</v>
       </c>
       <c r="B171" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B172" t="s">
         <v>320</v>
@@ -8261,12 +8267,12 @@
         <v>327</v>
       </c>
       <c r="B176" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B177" t="s">
         <v>329</v>
@@ -8277,12 +8283,12 @@
         <v>330</v>
       </c>
       <c r="B178" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B179" t="s">
         <v>332</v>
@@ -8293,20 +8299,20 @@
         <v>333</v>
       </c>
       <c r="B180" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B181" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B182" t="s">
         <v>336</v>
@@ -8525,12 +8531,12 @@
         <v>389</v>
       </c>
       <c r="B209" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B210" t="s">
         <v>391</v>
@@ -8573,12 +8579,12 @@
         <v>400</v>
       </c>
       <c r="B215" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B216" t="s">
         <v>402</v>
@@ -8597,12 +8603,12 @@
         <v>405</v>
       </c>
       <c r="B218" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B219" t="s">
         <v>407</v>
@@ -8629,20 +8635,20 @@
         <v>412</v>
       </c>
       <c r="B222" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B223" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B224" t="s">
         <v>415</v>
@@ -8701,12 +8707,12 @@
         <v>428</v>
       </c>
       <c r="B231" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B232" t="s">
         <v>430</v>
@@ -8837,12 +8843,12 @@
         <v>461</v>
       </c>
       <c r="B248" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B249" t="s">
         <v>463</v>
@@ -8861,12 +8867,12 @@
         <v>466</v>
       </c>
       <c r="B251" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B252" t="s">
         <v>468</v>
@@ -8877,20 +8883,20 @@
         <v>469</v>
       </c>
       <c r="B253" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B254" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B255" t="s">
         <v>472</v>
@@ -8901,12 +8907,12 @@
         <v>473</v>
       </c>
       <c r="B256" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B257" t="s">
         <v>475</v>
@@ -8981,12 +8987,12 @@
         <v>492</v>
       </c>
       <c r="B266" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B267" t="s">
         <v>494</v>
@@ -9005,12 +9011,12 @@
         <v>497</v>
       </c>
       <c r="B269" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B270" t="s">
         <v>499</v>
@@ -9021,12 +9027,12 @@
         <v>500</v>
       </c>
       <c r="B271" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B272" t="s">
         <v>502</v>
@@ -9053,12 +9059,12 @@
         <v>507</v>
       </c>
       <c r="B275" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B276" t="s">
         <v>509</v>
@@ -9109,12 +9115,12 @@
         <v>520</v>
       </c>
       <c r="B282" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B283" t="s">
         <v>522</v>
@@ -9141,12 +9147,12 @@
         <v>527</v>
       </c>
       <c r="B286" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B287" t="s">
         <v>529</v>
@@ -9173,12 +9179,12 @@
         <v>534</v>
       </c>
       <c r="B290" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="291" spans="1:2">
       <c r="A291" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B291" t="s">
         <v>536</v>
@@ -9213,20 +9219,20 @@
         <v>543</v>
       </c>
       <c r="B295" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B296" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B297" t="s">
         <v>546</v>
@@ -9405,20 +9411,20 @@
         <v>589</v>
       </c>
       <c r="B319" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B320" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B321" t="s">
         <v>592</v>
@@ -9453,12 +9459,12 @@
         <v>599</v>
       </c>
       <c r="B325" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B326" t="s">
         <v>601</v>
@@ -9501,12 +9507,12 @@
         <v>610</v>
       </c>
       <c r="B331" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B332" t="s">
         <v>612</v>
@@ -9573,12 +9579,12 @@
         <v>627</v>
       </c>
       <c r="B340" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B341" t="s">
         <v>629</v>
@@ -9733,12 +9739,12 @@
         <v>666</v>
       </c>
       <c r="B360" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B361" t="s">
         <v>668</v>
@@ -9765,12 +9771,12 @@
         <v>673</v>
       </c>
       <c r="B364" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="365" spans="1:2">
       <c r="A365" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B365" t="s">
         <v>675</v>
@@ -10309,12 +10315,12 @@
         <v>808</v>
       </c>
       <c r="B432" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="433" spans="1:2">
       <c r="A433" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B433" t="s">
         <v>810</v>
@@ -10349,12 +10355,12 @@
         <v>817</v>
       </c>
       <c r="B437" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B438" t="s">
         <v>819</v>
@@ -10413,12 +10419,12 @@
         <v>832</v>
       </c>
       <c r="B445" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="446" spans="1:2">
       <c r="A446" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B446" t="s">
         <v>834</v>
@@ -10445,12 +10451,12 @@
         <v>839</v>
       </c>
       <c r="B449" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B450" t="s">
         <v>841</v>
@@ -10493,12 +10499,12 @@
         <v>850</v>
       </c>
       <c r="B455" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="456" spans="1:2">
       <c r="A456" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B456" t="s">
         <v>852</v>
@@ -10581,20 +10587,20 @@
         <v>871</v>
       </c>
       <c r="B466" t="s">
-        <v>588</v>
+        <v>872</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B467" t="s">
-        <v>872</v>
+        <v>590</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B468" t="s">
         <v>874</v>
@@ -10637,15 +10643,15 @@
         <v>883</v>
       </c>
       <c r="B473" t="s">
-        <v>588</v>
+        <v>884</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B474" t="s">
-        <v>885</v>
+        <v>590</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -10653,12 +10659,12 @@
         <v>886</v>
       </c>
       <c r="B475" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B476" t="s">
         <v>888</v>
@@ -10709,12 +10715,12 @@
         <v>899</v>
       </c>
       <c r="B482" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B483" t="s">
         <v>901</v>
@@ -10733,12 +10739,12 @@
         <v>904</v>
       </c>
       <c r="B485" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B486" t="s">
         <v>906</v>
@@ -10749,12 +10755,12 @@
         <v>907</v>
       </c>
       <c r="B487" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B488" t="s">
         <v>909</v>
@@ -10933,12 +10939,12 @@
         <v>952</v>
       </c>
       <c r="B510" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="511" spans="1:2">
       <c r="A511" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B511" t="s">
         <v>954</v>
@@ -10957,12 +10963,12 @@
         <v>957</v>
       </c>
       <c r="B513" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="A514" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B514" t="s">
         <v>959</v>
@@ -11109,12 +11115,12 @@
         <v>994</v>
       </c>
       <c r="B532" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="533" spans="1:2">
       <c r="A533" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B533" t="s">
         <v>996</v>
@@ -11261,76 +11267,76 @@
         <v>1031</v>
       </c>
       <c r="B551" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B552" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B553" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B554" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B555" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B556" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B557" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B558" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B559" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B560" t="s">
         <v>1041</v>
@@ -11357,20 +11363,20 @@
         <v>1046</v>
       </c>
       <c r="B563" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B564" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="565" spans="1:2">
       <c r="A565" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B565" t="s">
         <v>1049</v>
@@ -11445,12 +11451,12 @@
         <v>1066</v>
       </c>
       <c r="B574" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B575" t="s">
         <v>1068</v>
@@ -11469,20 +11475,20 @@
         <v>1071</v>
       </c>
       <c r="B577" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B578" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B579" t="s">
         <v>1074</v>
@@ -11493,12 +11499,12 @@
         <v>1075</v>
       </c>
       <c r="B580" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B581" t="s">
         <v>1077</v>
@@ -11525,12 +11531,12 @@
         <v>1082</v>
       </c>
       <c r="B584" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B585" t="s">
         <v>1084</v>
@@ -11549,12 +11555,12 @@
         <v>1087</v>
       </c>
       <c r="B587" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B588" t="s">
         <v>1089</v>
@@ -11597,12 +11603,12 @@
         <v>1098</v>
       </c>
       <c r="B593" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B594" t="s">
         <v>1100</v>
@@ -11637,12 +11643,12 @@
         <v>1107</v>
       </c>
       <c r="B598" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B599" t="s">
         <v>1109</v>
@@ -11717,12 +11723,12 @@
         <v>1126</v>
       </c>
       <c r="B608" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B609" t="s">
         <v>1128</v>
@@ -11765,12 +11771,12 @@
         <v>1137</v>
       </c>
       <c r="B614" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B615" t="s">
         <v>1139</v>
@@ -11781,12 +11787,12 @@
         <v>1140</v>
       </c>
       <c r="B616" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B617" t="s">
         <v>1142</v>
@@ -11829,12 +11835,12 @@
         <v>1151</v>
       </c>
       <c r="B622" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B623" t="s">
         <v>1153</v>
@@ -11869,12 +11875,12 @@
         <v>1160</v>
       </c>
       <c r="B627" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B628" t="s">
         <v>1162</v>
@@ -11941,20 +11947,20 @@
         <v>1177</v>
       </c>
       <c r="B636" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B637" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B638" t="s">
         <v>1180</v>
@@ -11973,12 +11979,12 @@
         <v>1183</v>
       </c>
       <c r="B640" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B641" t="s">
         <v>1185</v>
@@ -11989,20 +11995,20 @@
         <v>1186</v>
       </c>
       <c r="B642" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B643" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B644" t="s">
         <v>1189</v>
@@ -12045,12 +12051,12 @@
         <v>1198</v>
       </c>
       <c r="B649" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B650" t="s">
         <v>1200</v>
@@ -12085,12 +12091,12 @@
         <v>1207</v>
       </c>
       <c r="B654" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="655" spans="1:2">
       <c r="A655" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B655" t="s">
         <v>1209</v>
@@ -12101,12 +12107,12 @@
         <v>1210</v>
       </c>
       <c r="B656" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B657" t="s">
         <v>1212</v>
@@ -12349,20 +12355,20 @@
         <v>1271</v>
       </c>
       <c r="B687" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B688" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B689" t="s">
         <v>1274</v>
@@ -12421,12 +12427,12 @@
         <v>1287</v>
       </c>
       <c r="B696" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="697" spans="1:2">
       <c r="A697" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B697" t="s">
         <v>1289</v>
@@ -12493,12 +12499,12 @@
         <v>1304</v>
       </c>
       <c r="B705" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B706" t="s">
         <v>1306</v>
@@ -12509,20 +12515,20 @@
         <v>1307</v>
       </c>
       <c r="B707" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B708" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B709" t="s">
         <v>1310</v>
@@ -12565,12 +12571,12 @@
         <v>1319</v>
       </c>
       <c r="B714" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B715" t="s">
         <v>1321</v>
@@ -12581,12 +12587,12 @@
         <v>1322</v>
       </c>
       <c r="B716" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B717" t="s">
         <v>1324</v>
@@ -12621,12 +12627,12 @@
         <v>1331</v>
       </c>
       <c r="B721" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B722" t="s">
         <v>1333</v>
@@ -12645,12 +12651,12 @@
         <v>1336</v>
       </c>
       <c r="B724" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B725" t="s">
         <v>1338</v>
@@ -12661,20 +12667,20 @@
         <v>1339</v>
       </c>
       <c r="B726" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B727" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B728" t="s">
         <v>1342</v>
@@ -12693,12 +12699,12 @@
         <v>1345</v>
       </c>
       <c r="B730" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B731" t="s">
         <v>1347</v>
@@ -12709,20 +12715,20 @@
         <v>1348</v>
       </c>
       <c r="B732" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B733" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B734" t="s">
         <v>1351</v>
@@ -12789,12 +12795,12 @@
         <v>1366</v>
       </c>
       <c r="B742" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B743" t="s">
         <v>1368</v>
@@ -12821,12 +12827,12 @@
         <v>1373</v>
       </c>
       <c r="B746" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B747" t="s">
         <v>1375</v>
@@ -12941,20 +12947,20 @@
         <v>1402</v>
       </c>
       <c r="B761" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="762" spans="1:2">
       <c r="A762" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B762" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="763" spans="1:2">
       <c r="A763" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B763" t="s">
         <v>1405</v>
@@ -12997,12 +13003,12 @@
         <v>1414</v>
       </c>
       <c r="B768" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B769" t="s">
         <v>1416</v>
@@ -13045,12 +13051,12 @@
         <v>1425</v>
       </c>
       <c r="B774" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="775" spans="1:2">
       <c r="A775" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B775" t="s">
         <v>1427</v>
@@ -13085,12 +13091,12 @@
         <v>1434</v>
       </c>
       <c r="B779" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="780" spans="1:2">
       <c r="A780" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B780" t="s">
         <v>1436</v>
@@ -13157,28 +13163,28 @@
         <v>1451</v>
       </c>
       <c r="B788" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B789" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B790" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B791" t="s">
         <v>1455</v>
@@ -13229,44 +13235,44 @@
         <v>1466</v>
       </c>
       <c r="B797" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B798" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B799" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B800" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B801" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B802" t="s">
         <v>1472</v>
@@ -13285,15 +13291,15 @@
         <v>1475</v>
       </c>
       <c r="B804" t="s">
-        <v>132</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B805" t="s">
-        <v>1477</v>
+        <v>134</v>
       </c>
     </row>
     <row r="806" spans="1:2">
@@ -13357,20 +13363,20 @@
         <v>1492</v>
       </c>
       <c r="B813" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B814" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B815" t="s">
         <v>1495</v>
@@ -13421,20 +13427,20 @@
         <v>1506</v>
       </c>
       <c r="B821" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B822" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B823" t="s">
         <v>1509</v>
@@ -13453,20 +13459,20 @@
         <v>1512</v>
       </c>
       <c r="B825" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B826" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B827" t="s">
         <v>1515</v>
@@ -13501,12 +13507,12 @@
         <v>1522</v>
       </c>
       <c r="B831" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B832" t="s">
         <v>1524</v>
@@ -13557,28 +13563,28 @@
         <v>1535</v>
       </c>
       <c r="B838" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B839" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B840" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B841" t="s">
         <v>1539</v>
@@ -13637,12 +13643,12 @@
         <v>1552</v>
       </c>
       <c r="B848" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B849" t="s">
         <v>1554</v>
@@ -13661,84 +13667,84 @@
         <v>1557</v>
       </c>
       <c r="B851" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B852" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B853" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B854" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B855" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B856" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B857" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B858" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B859" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B860" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B861" t="s">
         <v>1568</v>
@@ -13805,12 +13811,12 @@
         <v>1583</v>
       </c>
       <c r="B869" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B870" t="s">
         <v>1585</v>
@@ -13941,20 +13947,20 @@
         <v>1616</v>
       </c>
       <c r="B886" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B887" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B888" t="s">
         <v>1619</v>
@@ -14005,12 +14011,12 @@
         <v>1630</v>
       </c>
       <c r="B894" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B895" t="s">
         <v>1632</v>
@@ -14021,12 +14027,12 @@
         <v>1633</v>
       </c>
       <c r="B896" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B897" t="s">
         <v>1635</v>
@@ -14037,12 +14043,12 @@
         <v>1636</v>
       </c>
       <c r="B898" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B899" t="s">
         <v>1638</v>
@@ -14165,12 +14171,12 @@
         <v>1667</v>
       </c>
       <c r="B914" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B915" t="s">
         <v>1669</v>
@@ -14237,20 +14243,20 @@
         <v>1684</v>
       </c>
       <c r="B923" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B924" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B925" t="s">
         <v>1687</v>
@@ -14301,12 +14307,12 @@
         <v>1698</v>
       </c>
       <c r="B931" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="932" spans="1:2">
       <c r="A932" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B932" t="s">
         <v>1700</v>
@@ -14365,12 +14371,12 @@
         <v>1713</v>
       </c>
       <c r="B939" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B940" t="s">
         <v>1715</v>
@@ -14381,12 +14387,12 @@
         <v>1716</v>
       </c>
       <c r="B941" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B942" t="s">
         <v>1718</v>
@@ -14421,12 +14427,12 @@
         <v>1725</v>
       </c>
       <c r="B946" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B947" t="s">
         <v>1727</v>
@@ -14453,12 +14459,12 @@
         <v>1732</v>
       </c>
       <c r="B950" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B951" t="s">
         <v>1734</v>
@@ -14517,12 +14523,12 @@
         <v>1747</v>
       </c>
       <c r="B958" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B959" t="s">
         <v>1749</v>
@@ -14565,20 +14571,20 @@
         <v>1758</v>
       </c>
       <c r="B964" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B965" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B966" t="s">
         <v>1761</v>
@@ -14637,12 +14643,12 @@
         <v>1774</v>
       </c>
       <c r="B973" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B974" t="s">
         <v>1776</v>
@@ -14757,12 +14763,12 @@
         <v>1803</v>
       </c>
       <c r="B988" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B989" t="s">
         <v>1805</v>
@@ -14789,20 +14795,20 @@
         <v>1810</v>
       </c>
       <c r="B992" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B993" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B994" t="s">
         <v>1813</v>
@@ -14821,12 +14827,12 @@
         <v>1816</v>
       </c>
       <c r="B996" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B997" t="s">
         <v>1818</v>
@@ -14861,12 +14867,12 @@
         <v>1825</v>
       </c>
       <c r="B1001" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B1002" t="s">
         <v>1827</v>
@@ -14885,12 +14891,12 @@
         <v>1830</v>
       </c>
       <c r="B1004" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B1005" t="s">
         <v>1832</v>
@@ -14941,20 +14947,20 @@
         <v>1843</v>
       </c>
       <c r="B1011" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B1012" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B1013" t="s">
         <v>1846</v>
@@ -14989,12 +14995,12 @@
         <v>1853</v>
       </c>
       <c r="B1017" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1018" t="s">
         <v>1855</v>
@@ -15053,12 +15059,12 @@
         <v>1868</v>
       </c>
       <c r="B1025" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B1026" t="s">
         <v>1870</v>
@@ -15133,12 +15139,12 @@
         <v>1887</v>
       </c>
       <c r="B1035" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="B1036" t="s">
         <v>1889</v>
@@ -15149,44 +15155,44 @@
         <v>1890</v>
       </c>
       <c r="B1037" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1038" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="B1039" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="B1040" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="B1041" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B1042" t="s">
         <v>1896</v>
@@ -15213,12 +15219,12 @@
         <v>1901</v>
       </c>
       <c r="B1045" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B1046" t="s">
         <v>1903</v>
@@ -15245,12 +15251,12 @@
         <v>1908</v>
       </c>
       <c r="B1049" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="B1050" t="s">
         <v>1910</v>
@@ -15285,12 +15291,12 @@
         <v>1917</v>
       </c>
       <c r="B1054" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="B1055" t="s">
         <v>1919</v>
@@ -15301,12 +15307,12 @@
         <v>1920</v>
       </c>
       <c r="B1056" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="B1057" t="s">
         <v>1922</v>
@@ -15397,12 +15403,12 @@
         <v>1943</v>
       </c>
       <c r="B1068" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="B1069" t="s">
         <v>1945</v>
@@ -15533,12 +15539,12 @@
         <v>1976</v>
       </c>
       <c r="B1085" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="B1086" t="s">
         <v>1978</v>
@@ -15557,12 +15563,12 @@
         <v>1981</v>
       </c>
       <c r="B1088" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B1089" t="s">
         <v>1983</v>
@@ -15661,12 +15667,12 @@
         <v>2006</v>
       </c>
       <c r="B1101" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B1102" t="s">
         <v>2008</v>
@@ -15741,44 +15747,44 @@
         <v>2025</v>
       </c>
       <c r="B1111" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B1112" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B1113" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B1114" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B1115" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="B1116" t="s">
         <v>2031</v>
@@ -15805,12 +15811,12 @@
         <v>2036</v>
       </c>
       <c r="B1119" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B1120" t="s">
         <v>2038</v>
@@ -15821,12 +15827,12 @@
         <v>2039</v>
       </c>
       <c r="B1121" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="B1122" t="s">
         <v>2041</v>
@@ -16013,12 +16019,12 @@
         <v>2086</v>
       </c>
       <c r="B1145" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="B1146" t="s">
         <v>2088</v>
@@ -16045,20 +16051,20 @@
         <v>2093</v>
       </c>
       <c r="B1149" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="B1150" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="B1151" t="s">
         <v>2096</v>
@@ -16181,12 +16187,12 @@
         <v>2125</v>
       </c>
       <c r="B1166" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="B1167" t="s">
         <v>2127</v>
@@ -16213,12 +16219,12 @@
         <v>2132</v>
       </c>
       <c r="B1170" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="B1171" t="s">
         <v>2134</v>
@@ -16245,12 +16251,12 @@
         <v>2139</v>
       </c>
       <c r="B1174" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="B1175" t="s">
         <v>2141</v>
@@ -16261,20 +16267,20 @@
         <v>2142</v>
       </c>
       <c r="B1176" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="B1177" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="B1178" t="s">
         <v>2145</v>
@@ -16285,12 +16291,12 @@
         <v>2146</v>
       </c>
       <c r="B1179" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="B1180" t="s">
         <v>2148</v>
@@ -16325,12 +16331,12 @@
         <v>2155</v>
       </c>
       <c r="B1184" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="B1185" t="s">
         <v>2157</v>
@@ -16352,8 +16358,16 @@
         <v>2161</v>
       </c>
     </row>
+    <row r="1188" spans="1:2">
+      <c r="A1188" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>2163</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1187"/>
+  <autoFilter ref="A1:B1188"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2166">
   <si>
     <t>en</t>
   </si>
@@ -5207,6 +5207,12 @@
   </si>
   <si>
     <t>Тени Мордора</t>
+  </si>
+  <si>
+    <t>Shark</t>
+  </si>
+  <si>
+    <t>Акула</t>
   </si>
   <si>
     <t>Sheep</t>
@@ -6855,7 +6861,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1188"/>
+  <dimension ref="A1:B1189"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14467,12 +14473,12 @@
         <v>1734</v>
       </c>
       <c r="B951" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B952" t="s">
         <v>1736</v>
@@ -14531,12 +14537,12 @@
         <v>1749</v>
       </c>
       <c r="B959" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B960" t="s">
         <v>1751</v>
@@ -14579,20 +14585,20 @@
         <v>1760</v>
       </c>
       <c r="B965" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="B966" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B967" t="s">
         <v>1763</v>
@@ -14651,12 +14657,12 @@
         <v>1776</v>
       </c>
       <c r="B974" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B975" t="s">
         <v>1778</v>
@@ -14771,12 +14777,12 @@
         <v>1805</v>
       </c>
       <c r="B989" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B990" t="s">
         <v>1807</v>
@@ -14803,20 +14809,20 @@
         <v>1812</v>
       </c>
       <c r="B993" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B994" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B995" t="s">
         <v>1815</v>
@@ -14835,12 +14841,12 @@
         <v>1818</v>
       </c>
       <c r="B997" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B998" t="s">
         <v>1820</v>
@@ -14875,12 +14881,12 @@
         <v>1827</v>
       </c>
       <c r="B1002" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1003" t="s">
         <v>1829</v>
@@ -14899,12 +14905,12 @@
         <v>1832</v>
       </c>
       <c r="B1005" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B1006" t="s">
         <v>1834</v>
@@ -14955,20 +14961,20 @@
         <v>1845</v>
       </c>
       <c r="B1012" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B1013" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="B1014" t="s">
         <v>1848</v>
@@ -15003,12 +15009,12 @@
         <v>1855</v>
       </c>
       <c r="B1018" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B1019" t="s">
         <v>1857</v>
@@ -15067,12 +15073,12 @@
         <v>1870</v>
       </c>
       <c r="B1026" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B1027" t="s">
         <v>1872</v>
@@ -15147,12 +15153,12 @@
         <v>1889</v>
       </c>
       <c r="B1036" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="B1037" t="s">
         <v>1891</v>
@@ -15163,44 +15169,44 @@
         <v>1892</v>
       </c>
       <c r="B1038" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="B1039" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="B1040" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B1041" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="B1042" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="B1043" t="s">
         <v>1898</v>
@@ -15227,12 +15233,12 @@
         <v>1903</v>
       </c>
       <c r="B1046" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B1047" t="s">
         <v>1905</v>
@@ -15259,12 +15265,12 @@
         <v>1910</v>
       </c>
       <c r="B1050" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="B1051" t="s">
         <v>1912</v>
@@ -15299,12 +15305,12 @@
         <v>1919</v>
       </c>
       <c r="B1055" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="B1056" t="s">
         <v>1921</v>
@@ -15315,12 +15321,12 @@
         <v>1922</v>
       </c>
       <c r="B1057" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B1058" t="s">
         <v>1924</v>
@@ -15411,12 +15417,12 @@
         <v>1945</v>
       </c>
       <c r="B1069" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="B1070" t="s">
         <v>1947</v>
@@ -15547,12 +15553,12 @@
         <v>1978</v>
       </c>
       <c r="B1086" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B1087" t="s">
         <v>1980</v>
@@ -15571,12 +15577,12 @@
         <v>1983</v>
       </c>
       <c r="B1089" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="B1090" t="s">
         <v>1985</v>
@@ -15675,12 +15681,12 @@
         <v>2008</v>
       </c>
       <c r="B1102" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B1103" t="s">
         <v>2010</v>
@@ -15755,44 +15761,44 @@
         <v>2027</v>
       </c>
       <c r="B1112" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B1113" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B1114" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="B1115" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B1116" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="B1117" t="s">
         <v>2033</v>
@@ -15819,12 +15825,12 @@
         <v>2038</v>
       </c>
       <c r="B1120" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B1121" t="s">
         <v>2040</v>
@@ -15835,12 +15841,12 @@
         <v>2041</v>
       </c>
       <c r="B1122" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="B1123" t="s">
         <v>2043</v>
@@ -16027,12 +16033,12 @@
         <v>2088</v>
       </c>
       <c r="B1146" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="B1147" t="s">
         <v>2090</v>
@@ -16059,20 +16065,20 @@
         <v>2095</v>
       </c>
       <c r="B1150" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="B1151" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="B1152" t="s">
         <v>2098</v>
@@ -16195,12 +16201,12 @@
         <v>2127</v>
       </c>
       <c r="B1167" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="B1168" t="s">
         <v>2129</v>
@@ -16227,12 +16233,12 @@
         <v>2134</v>
       </c>
       <c r="B1171" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="B1172" t="s">
         <v>2136</v>
@@ -16259,12 +16265,12 @@
         <v>2141</v>
       </c>
       <c r="B1175" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="B1176" t="s">
         <v>2143</v>
@@ -16275,20 +16281,20 @@
         <v>2144</v>
       </c>
       <c r="B1177" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="B1178" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="B1179" t="s">
         <v>2147</v>
@@ -16299,12 +16305,12 @@
         <v>2148</v>
       </c>
       <c r="B1180" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="B1181" t="s">
         <v>2150</v>
@@ -16339,12 +16345,12 @@
         <v>2157</v>
       </c>
       <c r="B1185" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="B1186" t="s">
         <v>2159</v>
@@ -16366,8 +16372,16 @@
         <v>2163</v>
       </c>
     </row>
+    <row r="1189" spans="1:2">
+      <c r="A1189" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>2165</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1188"/>
+  <autoFilter ref="A1:B1189"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -1816,6 +1816,12 @@
     <t>Сказки</t>
   </si>
   <si>
+    <t>Fall Drop</t>
+  </si>
+  <si>
+    <t>Осенняя капель</t>
+  </si>
+  <si>
     <t>Fall Guys</t>
   </si>
   <si>
@@ -6509,12 +6515,6 @@
   </si>
   <si>
     <t>Теги Гипиксель (мутации)</t>
-  </si>
-  <si>
-    <t>Fall Drop</t>
-  </si>
-  <si>
-    <t>Осенняя капель</t>
   </si>
 </sst>
 </file>
@@ -9473,12 +9473,12 @@
         <v>601</v>
       </c>
       <c r="B326" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B327" t="s">
         <v>603</v>
@@ -9521,12 +9521,12 @@
         <v>612</v>
       </c>
       <c r="B332" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B333" t="s">
         <v>614</v>
@@ -9593,12 +9593,12 @@
         <v>629</v>
       </c>
       <c r="B341" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B342" t="s">
         <v>631</v>
@@ -9753,12 +9753,12 @@
         <v>668</v>
       </c>
       <c r="B361" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B362" t="s">
         <v>670</v>
@@ -9785,12 +9785,12 @@
         <v>675</v>
       </c>
       <c r="B365" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B366" t="s">
         <v>677</v>
@@ -10329,12 +10329,12 @@
         <v>810</v>
       </c>
       <c r="B433" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B434" t="s">
         <v>812</v>
@@ -10369,12 +10369,12 @@
         <v>819</v>
       </c>
       <c r="B438" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B439" t="s">
         <v>821</v>
@@ -10433,12 +10433,12 @@
         <v>834</v>
       </c>
       <c r="B446" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B447" t="s">
         <v>836</v>
@@ -10465,12 +10465,12 @@
         <v>841</v>
       </c>
       <c r="B450" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B451" t="s">
         <v>843</v>
@@ -10513,12 +10513,12 @@
         <v>852</v>
       </c>
       <c r="B456" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B457" t="s">
         <v>854</v>
@@ -10601,20 +10601,20 @@
         <v>873</v>
       </c>
       <c r="B467" t="s">
-        <v>590</v>
+        <v>874</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B468" t="s">
-        <v>874</v>
+        <v>590</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B469" t="s">
         <v>876</v>
@@ -10657,15 +10657,15 @@
         <v>885</v>
       </c>
       <c r="B474" t="s">
-        <v>590</v>
+        <v>886</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B475" t="s">
-        <v>887</v>
+        <v>590</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -10673,12 +10673,12 @@
         <v>888</v>
       </c>
       <c r="B476" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B477" t="s">
         <v>890</v>
@@ -10729,12 +10729,12 @@
         <v>901</v>
       </c>
       <c r="B483" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B484" t="s">
         <v>903</v>
@@ -10753,12 +10753,12 @@
         <v>906</v>
       </c>
       <c r="B486" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B487" t="s">
         <v>908</v>
@@ -10769,12 +10769,12 @@
         <v>909</v>
       </c>
       <c r="B488" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B489" t="s">
         <v>911</v>
@@ -10953,12 +10953,12 @@
         <v>954</v>
       </c>
       <c r="B511" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="512" spans="1:2">
       <c r="A512" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B512" t="s">
         <v>956</v>
@@ -10977,12 +10977,12 @@
         <v>959</v>
       </c>
       <c r="B514" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B515" t="s">
         <v>961</v>
@@ -11129,12 +11129,12 @@
         <v>996</v>
       </c>
       <c r="B533" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B534" t="s">
         <v>998</v>
@@ -11281,76 +11281,76 @@
         <v>1033</v>
       </c>
       <c r="B552" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B553" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B554" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B555" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B556" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B557" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B558" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B559" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B560" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B561" t="s">
         <v>1043</v>
@@ -11377,20 +11377,20 @@
         <v>1048</v>
       </c>
       <c r="B564" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="565" spans="1:2">
       <c r="A565" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B565" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="566" spans="1:2">
       <c r="A566" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B566" t="s">
         <v>1051</v>
@@ -11465,12 +11465,12 @@
         <v>1068</v>
       </c>
       <c r="B575" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="576" spans="1:2">
       <c r="A576" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B576" t="s">
         <v>1070</v>
@@ -11489,20 +11489,20 @@
         <v>1073</v>
       </c>
       <c r="B578" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B579" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B580" t="s">
         <v>1076</v>
@@ -11513,12 +11513,12 @@
         <v>1077</v>
       </c>
       <c r="B581" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B582" t="s">
         <v>1079</v>
@@ -11545,12 +11545,12 @@
         <v>1084</v>
       </c>
       <c r="B585" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B586" t="s">
         <v>1086</v>
@@ -11569,12 +11569,12 @@
         <v>1089</v>
       </c>
       <c r="B588" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B589" t="s">
         <v>1091</v>
@@ -11617,12 +11617,12 @@
         <v>1100</v>
       </c>
       <c r="B594" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B595" t="s">
         <v>1102</v>
@@ -11657,12 +11657,12 @@
         <v>1109</v>
       </c>
       <c r="B599" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B600" t="s">
         <v>1111</v>
@@ -11737,12 +11737,12 @@
         <v>1128</v>
       </c>
       <c r="B609" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B610" t="s">
         <v>1130</v>
@@ -11785,12 +11785,12 @@
         <v>1139</v>
       </c>
       <c r="B615" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B616" t="s">
         <v>1141</v>
@@ -11801,12 +11801,12 @@
         <v>1142</v>
       </c>
       <c r="B617" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B618" t="s">
         <v>1144</v>
@@ -11849,12 +11849,12 @@
         <v>1153</v>
       </c>
       <c r="B623" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B624" t="s">
         <v>1155</v>
@@ -11889,12 +11889,12 @@
         <v>1162</v>
       </c>
       <c r="B628" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B629" t="s">
         <v>1164</v>
@@ -11961,20 +11961,20 @@
         <v>1179</v>
       </c>
       <c r="B637" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B638" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B639" t="s">
         <v>1182</v>
@@ -11993,12 +11993,12 @@
         <v>1185</v>
       </c>
       <c r="B641" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B642" t="s">
         <v>1187</v>
@@ -12009,20 +12009,20 @@
         <v>1188</v>
       </c>
       <c r="B643" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B644" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B645" t="s">
         <v>1191</v>
@@ -12065,12 +12065,12 @@
         <v>1200</v>
       </c>
       <c r="B650" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B651" t="s">
         <v>1202</v>
@@ -12105,12 +12105,12 @@
         <v>1209</v>
       </c>
       <c r="B655" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="656" spans="1:2">
       <c r="A656" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B656" t="s">
         <v>1211</v>
@@ -12121,12 +12121,12 @@
         <v>1212</v>
       </c>
       <c r="B657" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B658" t="s">
         <v>1214</v>
@@ -12369,20 +12369,20 @@
         <v>1273</v>
       </c>
       <c r="B688" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B689" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B690" t="s">
         <v>1276</v>
@@ -12441,12 +12441,12 @@
         <v>1289</v>
       </c>
       <c r="B697" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="698" spans="1:2">
       <c r="A698" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B698" t="s">
         <v>1291</v>
@@ -12513,12 +12513,12 @@
         <v>1306</v>
       </c>
       <c r="B706" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B707" t="s">
         <v>1308</v>
@@ -12529,20 +12529,20 @@
         <v>1309</v>
       </c>
       <c r="B708" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B709" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B710" t="s">
         <v>1312</v>
@@ -12585,12 +12585,12 @@
         <v>1321</v>
       </c>
       <c r="B715" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B716" t="s">
         <v>1323</v>
@@ -12601,12 +12601,12 @@
         <v>1324</v>
       </c>
       <c r="B717" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B718" t="s">
         <v>1326</v>
@@ -12641,12 +12641,12 @@
         <v>1333</v>
       </c>
       <c r="B722" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B723" t="s">
         <v>1335</v>
@@ -12665,12 +12665,12 @@
         <v>1338</v>
       </c>
       <c r="B725" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B726" t="s">
         <v>1340</v>
@@ -12681,20 +12681,20 @@
         <v>1341</v>
       </c>
       <c r="B727" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B728" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B729" t="s">
         <v>1344</v>
@@ -12713,12 +12713,12 @@
         <v>1347</v>
       </c>
       <c r="B731" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B732" t="s">
         <v>1349</v>
@@ -12729,20 +12729,20 @@
         <v>1350</v>
       </c>
       <c r="B733" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B734" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B735" t="s">
         <v>1353</v>
@@ -12809,12 +12809,12 @@
         <v>1368</v>
       </c>
       <c r="B743" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B744" t="s">
         <v>1370</v>
@@ -12841,12 +12841,12 @@
         <v>1375</v>
       </c>
       <c r="B747" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B748" t="s">
         <v>1377</v>
@@ -12961,20 +12961,20 @@
         <v>1404</v>
       </c>
       <c r="B762" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="763" spans="1:2">
       <c r="A763" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="B763" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B764" t="s">
         <v>1407</v>
@@ -13017,12 +13017,12 @@
         <v>1416</v>
       </c>
       <c r="B769" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B770" t="s">
         <v>1418</v>
@@ -13065,12 +13065,12 @@
         <v>1427</v>
       </c>
       <c r="B775" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B776" t="s">
         <v>1429</v>
@@ -13105,12 +13105,12 @@
         <v>1436</v>
       </c>
       <c r="B780" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B781" t="s">
         <v>1438</v>
@@ -13177,28 +13177,28 @@
         <v>1453</v>
       </c>
       <c r="B789" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B790" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B791" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B792" t="s">
         <v>1457</v>
@@ -13249,44 +13249,44 @@
         <v>1468</v>
       </c>
       <c r="B798" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B799" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B800" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B801" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B802" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B803" t="s">
         <v>1474</v>
@@ -13305,15 +13305,15 @@
         <v>1477</v>
       </c>
       <c r="B805" t="s">
-        <v>134</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B806" t="s">
-        <v>1479</v>
+        <v>134</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -13377,20 +13377,20 @@
         <v>1494</v>
       </c>
       <c r="B814" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B815" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B816" t="s">
         <v>1497</v>
@@ -13441,20 +13441,20 @@
         <v>1508</v>
       </c>
       <c r="B822" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B823" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B824" t="s">
         <v>1511</v>
@@ -13473,20 +13473,20 @@
         <v>1514</v>
       </c>
       <c r="B826" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B827" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B828" t="s">
         <v>1517</v>
@@ -13521,12 +13521,12 @@
         <v>1524</v>
       </c>
       <c r="B832" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B833" t="s">
         <v>1526</v>
@@ -13577,28 +13577,28 @@
         <v>1537</v>
       </c>
       <c r="B839" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B840" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B841" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B842" t="s">
         <v>1541</v>
@@ -13657,12 +13657,12 @@
         <v>1554</v>
       </c>
       <c r="B849" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B850" t="s">
         <v>1556</v>
@@ -13681,84 +13681,84 @@
         <v>1559</v>
       </c>
       <c r="B852" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B853" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B854" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B855" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B856" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B857" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B858" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B859" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B860" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B861" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B862" t="s">
         <v>1570</v>
@@ -13825,12 +13825,12 @@
         <v>1585</v>
       </c>
       <c r="B870" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B871" t="s">
         <v>1587</v>
@@ -13961,20 +13961,20 @@
         <v>1618</v>
       </c>
       <c r="B887" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B888" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B889" t="s">
         <v>1621</v>
@@ -14025,12 +14025,12 @@
         <v>1632</v>
       </c>
       <c r="B895" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B896" t="s">
         <v>1634</v>
@@ -14041,12 +14041,12 @@
         <v>1635</v>
       </c>
       <c r="B897" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B898" t="s">
         <v>1637</v>
@@ -14057,12 +14057,12 @@
         <v>1638</v>
       </c>
       <c r="B899" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B900" t="s">
         <v>1640</v>
@@ -14185,12 +14185,12 @@
         <v>1669</v>
       </c>
       <c r="B915" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B916" t="s">
         <v>1671</v>
@@ -14257,20 +14257,20 @@
         <v>1686</v>
       </c>
       <c r="B924" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B925" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B926" t="s">
         <v>1689</v>
@@ -14321,12 +14321,12 @@
         <v>1700</v>
       </c>
       <c r="B932" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B933" t="s">
         <v>1702</v>
@@ -14385,12 +14385,12 @@
         <v>1715</v>
       </c>
       <c r="B940" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B941" t="s">
         <v>1717</v>
@@ -14401,12 +14401,12 @@
         <v>1718</v>
       </c>
       <c r="B942" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B943" t="s">
         <v>1720</v>
@@ -14441,12 +14441,12 @@
         <v>1727</v>
       </c>
       <c r="B947" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B948" t="s">
         <v>1729</v>
@@ -14481,12 +14481,12 @@
         <v>1736</v>
       </c>
       <c r="B952" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="B953" t="s">
         <v>1738</v>
@@ -14545,12 +14545,12 @@
         <v>1751</v>
       </c>
       <c r="B960" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B961" t="s">
         <v>1753</v>
@@ -14593,20 +14593,20 @@
         <v>1762</v>
       </c>
       <c r="B966" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B967" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="B968" t="s">
         <v>1765</v>
@@ -14665,12 +14665,12 @@
         <v>1778</v>
       </c>
       <c r="B975" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B976" t="s">
         <v>1780</v>
@@ -14785,12 +14785,12 @@
         <v>1807</v>
       </c>
       <c r="B990" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B991" t="s">
         <v>1809</v>
@@ -14817,20 +14817,20 @@
         <v>1814</v>
       </c>
       <c r="B994" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B995" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B996" t="s">
         <v>1817</v>
@@ -14849,12 +14849,12 @@
         <v>1820</v>
       </c>
       <c r="B998" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B999" t="s">
         <v>1822</v>
@@ -14889,12 +14889,12 @@
         <v>1829</v>
       </c>
       <c r="B1003" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B1004" t="s">
         <v>1831</v>
@@ -14913,12 +14913,12 @@
         <v>1834</v>
       </c>
       <c r="B1006" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1007" t="s">
         <v>1836</v>
@@ -14969,20 +14969,20 @@
         <v>1847</v>
       </c>
       <c r="B1013" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="B1014" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="B1015" t="s">
         <v>1850</v>
@@ -15017,12 +15017,12 @@
         <v>1857</v>
       </c>
       <c r="B1019" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B1020" t="s">
         <v>1859</v>
@@ -15081,12 +15081,12 @@
         <v>1872</v>
       </c>
       <c r="B1027" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B1028" t="s">
         <v>1874</v>
@@ -15161,12 +15161,12 @@
         <v>1891</v>
       </c>
       <c r="B1037" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="B1038" t="s">
         <v>1893</v>
@@ -15177,44 +15177,44 @@
         <v>1894</v>
       </c>
       <c r="B1039" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B1040" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="B1041" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="B1042" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B1043" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="B1044" t="s">
         <v>1900</v>
@@ -15241,12 +15241,12 @@
         <v>1905</v>
       </c>
       <c r="B1047" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1048" t="s">
         <v>1907</v>
@@ -15273,12 +15273,12 @@
         <v>1912</v>
       </c>
       <c r="B1051" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B1052" t="s">
         <v>1914</v>
@@ -15313,12 +15313,12 @@
         <v>1921</v>
       </c>
       <c r="B1056" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B1057" t="s">
         <v>1923</v>
@@ -15329,12 +15329,12 @@
         <v>1924</v>
       </c>
       <c r="B1058" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B1059" t="s">
         <v>1926</v>
@@ -15425,12 +15425,12 @@
         <v>1947</v>
       </c>
       <c r="B1070" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="B1071" t="s">
         <v>1949</v>
@@ -15561,12 +15561,12 @@
         <v>1980</v>
       </c>
       <c r="B1087" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="B1088" t="s">
         <v>1982</v>
@@ -15585,12 +15585,12 @@
         <v>1985</v>
       </c>
       <c r="B1090" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B1091" t="s">
         <v>1987</v>
@@ -15689,12 +15689,12 @@
         <v>2010</v>
       </c>
       <c r="B1103" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B1104" t="s">
         <v>2012</v>
@@ -15769,44 +15769,44 @@
         <v>2029</v>
       </c>
       <c r="B1113" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="B1114" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B1115" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="B1116" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B1117" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="B1118" t="s">
         <v>2035</v>
@@ -15833,12 +15833,12 @@
         <v>2040</v>
       </c>
       <c r="B1121" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B1122" t="s">
         <v>2042</v>
@@ -15849,12 +15849,12 @@
         <v>2043</v>
       </c>
       <c r="B1123" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="B1124" t="s">
         <v>2045</v>
@@ -16041,12 +16041,12 @@
         <v>2090</v>
       </c>
       <c r="B1147" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="B1148" t="s">
         <v>2092</v>
@@ -16073,20 +16073,20 @@
         <v>2097</v>
       </c>
       <c r="B1151" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="B1152" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="B1153" t="s">
         <v>2100</v>
@@ -16209,12 +16209,12 @@
         <v>2129</v>
       </c>
       <c r="B1168" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="B1169" t="s">
         <v>2131</v>
@@ -16241,12 +16241,12 @@
         <v>2136</v>
       </c>
       <c r="B1172" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="B1173" t="s">
         <v>2138</v>
@@ -16273,12 +16273,12 @@
         <v>2143</v>
       </c>
       <c r="B1176" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="B1177" t="s">
         <v>2145</v>
@@ -16289,20 +16289,20 @@
         <v>2146</v>
       </c>
       <c r="B1178" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="B1179" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="B1180" t="s">
         <v>2149</v>
@@ -16313,12 +16313,12 @@
         <v>2150</v>
       </c>
       <c r="B1181" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="B1182" t="s">
         <v>2152</v>
@@ -16353,12 +16353,12 @@
         <v>2159</v>
       </c>
       <c r="B1186" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="B1187" t="s">
         <v>2161</v>

--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2168">
   <si>
     <t>en</t>
   </si>
@@ -4823,6 +4823,12 @@
   </si>
   <si>
     <t>Хищник</t>
+  </si>
+  <si>
+    <t>Prehistoric Creature</t>
+  </si>
+  <si>
+    <t>Доисторическое существо</t>
   </si>
   <si>
     <t>Present</t>
@@ -6861,7 +6867,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1189"/>
+  <dimension ref="A1:B1190"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13969,20 +13975,20 @@
         <v>1620</v>
       </c>
       <c r="B888" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B889" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B890" t="s">
         <v>1623</v>
@@ -14033,12 +14039,12 @@
         <v>1634</v>
       </c>
       <c r="B896" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B897" t="s">
         <v>1636</v>
@@ -14049,12 +14055,12 @@
         <v>1637</v>
       </c>
       <c r="B898" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B899" t="s">
         <v>1639</v>
@@ -14065,12 +14071,12 @@
         <v>1640</v>
       </c>
       <c r="B900" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B901" t="s">
         <v>1642</v>
@@ -14193,12 +14199,12 @@
         <v>1671</v>
       </c>
       <c r="B916" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B917" t="s">
         <v>1673</v>
@@ -14265,20 +14271,20 @@
         <v>1688</v>
       </c>
       <c r="B925" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B926" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B927" t="s">
         <v>1691</v>
@@ -14329,12 +14335,12 @@
         <v>1702</v>
       </c>
       <c r="B933" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B934" t="s">
         <v>1704</v>
@@ -14393,12 +14399,12 @@
         <v>1717</v>
       </c>
       <c r="B941" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B942" t="s">
         <v>1719</v>
@@ -14409,12 +14415,12 @@
         <v>1720</v>
       </c>
       <c r="B943" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B944" t="s">
         <v>1722</v>
@@ -14449,12 +14455,12 @@
         <v>1729</v>
       </c>
       <c r="B948" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B949" t="s">
         <v>1731</v>
@@ -14489,12 +14495,12 @@
         <v>1738</v>
       </c>
       <c r="B953" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B954" t="s">
         <v>1740</v>
@@ -14553,12 +14559,12 @@
         <v>1753</v>
       </c>
       <c r="B961" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B962" t="s">
         <v>1755</v>
@@ -14601,20 +14607,20 @@
         <v>1764</v>
       </c>
       <c r="B967" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B968" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B969" t="s">
         <v>1767</v>
@@ -14673,12 +14679,12 @@
         <v>1780</v>
       </c>
       <c r="B976" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B977" t="s">
         <v>1782</v>
@@ -14793,12 +14799,12 @@
         <v>1809</v>
       </c>
       <c r="B991" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B992" t="s">
         <v>1811</v>
@@ -14825,20 +14831,20 @@
         <v>1816</v>
       </c>
       <c r="B995" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B996" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B997" t="s">
         <v>1819</v>
@@ -14857,12 +14863,12 @@
         <v>1822</v>
       </c>
       <c r="B999" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B1000" t="s">
         <v>1824</v>
@@ -14897,12 +14903,12 @@
         <v>1831</v>
       </c>
       <c r="B1004" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B1005" t="s">
         <v>1833</v>
@@ -14921,12 +14927,12 @@
         <v>1836</v>
       </c>
       <c r="B1007" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B1008" t="s">
         <v>1838</v>
@@ -14977,20 +14983,20 @@
         <v>1849</v>
       </c>
       <c r="B1014" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="B1015" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B1016" t="s">
         <v>1852</v>
@@ -15025,12 +15031,12 @@
         <v>1859</v>
       </c>
       <c r="B1020" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B1021" t="s">
         <v>1861</v>
@@ -15089,12 +15095,12 @@
         <v>1874</v>
       </c>
       <c r="B1028" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B1029" t="s">
         <v>1876</v>
@@ -15169,12 +15175,12 @@
         <v>1893</v>
       </c>
       <c r="B1038" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="B1039" t="s">
         <v>1895</v>
@@ -15185,44 +15191,44 @@
         <v>1896</v>
       </c>
       <c r="B1040" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="B1041" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B1042" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="B1043" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B1044" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="B1045" t="s">
         <v>1902</v>
@@ -15249,12 +15255,12 @@
         <v>1907</v>
       </c>
       <c r="B1048" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B1049" t="s">
         <v>1909</v>
@@ -15281,12 +15287,12 @@
         <v>1914</v>
       </c>
       <c r="B1052" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="B1053" t="s">
         <v>1916</v>
@@ -15321,12 +15327,12 @@
         <v>1923</v>
       </c>
       <c r="B1057" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="B1058" t="s">
         <v>1925</v>
@@ -15337,12 +15343,12 @@
         <v>1926</v>
       </c>
       <c r="B1059" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B1060" t="s">
         <v>1928</v>
@@ -15433,12 +15439,12 @@
         <v>1949</v>
       </c>
       <c r="B1071" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="B1072" t="s">
         <v>1951</v>
@@ -15569,12 +15575,12 @@
         <v>1982</v>
       </c>
       <c r="B1088" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="B1089" t="s">
         <v>1984</v>
@@ -15593,12 +15599,12 @@
         <v>1987</v>
       </c>
       <c r="B1091" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B1092" t="s">
         <v>1989</v>
@@ -15697,12 +15703,12 @@
         <v>2012</v>
       </c>
       <c r="B1104" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B1105" t="s">
         <v>2014</v>
@@ -15777,44 +15783,44 @@
         <v>2031</v>
       </c>
       <c r="B1114" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="B1115" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B1116" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="B1117" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="B1118" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="B1119" t="s">
         <v>2037</v>
@@ -15841,12 +15847,12 @@
         <v>2042</v>
       </c>
       <c r="B1122" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="B1123" t="s">
         <v>2044</v>
@@ -15857,12 +15863,12 @@
         <v>2045</v>
       </c>
       <c r="B1124" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="B1125" t="s">
         <v>2047</v>
@@ -16049,12 +16055,12 @@
         <v>2092</v>
       </c>
       <c r="B1148" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="B1149" t="s">
         <v>2094</v>
@@ -16081,20 +16087,20 @@
         <v>2099</v>
       </c>
       <c r="B1152" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B1153" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B1154" t="s">
         <v>2102</v>
@@ -16217,12 +16223,12 @@
         <v>2131</v>
       </c>
       <c r="B1169" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="B1170" t="s">
         <v>2133</v>
@@ -16249,12 +16255,12 @@
         <v>2138</v>
       </c>
       <c r="B1173" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="B1174" t="s">
         <v>2140</v>
@@ -16281,12 +16287,12 @@
         <v>2145</v>
       </c>
       <c r="B1177" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="B1178" t="s">
         <v>2147</v>
@@ -16297,20 +16303,20 @@
         <v>2148</v>
       </c>
       <c r="B1179" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="B1180" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="B1181" t="s">
         <v>2151</v>
@@ -16321,12 +16327,12 @@
         <v>2152</v>
       </c>
       <c r="B1182" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="B1183" t="s">
         <v>2154</v>
@@ -16361,12 +16367,12 @@
         <v>2161</v>
       </c>
       <c r="B1187" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="B1188" t="s">
         <v>2163</v>
@@ -16380,8 +16386,16 @@
         <v>2165</v>
       </c>
     </row>
+    <row r="1190" spans="1:2">
+      <c r="A1190" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>2167</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1189"/>
+  <autoFilter ref="A1:B1190"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2170">
   <si>
     <t>en</t>
   </si>
@@ -392,6 +392,12 @@
   </si>
   <si>
     <t>Назад в будущее</t>
+  </si>
+  <si>
+    <t>Backrooms (Movie)</t>
+  </si>
+  <si>
+    <t>«Backrooms» (фильм)</t>
   </si>
   <si>
     <t>Bag</t>
@@ -6867,7 +6873,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1190"/>
+  <dimension ref="A1:B1191"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -7455,20 +7461,20 @@
         <v>137</v>
       </c>
       <c r="B73" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B74" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B75" t="s">
         <v>140</v>
@@ -7663,12 +7669,12 @@
         <v>187</v>
       </c>
       <c r="B99" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B100" t="s">
         <v>189</v>
@@ -7719,12 +7725,12 @@
         <v>200</v>
       </c>
       <c r="B106" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B107" t="s">
         <v>202</v>
@@ -7767,12 +7773,12 @@
         <v>211</v>
       </c>
       <c r="B112" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B113" t="s">
         <v>213</v>
@@ -7799,12 +7805,12 @@
         <v>218</v>
       </c>
       <c r="B116" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B117" t="s">
         <v>220</v>
@@ -7863,12 +7869,12 @@
         <v>233</v>
       </c>
       <c r="B124" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B125" t="s">
         <v>235</v>
@@ -7895,12 +7901,12 @@
         <v>240</v>
       </c>
       <c r="B128" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B129" t="s">
         <v>242</v>
@@ -7919,12 +7925,12 @@
         <v>245</v>
       </c>
       <c r="B131" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B132" t="s">
         <v>247</v>
@@ -7935,12 +7941,12 @@
         <v>248</v>
       </c>
       <c r="B133" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B134" t="s">
         <v>250</v>
@@ -7975,12 +7981,12 @@
         <v>257</v>
       </c>
       <c r="B138" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B139" t="s">
         <v>259</v>
@@ -7999,12 +8005,12 @@
         <v>262</v>
       </c>
       <c r="B141" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B142" t="s">
         <v>264</v>
@@ -8079,28 +8085,28 @@
         <v>281</v>
       </c>
       <c r="B151" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B152" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B153" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B154" t="s">
         <v>285</v>
@@ -8247,12 +8253,12 @@
         <v>320</v>
       </c>
       <c r="B172" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B173" t="s">
         <v>322</v>
@@ -8287,12 +8293,12 @@
         <v>329</v>
       </c>
       <c r="B177" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B178" t="s">
         <v>331</v>
@@ -8303,12 +8309,12 @@
         <v>332</v>
       </c>
       <c r="B179" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B180" t="s">
         <v>334</v>
@@ -8319,20 +8325,20 @@
         <v>335</v>
       </c>
       <c r="B181" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B182" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B183" t="s">
         <v>338</v>
@@ -8551,12 +8557,12 @@
         <v>391</v>
       </c>
       <c r="B210" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B211" t="s">
         <v>393</v>
@@ -8599,12 +8605,12 @@
         <v>402</v>
       </c>
       <c r="B216" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B217" t="s">
         <v>404</v>
@@ -8623,12 +8629,12 @@
         <v>407</v>
       </c>
       <c r="B219" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B220" t="s">
         <v>409</v>
@@ -8655,20 +8661,20 @@
         <v>414</v>
       </c>
       <c r="B223" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B224" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B225" t="s">
         <v>417</v>
@@ -8727,12 +8733,12 @@
         <v>430</v>
       </c>
       <c r="B232" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B233" t="s">
         <v>432</v>
@@ -8863,12 +8869,12 @@
         <v>463</v>
       </c>
       <c r="B249" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B250" t="s">
         <v>465</v>
@@ -8887,12 +8893,12 @@
         <v>468</v>
       </c>
       <c r="B252" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B253" t="s">
         <v>470</v>
@@ -8903,20 +8909,20 @@
         <v>471</v>
       </c>
       <c r="B254" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B255" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B256" t="s">
         <v>474</v>
@@ -8927,12 +8933,12 @@
         <v>475</v>
       </c>
       <c r="B257" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B258" t="s">
         <v>477</v>
@@ -9007,12 +9013,12 @@
         <v>494</v>
       </c>
       <c r="B267" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B268" t="s">
         <v>496</v>
@@ -9031,12 +9037,12 @@
         <v>499</v>
       </c>
       <c r="B270" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B271" t="s">
         <v>501</v>
@@ -9047,12 +9053,12 @@
         <v>502</v>
       </c>
       <c r="B272" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B273" t="s">
         <v>504</v>
@@ -9079,12 +9085,12 @@
         <v>509</v>
       </c>
       <c r="B276" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B277" t="s">
         <v>511</v>
@@ -9135,12 +9141,12 @@
         <v>522</v>
       </c>
       <c r="B283" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B284" t="s">
         <v>524</v>
@@ -9167,12 +9173,12 @@
         <v>529</v>
       </c>
       <c r="B287" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B288" t="s">
         <v>531</v>
@@ -9199,12 +9205,12 @@
         <v>536</v>
       </c>
       <c r="B291" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B292" t="s">
         <v>538</v>
@@ -9239,20 +9245,20 @@
         <v>545</v>
       </c>
       <c r="B296" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B297" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B298" t="s">
         <v>548</v>
@@ -9431,20 +9437,20 @@
         <v>591</v>
       </c>
       <c r="B320" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B321" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B322" t="s">
         <v>594</v>
@@ -9487,12 +9493,12 @@
         <v>603</v>
       </c>
       <c r="B327" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B328" t="s">
         <v>605</v>
@@ -9535,12 +9541,12 @@
         <v>614</v>
       </c>
       <c r="B333" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B334" t="s">
         <v>616</v>
@@ -9607,12 +9613,12 @@
         <v>631</v>
       </c>
       <c r="B342" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B343" t="s">
         <v>633</v>
@@ -9767,12 +9773,12 @@
         <v>670</v>
       </c>
       <c r="B362" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B363" t="s">
         <v>672</v>
@@ -9799,12 +9805,12 @@
         <v>677</v>
       </c>
       <c r="B366" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B367" t="s">
         <v>679</v>
@@ -10343,12 +10349,12 @@
         <v>812</v>
       </c>
       <c r="B434" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B435" t="s">
         <v>814</v>
@@ -10383,12 +10389,12 @@
         <v>821</v>
       </c>
       <c r="B439" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B440" t="s">
         <v>823</v>
@@ -10447,12 +10453,12 @@
         <v>836</v>
       </c>
       <c r="B447" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="448" spans="1:2">
       <c r="A448" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B448" t="s">
         <v>838</v>
@@ -10479,12 +10485,12 @@
         <v>843</v>
       </c>
       <c r="B451" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B452" t="s">
         <v>845</v>
@@ -10527,12 +10533,12 @@
         <v>854</v>
       </c>
       <c r="B457" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B458" t="s">
         <v>856</v>
@@ -10615,20 +10621,20 @@
         <v>875</v>
       </c>
       <c r="B468" t="s">
-        <v>590</v>
+        <v>876</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B469" t="s">
-        <v>876</v>
+        <v>592</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B470" t="s">
         <v>878</v>
@@ -10671,15 +10677,15 @@
         <v>887</v>
       </c>
       <c r="B475" t="s">
-        <v>590</v>
+        <v>888</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B476" t="s">
-        <v>889</v>
+        <v>592</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -10687,12 +10693,12 @@
         <v>890</v>
       </c>
       <c r="B477" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B478" t="s">
         <v>892</v>
@@ -10743,12 +10749,12 @@
         <v>903</v>
       </c>
       <c r="B484" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B485" t="s">
         <v>905</v>
@@ -10767,12 +10773,12 @@
         <v>908</v>
       </c>
       <c r="B487" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B488" t="s">
         <v>910</v>
@@ -10783,12 +10789,12 @@
         <v>911</v>
       </c>
       <c r="B489" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B490" t="s">
         <v>913</v>
@@ -10967,12 +10973,12 @@
         <v>956</v>
       </c>
       <c r="B512" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B513" t="s">
         <v>958</v>
@@ -10991,12 +10997,12 @@
         <v>961</v>
       </c>
       <c r="B515" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B516" t="s">
         <v>963</v>
@@ -11143,12 +11149,12 @@
         <v>998</v>
       </c>
       <c r="B534" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B535" t="s">
         <v>1000</v>
@@ -11295,76 +11301,76 @@
         <v>1035</v>
       </c>
       <c r="B553" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B554" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B555" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B556" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B557" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B558" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B559" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B560" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B561" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B562" t="s">
         <v>1045</v>
@@ -11391,20 +11397,20 @@
         <v>1050</v>
       </c>
       <c r="B565" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="566" spans="1:2">
       <c r="A566" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B566" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B567" t="s">
         <v>1053</v>
@@ -11479,12 +11485,12 @@
         <v>1070</v>
       </c>
       <c r="B576" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B577" t="s">
         <v>1072</v>
@@ -11503,20 +11509,20 @@
         <v>1075</v>
       </c>
       <c r="B579" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B580" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B581" t="s">
         <v>1078</v>
@@ -11527,12 +11533,12 @@
         <v>1079</v>
       </c>
       <c r="B582" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B583" t="s">
         <v>1081</v>
@@ -11559,12 +11565,12 @@
         <v>1086</v>
       </c>
       <c r="B586" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B587" t="s">
         <v>1088</v>
@@ -11583,12 +11589,12 @@
         <v>1091</v>
       </c>
       <c r="B589" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B590" t="s">
         <v>1093</v>
@@ -11631,12 +11637,12 @@
         <v>1102</v>
       </c>
       <c r="B595" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B596" t="s">
         <v>1104</v>
@@ -11671,12 +11677,12 @@
         <v>1111</v>
       </c>
       <c r="B600" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B601" t="s">
         <v>1113</v>
@@ -11751,12 +11757,12 @@
         <v>1130</v>
       </c>
       <c r="B610" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B611" t="s">
         <v>1132</v>
@@ -11799,12 +11805,12 @@
         <v>1141</v>
       </c>
       <c r="B616" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B617" t="s">
         <v>1143</v>
@@ -11815,12 +11821,12 @@
         <v>1144</v>
       </c>
       <c r="B618" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B619" t="s">
         <v>1146</v>
@@ -11863,12 +11869,12 @@
         <v>1155</v>
       </c>
       <c r="B624" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B625" t="s">
         <v>1157</v>
@@ -11903,12 +11909,12 @@
         <v>1164</v>
       </c>
       <c r="B629" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B630" t="s">
         <v>1166</v>
@@ -11975,20 +11981,20 @@
         <v>1181</v>
       </c>
       <c r="B638" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B639" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B640" t="s">
         <v>1184</v>
@@ -12007,12 +12013,12 @@
         <v>1187</v>
       </c>
       <c r="B642" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B643" t="s">
         <v>1189</v>
@@ -12023,20 +12029,20 @@
         <v>1190</v>
       </c>
       <c r="B644" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B645" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B646" t="s">
         <v>1193</v>
@@ -12079,12 +12085,12 @@
         <v>1202</v>
       </c>
       <c r="B651" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B652" t="s">
         <v>1204</v>
@@ -12119,12 +12125,12 @@
         <v>1211</v>
       </c>
       <c r="B656" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B657" t="s">
         <v>1213</v>
@@ -12135,12 +12141,12 @@
         <v>1214</v>
       </c>
       <c r="B658" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B659" t="s">
         <v>1216</v>
@@ -12383,20 +12389,20 @@
         <v>1275</v>
       </c>
       <c r="B689" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B690" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B691" t="s">
         <v>1278</v>
@@ -12455,12 +12461,12 @@
         <v>1291</v>
       </c>
       <c r="B698" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="699" spans="1:2">
       <c r="A699" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B699" t="s">
         <v>1293</v>
@@ -12527,12 +12533,12 @@
         <v>1308</v>
       </c>
       <c r="B707" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B708" t="s">
         <v>1310</v>
@@ -12543,20 +12549,20 @@
         <v>1311</v>
       </c>
       <c r="B709" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B710" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B711" t="s">
         <v>1314</v>
@@ -12599,12 +12605,12 @@
         <v>1323</v>
       </c>
       <c r="B716" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B717" t="s">
         <v>1325</v>
@@ -12615,12 +12621,12 @@
         <v>1326</v>
       </c>
       <c r="B718" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B719" t="s">
         <v>1328</v>
@@ -12655,12 +12661,12 @@
         <v>1335</v>
       </c>
       <c r="B723" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B724" t="s">
         <v>1337</v>
@@ -12679,12 +12685,12 @@
         <v>1340</v>
       </c>
       <c r="B726" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B727" t="s">
         <v>1342</v>
@@ -12695,20 +12701,20 @@
         <v>1343</v>
       </c>
       <c r="B728" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B729" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B730" t="s">
         <v>1346</v>
@@ -12727,12 +12733,12 @@
         <v>1349</v>
       </c>
       <c r="B732" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B733" t="s">
         <v>1351</v>
@@ -12743,20 +12749,20 @@
         <v>1352</v>
       </c>
       <c r="B734" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B735" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B736" t="s">
         <v>1355</v>
@@ -12823,12 +12829,12 @@
         <v>1370</v>
       </c>
       <c r="B744" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B745" t="s">
         <v>1372</v>
@@ -12855,12 +12861,12 @@
         <v>1377</v>
       </c>
       <c r="B748" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B749" t="s">
         <v>1379</v>
@@ -12975,20 +12981,20 @@
         <v>1406</v>
       </c>
       <c r="B763" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B764" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B765" t="s">
         <v>1409</v>
@@ -13031,12 +13037,12 @@
         <v>1418</v>
       </c>
       <c r="B770" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B771" t="s">
         <v>1420</v>
@@ -13079,12 +13085,12 @@
         <v>1429</v>
       </c>
       <c r="B776" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B777" t="s">
         <v>1431</v>
@@ -13119,12 +13125,12 @@
         <v>1438</v>
       </c>
       <c r="B781" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B782" t="s">
         <v>1440</v>
@@ -13191,28 +13197,28 @@
         <v>1455</v>
       </c>
       <c r="B790" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B791" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B792" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B793" t="s">
         <v>1459</v>
@@ -13263,44 +13269,44 @@
         <v>1470</v>
       </c>
       <c r="B799" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B800" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B801" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B802" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B803" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B804" t="s">
         <v>1476</v>
@@ -13319,15 +13325,15 @@
         <v>1479</v>
       </c>
       <c r="B806" t="s">
-        <v>134</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B807" t="s">
-        <v>1481</v>
+        <v>136</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -13391,20 +13397,20 @@
         <v>1496</v>
       </c>
       <c r="B815" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B816" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B817" t="s">
         <v>1499</v>
@@ -13455,20 +13461,20 @@
         <v>1510</v>
       </c>
       <c r="B823" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B824" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B825" t="s">
         <v>1513</v>
@@ -13487,20 +13493,20 @@
         <v>1516</v>
       </c>
       <c r="B827" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B828" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B829" t="s">
         <v>1519</v>
@@ -13535,12 +13541,12 @@
         <v>1526</v>
       </c>
       <c r="B833" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B834" t="s">
         <v>1528</v>
@@ -13591,28 +13597,28 @@
         <v>1539</v>
       </c>
       <c r="B840" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B841" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B842" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B843" t="s">
         <v>1543</v>
@@ -13671,12 +13677,12 @@
         <v>1556</v>
       </c>
       <c r="B850" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B851" t="s">
         <v>1558</v>
@@ -13695,84 +13701,84 @@
         <v>1561</v>
       </c>
       <c r="B853" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B854" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B855" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B856" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B857" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B858" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B859" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B860" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B861" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B862" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B863" t="s">
         <v>1572</v>
@@ -13839,12 +13845,12 @@
         <v>1587</v>
       </c>
       <c r="B871" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B872" t="s">
         <v>1589</v>
@@ -13983,20 +13989,20 @@
         <v>1622</v>
       </c>
       <c r="B889" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B890" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B891" t="s">
         <v>1625</v>
@@ -14047,12 +14053,12 @@
         <v>1636</v>
       </c>
       <c r="B897" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B898" t="s">
         <v>1638</v>
@@ -14063,12 +14069,12 @@
         <v>1639</v>
       </c>
       <c r="B899" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B900" t="s">
         <v>1641</v>
@@ -14079,12 +14085,12 @@
         <v>1642</v>
       </c>
       <c r="B901" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B902" t="s">
         <v>1644</v>
@@ -14207,12 +14213,12 @@
         <v>1673</v>
       </c>
       <c r="B917" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B918" t="s">
         <v>1675</v>
@@ -14279,20 +14285,20 @@
         <v>1690</v>
       </c>
       <c r="B926" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B927" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B928" t="s">
         <v>1693</v>
@@ -14343,12 +14349,12 @@
         <v>1704</v>
       </c>
       <c r="B934" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B935" t="s">
         <v>1706</v>
@@ -14407,12 +14413,12 @@
         <v>1719</v>
       </c>
       <c r="B942" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B943" t="s">
         <v>1721</v>
@@ -14423,12 +14429,12 @@
         <v>1722</v>
       </c>
       <c r="B944" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B945" t="s">
         <v>1724</v>
@@ -14463,12 +14469,12 @@
         <v>1731</v>
       </c>
       <c r="B949" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B950" t="s">
         <v>1733</v>
@@ -14503,12 +14509,12 @@
         <v>1740</v>
       </c>
       <c r="B954" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B955" t="s">
         <v>1742</v>
@@ -14567,12 +14573,12 @@
         <v>1755</v>
       </c>
       <c r="B962" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="B963" t="s">
         <v>1757</v>
@@ -14615,20 +14621,20 @@
         <v>1766</v>
       </c>
       <c r="B968" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B969" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B970" t="s">
         <v>1769</v>
@@ -14687,12 +14693,12 @@
         <v>1782</v>
       </c>
       <c r="B977" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B978" t="s">
         <v>1784</v>
@@ -14807,12 +14813,12 @@
         <v>1811</v>
       </c>
       <c r="B992" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B993" t="s">
         <v>1813</v>
@@ -14839,20 +14845,20 @@
         <v>1818</v>
       </c>
       <c r="B996" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B997" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="B998" t="s">
         <v>1821</v>
@@ -14871,12 +14877,12 @@
         <v>1824</v>
       </c>
       <c r="B1000" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B1001" t="s">
         <v>1826</v>
@@ -14911,12 +14917,12 @@
         <v>1833</v>
       </c>
       <c r="B1005" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1006" t="s">
         <v>1835</v>
@@ -14935,12 +14941,12 @@
         <v>1838</v>
       </c>
       <c r="B1008" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B1009" t="s">
         <v>1840</v>
@@ -14991,20 +14997,20 @@
         <v>1851</v>
       </c>
       <c r="B1015" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B1016" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B1017" t="s">
         <v>1854</v>
@@ -15039,12 +15045,12 @@
         <v>1861</v>
       </c>
       <c r="B1021" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1022" t="s">
         <v>1863</v>
@@ -15103,12 +15109,12 @@
         <v>1876</v>
       </c>
       <c r="B1029" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="B1030" t="s">
         <v>1878</v>
@@ -15183,12 +15189,12 @@
         <v>1895</v>
       </c>
       <c r="B1039" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="B1040" t="s">
         <v>1897</v>
@@ -15199,44 +15205,44 @@
         <v>1898</v>
       </c>
       <c r="B1041" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="B1042" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B1043" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="B1044" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B1045" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B1046" t="s">
         <v>1904</v>
@@ -15263,12 +15269,12 @@
         <v>1909</v>
       </c>
       <c r="B1049" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B1050" t="s">
         <v>1911</v>
@@ -15295,12 +15301,12 @@
         <v>1916</v>
       </c>
       <c r="B1053" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="B1054" t="s">
         <v>1918</v>
@@ -15335,12 +15341,12 @@
         <v>1925</v>
       </c>
       <c r="B1058" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B1059" t="s">
         <v>1927</v>
@@ -15351,12 +15357,12 @@
         <v>1928</v>
       </c>
       <c r="B1060" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="B1061" t="s">
         <v>1930</v>
@@ -15447,12 +15453,12 @@
         <v>1951</v>
       </c>
       <c r="B1072" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="B1073" t="s">
         <v>1953</v>
@@ -15583,12 +15589,12 @@
         <v>1984</v>
       </c>
       <c r="B1089" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="B1090" t="s">
         <v>1986</v>
@@ -15607,12 +15613,12 @@
         <v>1989</v>
       </c>
       <c r="B1092" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="B1093" t="s">
         <v>1991</v>
@@ -15711,12 +15717,12 @@
         <v>2014</v>
       </c>
       <c r="B1105" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B1106" t="s">
         <v>2016</v>
@@ -15791,44 +15797,44 @@
         <v>2033</v>
       </c>
       <c r="B1115" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="B1116" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="B1117" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="B1118" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B1119" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="B1120" t="s">
         <v>2039</v>
@@ -15855,12 +15861,12 @@
         <v>2044</v>
       </c>
       <c r="B1123" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="B1124" t="s">
         <v>2046</v>
@@ -15871,12 +15877,12 @@
         <v>2047</v>
       </c>
       <c r="B1125" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="B1126" t="s">
         <v>2049</v>
@@ -16063,12 +16069,12 @@
         <v>2094</v>
       </c>
       <c r="B1149" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="B1150" t="s">
         <v>2096</v>
@@ -16095,20 +16101,20 @@
         <v>2101</v>
       </c>
       <c r="B1153" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="B1154" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="B1155" t="s">
         <v>2104</v>
@@ -16231,12 +16237,12 @@
         <v>2133</v>
       </c>
       <c r="B1170" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="B1171" t="s">
         <v>2135</v>
@@ -16263,12 +16269,12 @@
         <v>2140</v>
       </c>
       <c r="B1174" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="B1175" t="s">
         <v>2142</v>
@@ -16295,12 +16301,12 @@
         <v>2147</v>
       </c>
       <c r="B1178" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="B1179" t="s">
         <v>2149</v>
@@ -16311,20 +16317,20 @@
         <v>2150</v>
       </c>
       <c r="B1180" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="B1181" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="B1182" t="s">
         <v>2153</v>
@@ -16335,12 +16341,12 @@
         <v>2154</v>
       </c>
       <c r="B1183" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="B1184" t="s">
         <v>2156</v>
@@ -16375,12 +16381,12 @@
         <v>2163</v>
       </c>
       <c r="B1188" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="B1189" t="s">
         <v>2165</v>
@@ -16394,8 +16400,16 @@
         <v>2167</v>
       </c>
     </row>
+    <row r="1191" spans="1:2">
+      <c r="A1191" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>2169</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1190"/>
+  <autoFilter ref="A1:B1191"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2172">
   <si>
     <t>en</t>
   </si>
@@ -1439,6 +1439,12 @@
   </si>
   <si>
     <t>Diablo</t>
+  </si>
+  <si>
+    <t>Die of Death</t>
+  </si>
+  <si>
+    <t>Матрица смерти</t>
   </si>
   <si>
     <t>Digimon</t>
@@ -6873,7 +6879,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1191"/>
+  <dimension ref="A1:B1192"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -8925,12 +8931,12 @@
         <v>474</v>
       </c>
       <c r="B256" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B257" t="s">
         <v>476</v>
@@ -8941,12 +8947,12 @@
         <v>477</v>
       </c>
       <c r="B258" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B259" t="s">
         <v>479</v>
@@ -9021,12 +9027,12 @@
         <v>496</v>
       </c>
       <c r="B268" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B269" t="s">
         <v>498</v>
@@ -9045,12 +9051,12 @@
         <v>501</v>
       </c>
       <c r="B271" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B272" t="s">
         <v>503</v>
@@ -9061,12 +9067,12 @@
         <v>504</v>
       </c>
       <c r="B273" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B274" t="s">
         <v>506</v>
@@ -9093,12 +9099,12 @@
         <v>511</v>
       </c>
       <c r="B277" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B278" t="s">
         <v>513</v>
@@ -9149,12 +9155,12 @@
         <v>524</v>
       </c>
       <c r="B284" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B285" t="s">
         <v>526</v>
@@ -9181,12 +9187,12 @@
         <v>531</v>
       </c>
       <c r="B288" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B289" t="s">
         <v>533</v>
@@ -9213,12 +9219,12 @@
         <v>538</v>
       </c>
       <c r="B292" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B293" t="s">
         <v>540</v>
@@ -9253,20 +9259,20 @@
         <v>547</v>
       </c>
       <c r="B297" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B298" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B299" t="s">
         <v>550</v>
@@ -9445,20 +9451,20 @@
         <v>593</v>
       </c>
       <c r="B321" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B322" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B323" t="s">
         <v>596</v>
@@ -9501,12 +9507,12 @@
         <v>605</v>
       </c>
       <c r="B328" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B329" t="s">
         <v>607</v>
@@ -9549,12 +9555,12 @@
         <v>616</v>
       </c>
       <c r="B334" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B335" t="s">
         <v>618</v>
@@ -9621,12 +9627,12 @@
         <v>633</v>
       </c>
       <c r="B343" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B344" t="s">
         <v>635</v>
@@ -9781,12 +9787,12 @@
         <v>672</v>
       </c>
       <c r="B363" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B364" t="s">
         <v>674</v>
@@ -9813,12 +9819,12 @@
         <v>679</v>
       </c>
       <c r="B367" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B368" t="s">
         <v>681</v>
@@ -10357,12 +10363,12 @@
         <v>814</v>
       </c>
       <c r="B435" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B436" t="s">
         <v>816</v>
@@ -10397,12 +10403,12 @@
         <v>823</v>
       </c>
       <c r="B440" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B441" t="s">
         <v>825</v>
@@ -10461,12 +10467,12 @@
         <v>838</v>
       </c>
       <c r="B448" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B449" t="s">
         <v>840</v>
@@ -10493,12 +10499,12 @@
         <v>845</v>
       </c>
       <c r="B452" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="453" spans="1:2">
       <c r="A453" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B453" t="s">
         <v>847</v>
@@ -10541,12 +10547,12 @@
         <v>856</v>
       </c>
       <c r="B458" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B459" t="s">
         <v>858</v>
@@ -10629,20 +10635,20 @@
         <v>877</v>
       </c>
       <c r="B469" t="s">
-        <v>592</v>
+        <v>878</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B470" t="s">
-        <v>878</v>
+        <v>594</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B471" t="s">
         <v>880</v>
@@ -10685,15 +10691,15 @@
         <v>889</v>
       </c>
       <c r="B476" t="s">
-        <v>592</v>
+        <v>890</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B477" t="s">
-        <v>891</v>
+        <v>594</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -10701,12 +10707,12 @@
         <v>892</v>
       </c>
       <c r="B478" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B479" t="s">
         <v>894</v>
@@ -10757,12 +10763,12 @@
         <v>905</v>
       </c>
       <c r="B485" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B486" t="s">
         <v>907</v>
@@ -10781,12 +10787,12 @@
         <v>910</v>
       </c>
       <c r="B488" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B489" t="s">
         <v>912</v>
@@ -10797,12 +10803,12 @@
         <v>913</v>
       </c>
       <c r="B490" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B491" t="s">
         <v>915</v>
@@ -10981,12 +10987,12 @@
         <v>958</v>
       </c>
       <c r="B513" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="A514" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B514" t="s">
         <v>960</v>
@@ -11005,12 +11011,12 @@
         <v>963</v>
       </c>
       <c r="B516" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B517" t="s">
         <v>965</v>
@@ -11157,12 +11163,12 @@
         <v>1000</v>
       </c>
       <c r="B535" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B536" t="s">
         <v>1002</v>
@@ -11309,76 +11315,76 @@
         <v>1037</v>
       </c>
       <c r="B554" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B555" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B556" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B557" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B558" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B559" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B560" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B561" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B562" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B563" t="s">
         <v>1047</v>
@@ -11405,20 +11411,20 @@
         <v>1052</v>
       </c>
       <c r="B566" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B567" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B568" t="s">
         <v>1055</v>
@@ -11493,12 +11499,12 @@
         <v>1072</v>
       </c>
       <c r="B577" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B578" t="s">
         <v>1074</v>
@@ -11517,20 +11523,20 @@
         <v>1077</v>
       </c>
       <c r="B580" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B581" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B582" t="s">
         <v>1080</v>
@@ -11541,12 +11547,12 @@
         <v>1081</v>
       </c>
       <c r="B583" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B584" t="s">
         <v>1083</v>
@@ -11573,12 +11579,12 @@
         <v>1088</v>
       </c>
       <c r="B587" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B588" t="s">
         <v>1090</v>
@@ -11597,12 +11603,12 @@
         <v>1093</v>
       </c>
       <c r="B590" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B591" t="s">
         <v>1095</v>
@@ -11645,12 +11651,12 @@
         <v>1104</v>
       </c>
       <c r="B596" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B597" t="s">
         <v>1106</v>
@@ -11685,12 +11691,12 @@
         <v>1113</v>
       </c>
       <c r="B601" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B602" t="s">
         <v>1115</v>
@@ -11765,12 +11771,12 @@
         <v>1132</v>
       </c>
       <c r="B611" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B612" t="s">
         <v>1134</v>
@@ -11813,12 +11819,12 @@
         <v>1143</v>
       </c>
       <c r="B617" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B618" t="s">
         <v>1145</v>
@@ -11829,12 +11835,12 @@
         <v>1146</v>
       </c>
       <c r="B619" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B620" t="s">
         <v>1148</v>
@@ -11877,12 +11883,12 @@
         <v>1157</v>
       </c>
       <c r="B625" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B626" t="s">
         <v>1159</v>
@@ -11917,12 +11923,12 @@
         <v>1166</v>
       </c>
       <c r="B630" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B631" t="s">
         <v>1168</v>
@@ -11989,20 +11995,20 @@
         <v>1183</v>
       </c>
       <c r="B639" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B640" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B641" t="s">
         <v>1186</v>
@@ -12021,12 +12027,12 @@
         <v>1189</v>
       </c>
       <c r="B643" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B644" t="s">
         <v>1191</v>
@@ -12037,20 +12043,20 @@
         <v>1192</v>
       </c>
       <c r="B645" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B646" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B647" t="s">
         <v>1195</v>
@@ -12093,12 +12099,12 @@
         <v>1204</v>
       </c>
       <c r="B652" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B653" t="s">
         <v>1206</v>
@@ -12133,12 +12139,12 @@
         <v>1213</v>
       </c>
       <c r="B657" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B658" t="s">
         <v>1215</v>
@@ -12149,12 +12155,12 @@
         <v>1216</v>
       </c>
       <c r="B659" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B660" t="s">
         <v>1218</v>
@@ -12397,20 +12403,20 @@
         <v>1277</v>
       </c>
       <c r="B690" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B691" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B692" t="s">
         <v>1280</v>
@@ -12469,12 +12475,12 @@
         <v>1293</v>
       </c>
       <c r="B699" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="700" spans="1:2">
       <c r="A700" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B700" t="s">
         <v>1295</v>
@@ -12541,12 +12547,12 @@
         <v>1310</v>
       </c>
       <c r="B708" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B709" t="s">
         <v>1312</v>
@@ -12557,20 +12563,20 @@
         <v>1313</v>
       </c>
       <c r="B710" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B711" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B712" t="s">
         <v>1316</v>
@@ -12613,12 +12619,12 @@
         <v>1325</v>
       </c>
       <c r="B717" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B718" t="s">
         <v>1327</v>
@@ -12629,12 +12635,12 @@
         <v>1328</v>
       </c>
       <c r="B719" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B720" t="s">
         <v>1330</v>
@@ -12669,12 +12675,12 @@
         <v>1337</v>
       </c>
       <c r="B724" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B725" t="s">
         <v>1339</v>
@@ -12693,12 +12699,12 @@
         <v>1342</v>
       </c>
       <c r="B727" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B728" t="s">
         <v>1344</v>
@@ -12709,20 +12715,20 @@
         <v>1345</v>
       </c>
       <c r="B729" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B730" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B731" t="s">
         <v>1348</v>
@@ -12741,12 +12747,12 @@
         <v>1351</v>
       </c>
       <c r="B733" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B734" t="s">
         <v>1353</v>
@@ -12757,20 +12763,20 @@
         <v>1354</v>
       </c>
       <c r="B735" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B736" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B737" t="s">
         <v>1357</v>
@@ -12837,12 +12843,12 @@
         <v>1372</v>
       </c>
       <c r="B745" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B746" t="s">
         <v>1374</v>
@@ -12869,12 +12875,12 @@
         <v>1379</v>
       </c>
       <c r="B749" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B750" t="s">
         <v>1381</v>
@@ -12989,20 +12995,20 @@
         <v>1408</v>
       </c>
       <c r="B764" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B765" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B766" t="s">
         <v>1411</v>
@@ -13045,12 +13051,12 @@
         <v>1420</v>
       </c>
       <c r="B771" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B772" t="s">
         <v>1422</v>
@@ -13093,12 +13099,12 @@
         <v>1431</v>
       </c>
       <c r="B777" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B778" t="s">
         <v>1433</v>
@@ -13133,12 +13139,12 @@
         <v>1440</v>
       </c>
       <c r="B782" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B783" t="s">
         <v>1442</v>
@@ -13205,28 +13211,28 @@
         <v>1457</v>
       </c>
       <c r="B791" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B792" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B793" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B794" t="s">
         <v>1461</v>
@@ -13277,44 +13283,44 @@
         <v>1472</v>
       </c>
       <c r="B800" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B801" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B802" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B803" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B804" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B805" t="s">
         <v>1478</v>
@@ -13333,15 +13339,15 @@
         <v>1481</v>
       </c>
       <c r="B807" t="s">
-        <v>136</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B808" t="s">
-        <v>1483</v>
+        <v>136</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -13405,20 +13411,20 @@
         <v>1498</v>
       </c>
       <c r="B816" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B817" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B818" t="s">
         <v>1501</v>
@@ -13469,20 +13475,20 @@
         <v>1512</v>
       </c>
       <c r="B824" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B825" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B826" t="s">
         <v>1515</v>
@@ -13501,20 +13507,20 @@
         <v>1518</v>
       </c>
       <c r="B828" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B829" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B830" t="s">
         <v>1521</v>
@@ -13549,12 +13555,12 @@
         <v>1528</v>
       </c>
       <c r="B834" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B835" t="s">
         <v>1530</v>
@@ -13605,28 +13611,28 @@
         <v>1541</v>
       </c>
       <c r="B841" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B842" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B843" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B844" t="s">
         <v>1545</v>
@@ -13685,12 +13691,12 @@
         <v>1558</v>
       </c>
       <c r="B851" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B852" t="s">
         <v>1560</v>
@@ -13709,84 +13715,84 @@
         <v>1563</v>
       </c>
       <c r="B854" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B855" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B856" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B857" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B858" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B859" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B860" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B861" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B862" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B863" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B864" t="s">
         <v>1574</v>
@@ -13853,12 +13859,12 @@
         <v>1589</v>
       </c>
       <c r="B872" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B873" t="s">
         <v>1591</v>
@@ -13997,20 +14003,20 @@
         <v>1624</v>
       </c>
       <c r="B890" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B891" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B892" t="s">
         <v>1627</v>
@@ -14061,12 +14067,12 @@
         <v>1638</v>
       </c>
       <c r="B898" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B899" t="s">
         <v>1640</v>
@@ -14077,12 +14083,12 @@
         <v>1641</v>
       </c>
       <c r="B900" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B901" t="s">
         <v>1643</v>
@@ -14093,12 +14099,12 @@
         <v>1644</v>
       </c>
       <c r="B902" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B903" t="s">
         <v>1646</v>
@@ -14221,12 +14227,12 @@
         <v>1675</v>
       </c>
       <c r="B918" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B919" t="s">
         <v>1677</v>
@@ -14293,20 +14299,20 @@
         <v>1692</v>
       </c>
       <c r="B927" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B928" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B929" t="s">
         <v>1695</v>
@@ -14357,12 +14363,12 @@
         <v>1706</v>
       </c>
       <c r="B935" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B936" t="s">
         <v>1708</v>
@@ -14421,12 +14427,12 @@
         <v>1721</v>
       </c>
       <c r="B943" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B944" t="s">
         <v>1723</v>
@@ -14437,12 +14443,12 @@
         <v>1724</v>
       </c>
       <c r="B945" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B946" t="s">
         <v>1726</v>
@@ -14477,12 +14483,12 @@
         <v>1733</v>
       </c>
       <c r="B950" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B951" t="s">
         <v>1735</v>
@@ -14517,12 +14523,12 @@
         <v>1742</v>
       </c>
       <c r="B955" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B956" t="s">
         <v>1744</v>
@@ -14581,12 +14587,12 @@
         <v>1757</v>
       </c>
       <c r="B963" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B964" t="s">
         <v>1759</v>
@@ -14629,20 +14635,20 @@
         <v>1768</v>
       </c>
       <c r="B969" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B970" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B971" t="s">
         <v>1771</v>
@@ -14701,12 +14707,12 @@
         <v>1784</v>
       </c>
       <c r="B978" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B979" t="s">
         <v>1786</v>
@@ -14821,12 +14827,12 @@
         <v>1813</v>
       </c>
       <c r="B993" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B994" t="s">
         <v>1815</v>
@@ -14853,20 +14859,20 @@
         <v>1820</v>
       </c>
       <c r="B997" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B998" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B999" t="s">
         <v>1823</v>
@@ -14885,12 +14891,12 @@
         <v>1826</v>
       </c>
       <c r="B1001" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="B1002" t="s">
         <v>1828</v>
@@ -14925,12 +14931,12 @@
         <v>1835</v>
       </c>
       <c r="B1006" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1007" t="s">
         <v>1837</v>
@@ -14949,12 +14955,12 @@
         <v>1840</v>
       </c>
       <c r="B1009" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B1010" t="s">
         <v>1842</v>
@@ -15005,20 +15011,20 @@
         <v>1853</v>
       </c>
       <c r="B1016" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1017" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="B1018" t="s">
         <v>1856</v>
@@ -15053,12 +15059,12 @@
         <v>1863</v>
       </c>
       <c r="B1022" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B1023" t="s">
         <v>1865</v>
@@ -15117,12 +15123,12 @@
         <v>1878</v>
       </c>
       <c r="B1030" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B1031" t="s">
         <v>1880</v>
@@ -15197,12 +15203,12 @@
         <v>1897</v>
       </c>
       <c r="B1040" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B1041" t="s">
         <v>1899</v>
@@ -15213,44 +15219,44 @@
         <v>1900</v>
       </c>
       <c r="B1042" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="B1043" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B1044" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B1045" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B1046" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="B1047" t="s">
         <v>1906</v>
@@ -15277,12 +15283,12 @@
         <v>1911</v>
       </c>
       <c r="B1050" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="B1051" t="s">
         <v>1913</v>
@@ -15309,12 +15315,12 @@
         <v>1918</v>
       </c>
       <c r="B1054" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="B1055" t="s">
         <v>1920</v>
@@ -15349,12 +15355,12 @@
         <v>1927</v>
       </c>
       <c r="B1059" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="B1060" t="s">
         <v>1929</v>
@@ -15365,12 +15371,12 @@
         <v>1930</v>
       </c>
       <c r="B1061" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="B1062" t="s">
         <v>1932</v>
@@ -15461,12 +15467,12 @@
         <v>1953</v>
       </c>
       <c r="B1073" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="B1074" t="s">
         <v>1955</v>
@@ -15597,12 +15603,12 @@
         <v>1986</v>
       </c>
       <c r="B1090" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="B1091" t="s">
         <v>1988</v>
@@ -15621,12 +15627,12 @@
         <v>1991</v>
       </c>
       <c r="B1093" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B1094" t="s">
         <v>1993</v>
@@ -15725,12 +15731,12 @@
         <v>2016</v>
       </c>
       <c r="B1106" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B1107" t="s">
         <v>2018</v>
@@ -15805,44 +15811,44 @@
         <v>2035</v>
       </c>
       <c r="B1116" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="B1117" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B1118" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="B1119" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B1120" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="B1121" t="s">
         <v>2041</v>
@@ -15869,12 +15875,12 @@
         <v>2046</v>
       </c>
       <c r="B1124" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="B1125" t="s">
         <v>2048</v>
@@ -15885,12 +15891,12 @@
         <v>2049</v>
       </c>
       <c r="B1126" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="B1127" t="s">
         <v>2051</v>
@@ -16077,12 +16083,12 @@
         <v>2096</v>
       </c>
       <c r="B1150" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="B1151" t="s">
         <v>2098</v>
@@ -16109,20 +16115,20 @@
         <v>2103</v>
       </c>
       <c r="B1154" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="B1155" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="B1156" t="s">
         <v>2106</v>
@@ -16245,12 +16251,12 @@
         <v>2135</v>
       </c>
       <c r="B1171" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="B1172" t="s">
         <v>2137</v>
@@ -16277,12 +16283,12 @@
         <v>2142</v>
       </c>
       <c r="B1175" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="B1176" t="s">
         <v>2144</v>
@@ -16309,12 +16315,12 @@
         <v>2149</v>
       </c>
       <c r="B1179" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="B1180" t="s">
         <v>2151</v>
@@ -16325,20 +16331,20 @@
         <v>2152</v>
       </c>
       <c r="B1181" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="B1182" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="B1183" t="s">
         <v>2155</v>
@@ -16349,12 +16355,12 @@
         <v>2156</v>
       </c>
       <c r="B1184" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="B1185" t="s">
         <v>2158</v>
@@ -16389,12 +16395,12 @@
         <v>2165</v>
       </c>
       <c r="B1189" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="B1190" t="s">
         <v>2167</v>
@@ -16408,8 +16414,16 @@
         <v>2169</v>
       </c>
     </row>
+    <row r="1192" spans="1:2">
+      <c r="A1192" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>2171</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1191"/>
+  <autoFilter ref="A1:B1192"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ru/headTags.xlsx
+++ b/lang/ru/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1193</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2174">
   <si>
     <t>en</t>
   </si>
@@ -2339,6 +2339,12 @@
   </si>
   <si>
     <t>Шрифт (оранжевый)</t>
+  </si>
+  <si>
+    <t>Font (Pale Oak)</t>
+  </si>
+  <si>
+    <t>Шрифт (Pale Oak)</t>
   </si>
   <si>
     <t>Font (Pink)</t>
@@ -6879,7 +6885,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1192"/>
+  <dimension ref="A1:B1193"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -10371,12 +10377,12 @@
         <v>816</v>
       </c>
       <c r="B436" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B437" t="s">
         <v>818</v>
@@ -10411,12 +10417,12 @@
         <v>825</v>
       </c>
       <c r="B441" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B442" t="s">
         <v>827</v>
@@ -10475,12 +10481,12 @@
         <v>840</v>
       </c>
       <c r="B449" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B450" t="s">
         <v>842</v>
@@ -10507,12 +10513,12 @@
         <v>847</v>
       </c>
       <c r="B453" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B454" t="s">
         <v>849</v>
@@ -10555,12 +10561,12 @@
         <v>858</v>
       </c>
       <c r="B459" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="460" spans="1:2">
       <c r="A460" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B460" t="s">
         <v>860</v>
@@ -10643,20 +10649,20 @@
         <v>879</v>
       </c>
       <c r="B470" t="s">
-        <v>594</v>
+        <v>880</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B471" t="s">
-        <v>880</v>
+        <v>594</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B472" t="s">
         <v>882</v>
@@ -10699,15 +10705,15 @@
         <v>891</v>
       </c>
       <c r="B477" t="s">
-        <v>594</v>
+        <v>892</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B478" t="s">
-        <v>893</v>
+        <v>594</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -10715,12 +10721,12 @@
         <v>894</v>
       </c>
       <c r="B479" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B480" t="s">
         <v>896</v>
@@ -10771,12 +10777,12 @@
         <v>907</v>
       </c>
       <c r="B486" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B487" t="s">
         <v>909</v>
@@ -10795,12 +10801,12 @@
         <v>912</v>
       </c>
       <c r="B489" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B490" t="s">
         <v>914</v>
@@ -10811,12 +10817,12 @@
         <v>915</v>
       </c>
       <c r="B491" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B492" t="s">
         <v>917</v>
@@ -10995,12 +11001,12 @@
         <v>960</v>
       </c>
       <c r="B514" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B515" t="s">
         <v>962</v>
@@ -11019,12 +11025,12 @@
         <v>965</v>
       </c>
       <c r="B517" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B518" t="s">
         <v>967</v>
@@ -11171,12 +11177,12 @@
         <v>1002</v>
       </c>
       <c r="B536" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B537" t="s">
         <v>1004</v>
@@ -11323,76 +11329,76 @@
         <v>1039</v>
       </c>
       <c r="B555" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B556" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B557" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B558" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B559" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B560" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B561" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B562" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B563" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B564" t="s">
         <v>1049</v>
@@ -11419,20 +11425,20 @@
         <v>1054</v>
       </c>
       <c r="B567" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B568" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B569" t="s">
         <v>1057</v>
@@ -11507,12 +11513,12 @@
         <v>1074</v>
       </c>
       <c r="B578" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B579" t="s">
         <v>1076</v>
@@ -11531,20 +11537,20 @@
         <v>1079</v>
       </c>
       <c r="B581" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B582" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B583" t="s">
         <v>1082</v>
@@ -11555,12 +11561,12 @@
         <v>1083</v>
       </c>
       <c r="B584" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B585" t="s">
         <v>1085</v>
@@ -11587,12 +11593,12 @@
         <v>1090</v>
       </c>
       <c r="B588" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B589" t="s">
         <v>1092</v>
@@ -11611,12 +11617,12 @@
         <v>1095</v>
       </c>
       <c r="B591" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B592" t="s">
         <v>1097</v>
@@ -11659,12 +11665,12 @@
         <v>1106</v>
       </c>
       <c r="B597" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B598" t="s">
         <v>1108</v>
@@ -11699,12 +11705,12 @@
         <v>1115</v>
       </c>
       <c r="B602" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B603" t="s">
         <v>1117</v>
@@ -11779,12 +11785,12 @@
         <v>1134</v>
       </c>
       <c r="B612" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B613" t="s">
         <v>1136</v>
@@ -11827,12 +11833,12 @@
         <v>1145</v>
       </c>
       <c r="B618" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B619" t="s">
         <v>1147</v>
@@ -11843,12 +11849,12 @@
         <v>1148</v>
       </c>
       <c r="B620" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B621" t="s">
         <v>1150</v>
@@ -11891,12 +11897,12 @@
         <v>1159</v>
       </c>
       <c r="B626" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B627" t="s">
         <v>1161</v>
@@ -11931,12 +11937,12 @@
         <v>1168</v>
       </c>
       <c r="B631" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B632" t="s">
         <v>1170</v>
@@ -12003,20 +12009,20 @@
         <v>1185</v>
       </c>
       <c r="B640" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B641" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B642" t="s">
         <v>1188</v>
@@ -12035,12 +12041,12 @@
         <v>1191</v>
       </c>
       <c r="B644" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B645" t="s">
         <v>1193</v>
@@ -12051,20 +12057,20 @@
         <v>1194</v>
       </c>
       <c r="B646" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B647" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B648" t="s">
         <v>1197</v>
@@ -12107,12 +12113,12 @@
         <v>1206</v>
       </c>
       <c r="B653" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B654" t="s">
         <v>1208</v>
@@ -12147,12 +12153,12 @@
         <v>1215</v>
       </c>
       <c r="B658" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B659" t="s">
         <v>1217</v>
@@ -12163,12 +12169,12 @@
         <v>1218</v>
       </c>
       <c r="B660" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B661" t="s">
         <v>1220</v>
@@ -12411,20 +12417,20 @@
         <v>1279</v>
       </c>
       <c r="B691" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B692" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B693" t="s">
         <v>1282</v>
@@ -12483,12 +12489,12 @@
         <v>1295</v>
       </c>
       <c r="B700" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B701" t="s">
         <v>1297</v>
@@ -12555,12 +12561,12 @@
         <v>1312</v>
       </c>
       <c r="B709" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B710" t="s">
         <v>1314</v>
@@ -12571,20 +12577,20 @@
         <v>1315</v>
       </c>
       <c r="B711" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B712" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B713" t="s">
         <v>1318</v>
@@ -12627,12 +12633,12 @@
         <v>1327</v>
       </c>
       <c r="B718" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B719" t="s">
         <v>1329</v>
@@ -12643,12 +12649,12 @@
         <v>1330</v>
       </c>
       <c r="B720" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B721" t="s">
         <v>1332</v>
@@ -12683,12 +12689,12 @@
         <v>1339</v>
       </c>
       <c r="B725" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B726" t="s">
         <v>1341</v>
@@ -12707,12 +12713,12 @@
         <v>1344</v>
       </c>
       <c r="B728" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B729" t="s">
         <v>1346</v>
@@ -12723,20 +12729,20 @@
         <v>1347</v>
       </c>
       <c r="B730" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B731" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B732" t="s">
         <v>1350</v>
@@ -12755,12 +12761,12 @@
         <v>1353</v>
       </c>
       <c r="B734" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B735" t="s">
         <v>1355</v>
@@ -12771,20 +12777,20 @@
         <v>1356</v>
       </c>
       <c r="B736" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B737" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B738" t="s">
         <v>1359</v>
@@ -12851,12 +12857,12 @@
         <v>1374</v>
       </c>
       <c r="B746" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B747" t="s">
         <v>1376</v>
@@ -12883,12 +12889,12 @@
         <v>1381</v>
       </c>
       <c r="B750" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B751" t="s">
         <v>1383</v>
@@ -13003,20 +13009,20 @@
         <v>1410</v>
       </c>
       <c r="B765" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B766" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B767" t="s">
         <v>1413</v>
@@ -13059,12 +13065,12 @@
         <v>1422</v>
       </c>
       <c r="B772" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B773" t="s">
         <v>1424</v>
@@ -13107,12 +13113,12 @@
         <v>1433</v>
       </c>
       <c r="B778" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B779" t="s">
         <v>1435</v>
@@ -13147,12 +13153,12 @@
         <v>1442</v>
       </c>
       <c r="B783" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B784" t="s">
         <v>1444</v>
@@ -13219,28 +13225,28 @@
         <v>1459</v>
       </c>
       <c r="B792" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B793" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B794" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B795" t="s">
         <v>1463</v>
@@ -13291,44 +13297,44 @@
         <v>1474</v>
       </c>
       <c r="B801" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B802" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B803" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B804" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B805" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B806" t="s">
         <v>1480</v>
@@ -13347,15 +13353,15 @@
         <v>1483</v>
       </c>
       <c r="B808" t="s">
-        <v>136</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B809" t="s">
-        <v>1485</v>
+        <v>136</v>
       </c>
     </row>
     <row r="810" spans="1:2">
@@ -13419,20 +13425,20 @@
         <v>1500</v>
       </c>
       <c r="B817" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B818" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B819" t="s">
         <v>1503</v>
@@ -13483,20 +13489,20 @@
         <v>1514</v>
       </c>
       <c r="B825" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B826" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B827" t="s">
         <v>1517</v>
@@ -13515,20 +13521,20 @@
         <v>1520</v>
       </c>
       <c r="B829" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B830" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B831" t="s">
         <v>1523</v>
@@ -13563,12 +13569,12 @@
         <v>1530</v>
       </c>
       <c r="B835" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B836" t="s">
         <v>1532</v>
@@ -13619,28 +13625,28 @@
         <v>1543</v>
       </c>
       <c r="B842" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B843" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B844" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B845" t="s">
         <v>1547</v>
@@ -13699,12 +13705,12 @@
         <v>1560</v>
       </c>
       <c r="B852" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B853" t="s">
         <v>1562</v>
@@ -13723,84 +13729,84 @@
         <v>1565</v>
       </c>
       <c r="B855" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B856" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B857" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B858" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B859" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B860" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B861" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B862" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B863" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B864" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B865" t="s">
         <v>1576</v>
@@ -13867,12 +13873,12 @@
         <v>1591</v>
       </c>
       <c r="B873" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B874" t="s">
         <v>1593</v>
@@ -14011,20 +14017,20 @@
         <v>1626</v>
       </c>
       <c r="B891" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B892" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B893" t="s">
         <v>1629</v>
@@ -14075,12 +14081,12 @@
         <v>1640</v>
       </c>
       <c r="B899" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B900" t="s">
         <v>1642</v>
@@ -14091,12 +14097,12 @@
         <v>1643</v>
       </c>
       <c r="B901" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B902" t="s">
         <v>1645</v>
@@ -14107,12 +14113,12 @@
         <v>1646</v>
       </c>
       <c r="B903" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B904" t="s">
         <v>1648</v>
@@ -14235,12 +14241,12 @@
         <v>1677</v>
       </c>
       <c r="B919" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B920" t="s">
         <v>1679</v>
@@ -14307,20 +14313,20 @@
         <v>1694</v>
       </c>
       <c r="B928" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B929" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B930" t="s">
         <v>1697</v>
@@ -14371,12 +14377,12 @@
         <v>1708</v>
       </c>
       <c r="B936" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B937" t="s">
         <v>1710</v>
@@ -14435,12 +14441,12 @@
         <v>1723</v>
       </c>
       <c r="B944" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B945" t="s">
         <v>1725</v>
@@ -14451,12 +14457,12 @@
         <v>1726</v>
       </c>
       <c r="B946" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B947" t="s">
         <v>1728</v>
@@ -14491,12 +14497,12 @@
         <v>1735</v>
       </c>
       <c r="B951" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B952" t="s">
         <v>1737</v>
@@ -14531,12 +14537,12 @@
         <v>1744</v>
       </c>
       <c r="B956" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B957" t="s">
         <v>1746</v>
@@ -14595,12 +14601,12 @@
         <v>1759</v>
       </c>
       <c r="B964" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B965" t="s">
         <v>1761</v>
@@ -14643,20 +14649,20 @@
         <v>1770</v>
       </c>
       <c r="B970" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B971" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B972" t="s">
         <v>1773</v>
@@ -14715,12 +14721,12 @@
         <v>1786</v>
       </c>
       <c r="B979" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B980" t="s">
         <v>1788</v>
@@ -14835,12 +14841,12 @@
         <v>1815</v>
       </c>
       <c r="B994" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B995" t="s">
         <v>1817</v>
@@ -14867,20 +14873,20 @@
         <v>1822</v>
       </c>
       <c r="B998" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B999" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1000" t="s">
         <v>1825</v>
@@ -14899,12 +14905,12 @@
         <v>1828</v>
       </c>
       <c r="B1002" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1003" t="s">
         <v>1830</v>
@@ -14939,12 +14945,12 @@
         <v>1837</v>
       </c>
       <c r="B1007" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B1008" t="s">
         <v>1839</v>
@@ -14963,12 +14969,12 @@
         <v>1842</v>
       </c>
       <c r="B1010" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="B1011" t="s">
         <v>1844</v>
@@ -15019,20 +15025,20 @@
         <v>1855</v>
       </c>
       <c r="B1017" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B1018" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="B1019" t="s">
         <v>1858</v>
@@ -15067,12 +15073,12 @@
         <v>1865</v>
       </c>
       <c r="B1023" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B1024" t="s">
         <v>1867</v>
@@ -15131,12 +15137,12 @@
         <v>1880</v>
       </c>
       <c r="B1031" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1032" t="s">
         <v>1882</v>
@@ -15211,12 +15217,12 @@
         <v>1899</v>
       </c>
       <c r="B1041" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B1042" t="s">
         <v>1901</v>
@@ -15227,44 +15233,44 @@
         <v>1902</v>
       </c>
       <c r="B1043" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B1044" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B1045" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="B1046" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1047" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1048" t="s">
         <v>1908</v>
@@ -15291,12 +15297,12 @@
         <v>1913</v>
       </c>
       <c r="B1051" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B1052" t="s">
         <v>1915</v>
@@ -15323,12 +15329,12 @@
         <v>1920</v>
       </c>
       <c r="B1055" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="B1056" t="s">
         <v>1922</v>
@@ -15363,12 +15369,12 @@
         <v>1929</v>
       </c>
       <c r="B1060" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B1061" t="s">
         <v>1931</v>
@@ -15379,12 +15385,12 @@
         <v>1932</v>
       </c>
       <c r="B1062" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B1063" t="s">
         <v>1934</v>
@@ -15475,12 +15481,12 @@
         <v>1955</v>
       </c>
       <c r="B1074" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="B1075" t="s">
         <v>1957</v>
@@ -15611,12 +15617,12 @@
         <v>1988</v>
       </c>
       <c r="B1091" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B1092" t="s">
         <v>1990</v>
@@ -15635,12 +15641,12 @@
         <v>1993</v>
       </c>
       <c r="B1094" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="B1095" t="s">
         <v>1995</v>
@@ -15739,12 +15745,12 @@
         <v>2018</v>
       </c>
       <c r="B1107" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B1108" t="s">
         <v>2020</v>
@@ -15819,44 +15825,44 @@
         <v>2037</v>
       </c>
       <c r="B1117" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="B1118" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B1119" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="B1120" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B1121" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="B1122" t="s">
         <v>2043</v>
@@ -15883,12 +15889,12 @@
         <v>2048</v>
       </c>
       <c r="B1125" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B1126" t="s">
         <v>2050</v>
@@ -15899,12 +15905,12 @@
         <v>2051</v>
       </c>
       <c r="B1127" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="B1128" t="s">
         <v>2053</v>
@@ -16091,12 +16097,12 @@
         <v>2098</v>
       </c>
       <c r="B1151" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="B1152" t="s">
         <v>2100</v>
@@ -16123,20 +16129,20 @@
         <v>2105</v>
       </c>
       <c r="B1155" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="B1156" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="B1157" t="s">
         <v>2108</v>
@@ -16259,12 +16265,12 @@
         <v>2137</v>
       </c>
       <c r="B1172" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="B1173" t="s">
         <v>2139</v>
@@ -16291,12 +16297,12 @@
         <v>2144</v>
       </c>
       <c r="B1176" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="B1177" t="s">
         <v>2146</v>
@@ -16323,12 +16329,12 @@
         <v>2151</v>
       </c>
       <c r="B1180" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="B1181" t="s">
         <v>2153</v>
@@ -16339,20 +16345,20 @@
         <v>2154</v>
       </c>
       <c r="B1182" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="B1183" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="B1184" t="s">
         <v>2157</v>
@@ -16363,12 +16369,12 @@
         <v>2158</v>
       </c>
       <c r="B1185" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="B1186" t="s">
         <v>2160</v>
@@ -16403,12 +16409,12 @@
         <v>2167</v>
       </c>
       <c r="B1190" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="B1191" t="s">
         <v>2169</v>
@@ -16422,8 +16428,16 @@
         <v>2171</v>
       </c>
     </row>
+    <row r="1193" spans="1:2">
+      <c r="A1193" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>2173</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1192"/>
+  <autoFilter ref="A1:B1193"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
